--- a/assets_output/07_multinomial_logistic_regression.xlsx
+++ b/assets_output/07_multinomial_logistic_regression.xlsx
@@ -13,10 +13,182 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="53">
+  <si>
+    <t>MNLogit: 'Outcomes 3.08 years after a person's first route started', table 0</t>
+  </si>
+  <si>
+    <t>Model:</t>
+  </si>
+  <si>
+    <t>Dependent Variable:</t>
+  </si>
+  <si>
+    <t>Date:</t>
+  </si>
+  <si>
+    <t>No. Observations:</t>
+  </si>
+  <si>
+    <t>Df Model:</t>
+  </si>
+  <si>
+    <t>Df Residuals:</t>
+  </si>
+  <si>
+    <t>Converged:</t>
+  </si>
+  <si>
+    <t>No. Iterations:</t>
+  </si>
+  <si>
+    <t>MNLogit</t>
+  </si>
+  <si>
+    <t>cli_outcome</t>
+  </si>
+  <si>
+    <t>2026-05-16 17:00</t>
+  </si>
+  <si>
+    <t>2056</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>2029</t>
+  </si>
+  <si>
+    <t>1.0000</t>
+  </si>
+  <si>
+    <t>9.0000</t>
+  </si>
+  <si>
+    <t>Method:</t>
+  </si>
+  <si>
+    <t>Pseudo R-squared:</t>
+  </si>
+  <si>
+    <t>AIC:</t>
+  </si>
+  <si>
+    <t>BIC:</t>
+  </si>
+  <si>
+    <t>Log-Likelihood:</t>
+  </si>
+  <si>
+    <t>LL-Null:</t>
+  </si>
+  <si>
+    <t>LLR p-value:</t>
+  </si>
+  <si>
+    <t>Scale:</t>
+  </si>
+  <si>
+    <t>MLE</t>
+  </si>
+  <si>
+    <t>0.111</t>
+  </si>
+  <si>
+    <t>4182.5573</t>
+  </si>
+  <si>
+    <t>4334.5273</t>
+  </si>
+  <si>
+    <t>-2064.3</t>
+  </si>
+  <si>
+    <t>-2322.2</t>
+  </si>
+  <si>
+    <t>8.4044e-94</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Outcomes 3.08 years after a person's first route started', table 1</t>
+  </si>
+  <si>
+    <t>cli_outcome = 0</t>
+  </si>
+  <si>
+    <t>Coef.</t>
+  </si>
+  <si>
+    <t>Std.Err.</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>P&gt;|t|</t>
+  </si>
+  <si>
+    <t>[0.025</t>
+  </si>
+  <si>
+    <t>0.975]</t>
+  </si>
+  <si>
+    <t>(Intercept)</t>
+  </si>
+  <si>
+    <t>uk_immigration_status_Non-EEA National</t>
+  </si>
+  <si>
+    <t>uk_immigration_status_EEA National</t>
+  </si>
+  <si>
+    <t>age_cat_34-</t>
+  </si>
+  <si>
+    <t>offending_True</t>
+  </si>
+  <si>
+    <t>physical_health_True</t>
+  </si>
+  <si>
+    <t>substance_use_True</t>
+  </si>
+  <si>
+    <t>rough_sleeping_True</t>
+  </si>
+  <si>
+    <t>sex_working_True</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Outcomes 3.08 years after a person's first route started', table 2</t>
+  </si>
+  <si>
+    <t>cli_outcome = 1</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Outcomes 3.08 years after a person's first route started', table 3</t>
+  </si>
+  <si>
+    <t>cli_outcome = 2</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -32,7 +204,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -40,12 +212,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -340,9 +530,951 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="B13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14">
+        <v>-1.4</v>
+      </c>
+      <c r="D14">
+        <v>0.1</v>
+      </c>
+      <c r="E14">
+        <v>-11.7</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>-1.6</v>
+      </c>
+      <c r="H14">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15">
+        <v>-0.7</v>
+      </c>
+      <c r="D15">
+        <v>0.2</v>
+      </c>
+      <c r="E15">
+        <v>-3.2</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>-1.1</v>
+      </c>
+      <c r="H15">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16">
+        <v>-0.2</v>
+      </c>
+      <c r="D16">
+        <v>0.3</v>
+      </c>
+      <c r="E16">
+        <v>-0.5</v>
+      </c>
+      <c r="F16">
+        <v>0.6</v>
+      </c>
+      <c r="G16">
+        <v>-0.8</v>
+      </c>
+      <c r="H16">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17">
+        <v>0.3</v>
+      </c>
+      <c r="D17">
+        <v>0.1</v>
+      </c>
+      <c r="E17">
+        <v>2.8</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0.1</v>
+      </c>
+      <c r="H17">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18">
+        <v>1.1</v>
+      </c>
+      <c r="D18">
+        <v>0.2</v>
+      </c>
+      <c r="E18">
+        <v>6.7</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0.8</v>
+      </c>
+      <c r="H18">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19">
+        <v>0.3</v>
+      </c>
+      <c r="D19">
+        <v>0.1</v>
+      </c>
+      <c r="E19">
+        <v>2.5</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0.1</v>
+      </c>
+      <c r="H19">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20">
+        <v>1.3</v>
+      </c>
+      <c r="D20">
+        <v>0.1</v>
+      </c>
+      <c r="E20">
+        <v>11.5</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>1.1</v>
+      </c>
+      <c r="H20">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21">
+        <v>0.6</v>
+      </c>
+      <c r="D21">
+        <v>0.2</v>
+      </c>
+      <c r="E21">
+        <v>3.9</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0.3</v>
+      </c>
+      <c r="H21">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22">
+        <v>2.1</v>
+      </c>
+      <c r="D22">
+        <v>0.8</v>
+      </c>
+      <c r="E22">
+        <v>2.7</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0.5</v>
+      </c>
+      <c r="H22">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="B25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26">
+        <v>-2</v>
+      </c>
+      <c r="D26">
+        <v>0.1</v>
+      </c>
+      <c r="E26">
+        <v>-14.1</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>-2.2</v>
+      </c>
+      <c r="H26">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27">
+        <v>-0.8</v>
+      </c>
+      <c r="D27">
+        <v>0.3</v>
+      </c>
+      <c r="E27">
+        <v>-2.9</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>-1.3</v>
+      </c>
+      <c r="H27">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28">
+        <v>0.1</v>
+      </c>
+      <c r="D28">
+        <v>0.3</v>
+      </c>
+      <c r="E28">
+        <v>0.2</v>
+      </c>
+      <c r="F28">
+        <v>0.8</v>
+      </c>
+      <c r="G28">
+        <v>-0.6</v>
+      </c>
+      <c r="H28">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29">
+        <v>0.3</v>
+      </c>
+      <c r="D29">
+        <v>0.1</v>
+      </c>
+      <c r="E29">
+        <v>2.6</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0.1</v>
+      </c>
+      <c r="H29">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30">
+        <v>1.4</v>
+      </c>
+      <c r="D30">
+        <v>0.2</v>
+      </c>
+      <c r="E30">
+        <v>8</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31">
+        <v>-0.1</v>
+      </c>
+      <c r="D31">
+        <v>0.1</v>
+      </c>
+      <c r="E31">
+        <v>-1</v>
+      </c>
+      <c r="F31">
+        <v>0.3</v>
+      </c>
+      <c r="G31">
+        <v>-0.4</v>
+      </c>
+      <c r="H31">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32">
+        <v>1.4</v>
+      </c>
+      <c r="D32">
+        <v>0.1</v>
+      </c>
+      <c r="E32">
+        <v>10.3</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>1.2</v>
+      </c>
+      <c r="H32">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33">
+        <v>1.3</v>
+      </c>
+      <c r="D33">
+        <v>0.2</v>
+      </c>
+      <c r="E33">
+        <v>7.9</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34">
+        <v>0.8</v>
+      </c>
+      <c r="E34">
+        <v>2.5</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0.4</v>
+      </c>
+      <c r="H34">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="B37" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38">
+        <v>-3.9</v>
+      </c>
+      <c r="D38">
+        <v>0.4</v>
+      </c>
+      <c r="E38">
+        <v>-10.1</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>-4.7</v>
+      </c>
+      <c r="H38">
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39">
+        <v>-0.5</v>
+      </c>
+      <c r="D39">
+        <v>0.8</v>
+      </c>
+      <c r="E39">
+        <v>-0.7</v>
+      </c>
+      <c r="F39">
+        <v>0.5</v>
+      </c>
+      <c r="G39">
+        <v>-2</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40">
+        <v>0.6</v>
+      </c>
+      <c r="D40">
+        <v>0.8</v>
+      </c>
+      <c r="E40">
+        <v>0.8</v>
+      </c>
+      <c r="F40">
+        <v>0.4</v>
+      </c>
+      <c r="G40">
+        <v>-0.9</v>
+      </c>
+      <c r="H40">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41">
+        <v>-1</v>
+      </c>
+      <c r="D41">
+        <v>0.5</v>
+      </c>
+      <c r="E41">
+        <v>-2.1</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>-2</v>
+      </c>
+      <c r="H41">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42">
+        <v>0.5</v>
+      </c>
+      <c r="D42">
+        <v>0.5</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <v>0.3</v>
+      </c>
+      <c r="G42">
+        <v>-0.5</v>
+      </c>
+      <c r="H42">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43">
+        <v>0.5</v>
+      </c>
+      <c r="D43">
+        <v>0.4</v>
+      </c>
+      <c r="E43">
+        <v>1.3</v>
+      </c>
+      <c r="F43">
+        <v>0.2</v>
+      </c>
+      <c r="G43">
+        <v>-0.2</v>
+      </c>
+      <c r="H43">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44">
+        <v>1.3</v>
+      </c>
+      <c r="D44">
+        <v>0.4</v>
+      </c>
+      <c r="E44">
+        <v>3.5</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0.6</v>
+      </c>
+      <c r="H44">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" t="s">
+        <v>47</v>
+      </c>
+      <c r="C45">
+        <v>0.1</v>
+      </c>
+      <c r="D45">
+        <v>0.5</v>
+      </c>
+      <c r="E45">
+        <v>0.1</v>
+      </c>
+      <c r="F45">
+        <v>0.9</v>
+      </c>
+      <c r="G45">
+        <v>-0.9</v>
+      </c>
+      <c r="H45">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" t="s">
+        <v>48</v>
+      </c>
+      <c r="C46">
+        <v>2.3</v>
+      </c>
+      <c r="D46">
+        <v>1.3</v>
+      </c>
+      <c r="E46">
+        <v>1.8</v>
+      </c>
+      <c r="F46">
+        <v>0.1</v>
+      </c>
+      <c r="G46">
+        <v>-0.2</v>
+      </c>
+      <c r="H46">
+        <v>4.8</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/assets_output/07_multinomial_logistic_regression.xlsx
+++ b/assets_output/07_multinomial_logistic_regression.xlsx
@@ -14,44 +14,269 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="163">
+  <si>
+    <t>MNLogit: 'Entry point into BAHSA services (pathway type and level)', table 0</t>
+  </si>
+  <si>
+    <t>Model:</t>
+  </si>
+  <si>
+    <t>Dependent Variable:</t>
+  </si>
+  <si>
+    <t>Date:</t>
+  </si>
+  <si>
+    <t>No. Observations:</t>
+  </si>
+  <si>
+    <t>Df Model:</t>
+  </si>
+  <si>
+    <t>Df Residuals:</t>
+  </si>
+  <si>
+    <t>Converged:</t>
+  </si>
+  <si>
+    <t>No. Iterations:</t>
+  </si>
+  <si>
+    <t>MNLogit</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>2026-05-17 15:47</t>
+  </si>
+  <si>
+    <t>4355</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>4260</t>
+  </si>
+  <si>
+    <t>1.0000</t>
+  </si>
+  <si>
+    <t>8.0000</t>
+  </si>
+  <si>
+    <t>Method:</t>
+  </si>
+  <si>
+    <t>Pseudo R-squared:</t>
+  </si>
+  <si>
+    <t>AIC:</t>
+  </si>
+  <si>
+    <t>BIC:</t>
+  </si>
+  <si>
+    <t>Log-Likelihood:</t>
+  </si>
+  <si>
+    <t>LL-Null:</t>
+  </si>
+  <si>
+    <t>LLR p-value:</t>
+  </si>
+  <si>
+    <t>Scale:</t>
+  </si>
+  <si>
+    <t>MLE</t>
+  </si>
+  <si>
+    <t>0.266</t>
+  </si>
+  <si>
+    <t>9043.2824</t>
+  </si>
+  <si>
+    <t>9649.2950</t>
+  </si>
+  <si>
+    <t>-4426.6</t>
+  </si>
+  <si>
+    <t>-6032.8</t>
+  </si>
+  <si>
+    <t>0.0000</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Entry point into BAHSA services (pathway type and level)', table 1</t>
+  </si>
+  <si>
+    <t>y = 0</t>
+  </si>
+  <si>
+    <t>Coef.</t>
+  </si>
+  <si>
+    <t>Std.Err.</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>P&gt;|t|</t>
+  </si>
+  <si>
+    <t>[0.025</t>
+  </si>
+  <si>
+    <t>0.975]</t>
+  </si>
+  <si>
+    <t>(Intercept)</t>
+  </si>
+  <si>
+    <t>referral_agency_Service provider (rough sleeping and SH)</t>
+  </si>
+  <si>
+    <t>referral_agency_Service provider (SU pathway, prison resettlement and SH)</t>
+  </si>
+  <si>
+    <t>referral_agency_Service provider (_other SH)</t>
+  </si>
+  <si>
+    <t>referral_agency__Others</t>
+  </si>
+  <si>
+    <t>referral_agency_Local authority (_other)</t>
+  </si>
+  <si>
+    <t>gender_Female</t>
+  </si>
+  <si>
+    <t>global_majority_Yes</t>
+  </si>
+  <si>
+    <t>uk_immigration_status_Non-EEA National</t>
+  </si>
+  <si>
+    <t>uk_immigration_status_EEA National</t>
+  </si>
+  <si>
+    <t>age_cat_34-</t>
+  </si>
+  <si>
+    <t>offending_True</t>
+  </si>
+  <si>
+    <t>physical_health_True</t>
+  </si>
+  <si>
+    <t>mental_health_True</t>
+  </si>
+  <si>
+    <t>substance_use_True</t>
+  </si>
+  <si>
+    <t>rough_sleeping_True</t>
+  </si>
+  <si>
+    <t>sex_working_True</t>
+  </si>
+  <si>
+    <t>risk_violence_abuse_True</t>
+  </si>
+  <si>
+    <t>risk_exploitation_True</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Entry point into BAHSA services (pathway type and level)', table 2</t>
+  </si>
+  <si>
+    <t>y = 1</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Entry point into BAHSA services (pathway type and level)', table 3</t>
+  </si>
+  <si>
+    <t>y = 2</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Entry point into BAHSA services (pathway type and level)', table 4</t>
+  </si>
+  <si>
+    <t>y = 3</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Entry point into BAHSA services (pathway type and level)', table 5</t>
+  </si>
+  <si>
+    <t>y = 4</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Route outcomes after 3.08 years', table 0</t>
+  </si>
+  <si>
+    <t>rt_outcome</t>
+  </si>
+  <si>
+    <t>2727</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>2694</t>
+  </si>
+  <si>
+    <t>9.0000</t>
+  </si>
+  <si>
+    <t>0.113</t>
+  </si>
+  <si>
+    <t>5715.6312</t>
+  </si>
+  <si>
+    <t>5910.6928</t>
+  </si>
+  <si>
+    <t>-2824.8</t>
+  </si>
+  <si>
+    <t>-3183.9</t>
+  </si>
+  <si>
+    <t>8.0006e-132</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Route outcomes after 3.08 years', table 1</t>
+  </si>
+  <si>
+    <t>rt_outcome = 0</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Route outcomes after 3.08 years', table 2</t>
+  </si>
+  <si>
+    <t>rt_outcome = 1</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Route outcomes after 3.08 years', table 3</t>
+  </si>
+  <si>
+    <t>rt_outcome = 2</t>
+  </si>
   <si>
     <t>MNLogit: 'Outcomes 3.08 years after a person's first route started', table 0</t>
   </si>
   <si>
-    <t>Model:</t>
-  </si>
-  <si>
-    <t>Dependent Variable:</t>
-  </si>
-  <si>
-    <t>Date:</t>
-  </si>
-  <si>
-    <t>No. Observations:</t>
-  </si>
-  <si>
-    <t>Df Model:</t>
-  </si>
-  <si>
-    <t>Df Residuals:</t>
-  </si>
-  <si>
-    <t>Converged:</t>
-  </si>
-  <si>
-    <t>No. Iterations:</t>
-  </si>
-  <si>
-    <t>MNLogit</t>
-  </si>
-  <si>
     <t>cli_outcome</t>
   </si>
   <si>
-    <t>2026-05-16 17:00</t>
-  </si>
-  <si>
     <t>2056</t>
   </si>
   <si>
@@ -61,39 +286,6 @@
     <t>2029</t>
   </si>
   <si>
-    <t>1.0000</t>
-  </si>
-  <si>
-    <t>9.0000</t>
-  </si>
-  <si>
-    <t>Method:</t>
-  </si>
-  <si>
-    <t>Pseudo R-squared:</t>
-  </si>
-  <si>
-    <t>AIC:</t>
-  </si>
-  <si>
-    <t>BIC:</t>
-  </si>
-  <si>
-    <t>Log-Likelihood:</t>
-  </si>
-  <si>
-    <t>LL-Null:</t>
-  </si>
-  <si>
-    <t>LLR p-value:</t>
-  </si>
-  <si>
-    <t>Scale:</t>
-  </si>
-  <si>
-    <t>MLE</t>
-  </si>
-  <si>
     <t>0.111</t>
   </si>
   <si>
@@ -118,51 +310,6 @@
     <t>cli_outcome = 0</t>
   </si>
   <si>
-    <t>Coef.</t>
-  </si>
-  <si>
-    <t>Std.Err.</t>
-  </si>
-  <si>
-    <t>t</t>
-  </si>
-  <si>
-    <t>P&gt;|t|</t>
-  </si>
-  <si>
-    <t>[0.025</t>
-  </si>
-  <si>
-    <t>0.975]</t>
-  </si>
-  <si>
-    <t>(Intercept)</t>
-  </si>
-  <si>
-    <t>uk_immigration_status_Non-EEA National</t>
-  </si>
-  <si>
-    <t>uk_immigration_status_EEA National</t>
-  </si>
-  <si>
-    <t>age_cat_34-</t>
-  </si>
-  <si>
-    <t>offending_True</t>
-  </si>
-  <si>
-    <t>physical_health_True</t>
-  </si>
-  <si>
-    <t>substance_use_True</t>
-  </si>
-  <si>
-    <t>rough_sleeping_True</t>
-  </si>
-  <si>
-    <t>sex_working_True</t>
-  </si>
-  <si>
     <t>MNLogit: 'Outcomes 3.08 years after a person's first route started', table 2</t>
   </si>
   <si>
@@ -173,6 +320,189 @@
   </si>
   <si>
     <t>cli_outcome = 2</t>
+  </si>
+  <si>
+    <t>MNLogit: 'People with multiple returns during 7.5 yrs', table 0</t>
+  </si>
+  <si>
+    <t>Logit</t>
+  </si>
+  <si>
+    <t>multiple_returns</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>2049</t>
+  </si>
+  <si>
+    <t>7.0000</t>
+  </si>
+  <si>
+    <t>0.150</t>
+  </si>
+  <si>
+    <t>1356.9324</t>
+  </si>
+  <si>
+    <t>1396.3320</t>
+  </si>
+  <si>
+    <t>-671.47</t>
+  </si>
+  <si>
+    <t>-790.07</t>
+  </si>
+  <si>
+    <t>2.2251e-48</t>
+  </si>
+  <si>
+    <t>MNLogit: 'People with multiple returns during 7.5 yrs', table 1</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>P&gt;|z|</t>
+  </si>
+  <si>
+    <t>MNLogit: 'People with a route in top 10% of route durations', table 0</t>
+  </si>
+  <si>
+    <t>has_longer_term_rt</t>
+  </si>
+  <si>
+    <t>6.0000</t>
+  </si>
+  <si>
+    <t>0.060</t>
+  </si>
+  <si>
+    <t>2047.5624</t>
+  </si>
+  <si>
+    <t>2086.9620</t>
+  </si>
+  <si>
+    <t>-1016.8</t>
+  </si>
+  <si>
+    <t>-1081.6</t>
+  </si>
+  <si>
+    <t>1.4603e-25</t>
+  </si>
+  <si>
+    <t>MNLogit: 'People with a route in top 10% of route durations', table 1</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Returns within 2 years after moving to independent accommodation', table 0</t>
+  </si>
+  <si>
+    <t>after_rt_ret_within_2y</t>
+  </si>
+  <si>
+    <t>730</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>726</t>
+  </si>
+  <si>
+    <t>0.200</t>
+  </si>
+  <si>
+    <t>165.9811</t>
+  </si>
+  <si>
+    <t>184.3532</t>
+  </si>
+  <si>
+    <t>-78.991</t>
+  </si>
+  <si>
+    <t>-98.709</t>
+  </si>
+  <si>
+    <t>1.4022e-08</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Returns within 2 years after moving to independent accommodation', table 1</t>
+  </si>
+  <si>
+    <t>lgbtq_plus_Yes</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Outcomes from individual placements', table 0</t>
+  </si>
+  <si>
+    <t>pl_outcome</t>
+  </si>
+  <si>
+    <t>5294</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>5222</t>
+  </si>
+  <si>
+    <t>0.064</t>
+  </si>
+  <si>
+    <t>17793.7659</t>
+  </si>
+  <si>
+    <t>18267.1176</t>
+  </si>
+  <si>
+    <t>-8824.9</t>
+  </si>
+  <si>
+    <t>-9430.9</t>
+  </si>
+  <si>
+    <t>2.8415e-210</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Outcomes from individual placements', table 1</t>
+  </si>
+  <si>
+    <t>pl_outcome = 0</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Outcomes from individual placements', table 2</t>
+  </si>
+  <si>
+    <t>pl_outcome = 1</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Outcomes from individual placements', table 3</t>
+  </si>
+  <si>
+    <t>pl_outcome = 2</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Outcomes from individual placements', table 4</t>
+  </si>
+  <si>
+    <t>pl_outcome = 3</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Outcomes from individual placements', table 5</t>
+  </si>
+  <si>
+    <t>pl_outcome = 4</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Outcomes from individual placements', table 6</t>
+  </si>
+  <si>
+    <t>pl_outcome = 5</t>
   </si>
 </sst>
 </file>
@@ -530,7 +860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H381"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -724,22 +1054,22 @@
         <v>40</v>
       </c>
       <c r="C14">
-        <v>-1.4</v>
+        <v>-2.2</v>
       </c>
       <c r="D14">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E14">
-        <v>-11.7</v>
+        <v>-11.3</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>-1.6</v>
+        <v>-2.5</v>
       </c>
       <c r="H14">
-        <v>-1.1</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -750,22 +1080,22 @@
         <v>41</v>
       </c>
       <c r="C15">
-        <v>-0.7</v>
+        <v>-0.2</v>
       </c>
       <c r="D15">
         <v>0.2</v>
       </c>
       <c r="E15">
-        <v>-3.2</v>
+        <v>-1.3</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G15">
-        <v>-1.1</v>
+        <v>-0.5</v>
       </c>
       <c r="H15">
-        <v>-0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -782,10 +1112,10 @@
         <v>0.3</v>
       </c>
       <c r="E16">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="F16">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G16">
         <v>-0.8</v>
@@ -805,19 +1135,19 @@
         <v>0.3</v>
       </c>
       <c r="D17">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E17">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G17">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="H17">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -828,22 +1158,22 @@
         <v>44</v>
       </c>
       <c r="C18">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E18">
-        <v>6.7</v>
+        <v>0.1</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="G18">
-        <v>0.8</v>
+        <v>-0.6</v>
       </c>
       <c r="H18">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -854,22 +1184,22 @@
         <v>45</v>
       </c>
       <c r="C19">
-        <v>0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="D19">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="E19">
-        <v>2.5</v>
+        <v>-1</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G19">
-        <v>0.1</v>
+        <v>-1.1</v>
       </c>
       <c r="H19">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -880,22 +1210,22 @@
         <v>46</v>
       </c>
       <c r="C20">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="D20">
         <v>0.1</v>
       </c>
       <c r="E20">
-        <v>11.5</v>
+        <v>13.8</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="H20">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -906,22 +1236,22 @@
         <v>47</v>
       </c>
       <c r="C21">
-        <v>0.6</v>
+        <v>-0</v>
       </c>
       <c r="D21">
         <v>0.2</v>
       </c>
       <c r="E21">
-        <v>3.9</v>
+        <v>-0.2</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="G21">
-        <v>0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="H21">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -932,378 +1262,428 @@
         <v>48</v>
       </c>
       <c r="C22">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="D22">
+        <v>0.2</v>
+      </c>
+      <c r="E22">
         <v>0.8</v>
       </c>
-      <c r="E22">
-        <v>2.7</v>
-      </c>
       <c r="F22">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G22">
-        <v>0.5</v>
+        <v>-0.3</v>
       </c>
       <c r="H22">
-        <v>3.6</v>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23">
+        <v>0.3</v>
+      </c>
+      <c r="D23">
+        <v>0.3</v>
+      </c>
+      <c r="E23">
+        <v>0.8</v>
+      </c>
+      <c r="F23">
+        <v>0.4</v>
+      </c>
+      <c r="G23">
+        <v>-0.4</v>
+      </c>
+      <c r="H23">
+        <v>0.9</v>
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" t="s">
-        <v>49</v>
+      <c r="A24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24">
+        <v>0.2</v>
+      </c>
+      <c r="D24">
+        <v>0.1</v>
+      </c>
+      <c r="E24">
+        <v>1.2</v>
+      </c>
+      <c r="F24">
+        <v>0.2</v>
+      </c>
+      <c r="G24">
+        <v>-0.1</v>
+      </c>
+      <c r="H24">
+        <v>0.4</v>
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="B25" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>39</v>
+      <c r="A25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25">
+        <v>-0.2</v>
+      </c>
+      <c r="D25">
+        <v>0.2</v>
+      </c>
+      <c r="E25">
+        <v>-1.3</v>
+      </c>
+      <c r="F25">
+        <v>0.2</v>
+      </c>
+      <c r="G25">
+        <v>-0.6</v>
+      </c>
+      <c r="H25">
+        <v>0.1</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C26">
-        <v>-2</v>
+        <v>-0.4</v>
       </c>
       <c r="D26">
         <v>0.1</v>
       </c>
       <c r="E26">
-        <v>-14.1</v>
+        <v>-2.8</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>-2.2</v>
+        <v>-0.6</v>
       </c>
       <c r="H26">
-        <v>-1.7</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C27">
-        <v>-0.8</v>
+        <v>0.1</v>
       </c>
       <c r="D27">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E27">
-        <v>-2.9</v>
+        <v>0.4</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G27">
-        <v>-1.3</v>
+        <v>-0.2</v>
       </c>
       <c r="H27">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C28">
-        <v>0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="D28">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E28">
-        <v>0.2</v>
+        <v>-4.6</v>
       </c>
       <c r="F28">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>-0.6</v>
+        <v>-0.9</v>
       </c>
       <c r="H28">
-        <v>0.8</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C29">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="D29">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E29">
-        <v>2.6</v>
+        <v>-1.7</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G29">
-        <v>0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="H29">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C30">
-        <v>1.4</v>
+        <v>-0.2</v>
       </c>
       <c r="D30">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E30">
-        <v>8</v>
+        <v>-0.6</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>-0.7</v>
       </c>
       <c r="H30">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C31">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>0.3</v>
       </c>
       <c r="F31">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="G31">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="H31">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C32">
-        <v>1.4</v>
+        <v>-0</v>
       </c>
       <c r="D32">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E32">
-        <v>10.3</v>
+        <v>-0.1</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="G32">
-        <v>1.2</v>
+        <v>-0.4</v>
       </c>
       <c r="H32">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B33" t="s">
-        <v>47</v>
-      </c>
-      <c r="C33">
-        <v>1.3</v>
-      </c>
-      <c r="D33">
-        <v>0.2</v>
-      </c>
-      <c r="E33">
-        <v>7.9</v>
-      </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-      <c r="H33">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B34" t="s">
-        <v>48</v>
-      </c>
-      <c r="C34">
-        <v>2</v>
-      </c>
-      <c r="D34">
-        <v>0.8</v>
-      </c>
-      <c r="E34">
-        <v>2.5</v>
-      </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-      <c r="G34">
-        <v>0.4</v>
-      </c>
-      <c r="H34">
-        <v>3.6</v>
+      <c r="A34" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="B35" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" t="s">
-        <v>51</v>
+      <c r="A36" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36">
+        <v>-2.8</v>
+      </c>
+      <c r="D36">
+        <v>0.3</v>
+      </c>
+      <c r="E36">
+        <v>-10.5</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>-3.3</v>
+      </c>
+      <c r="H36">
+        <v>-2.3</v>
       </c>
     </row>
     <row r="37" spans="1:8">
-      <c r="B37" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>39</v>
+      <c r="A37" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37">
+        <v>-0.5</v>
+      </c>
+      <c r="D37">
+        <v>0.3</v>
+      </c>
+      <c r="E37">
+        <v>-1.9</v>
+      </c>
+      <c r="F37">
+        <v>0.1</v>
+      </c>
+      <c r="G37">
+        <v>-1</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C38">
-        <v>-3.9</v>
+        <v>-1.2</v>
       </c>
       <c r="D38">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E38">
-        <v>-10.1</v>
+        <v>-1.7</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G38">
-        <v>-4.7</v>
+        <v>-2.7</v>
       </c>
       <c r="H38">
-        <v>-3.2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C39">
-        <v>-0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D39">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="E39">
-        <v>-0.7</v>
+        <v>2.2</v>
       </c>
       <c r="F39">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>-2</v>
+        <v>0.1</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B40" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C40">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="D40">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="E40">
         <v>0.8</v>
@@ -1312,166 +1692,7127 @@
         <v>0.4</v>
       </c>
       <c r="G40">
-        <v>-0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="H40">
-        <v>2.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C41">
         <v>-1</v>
       </c>
       <c r="D41">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E41">
-        <v>-2.1</v>
+        <v>-1.6</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G41">
-        <v>-2</v>
+        <v>-2.2</v>
       </c>
       <c r="H41">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C42">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="D42">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>10.3</v>
       </c>
       <c r="F42">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>-0.5</v>
+        <v>1.7</v>
       </c>
       <c r="H42">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B43" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C43">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="D43">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E43">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F43">
         <v>0.2</v>
       </c>
       <c r="G43">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="H43">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C44">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="D44">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E44">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G44">
-        <v>0.6</v>
+        <v>-0.4</v>
       </c>
       <c r="H44">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C45">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="D45">
         <v>0.5</v>
       </c>
       <c r="E45">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="F45">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G45">
         <v>-0.9</v>
       </c>
       <c r="H45">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46">
+        <v>0.1</v>
+      </c>
+      <c r="D46">
+        <v>0.2</v>
+      </c>
+      <c r="E46">
+        <v>0.3</v>
+      </c>
+      <c r="F46">
+        <v>0.7</v>
+      </c>
+      <c r="G46">
+        <v>-0.3</v>
+      </c>
+      <c r="H46">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47">
+        <v>-0.7</v>
+      </c>
+      <c r="D47">
+        <v>0.3</v>
+      </c>
+      <c r="E47">
+        <v>-2.4</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>-1.3</v>
+      </c>
+      <c r="H47">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" t="s">
+        <v>52</v>
+      </c>
+      <c r="C48">
+        <v>-0.1</v>
+      </c>
+      <c r="D48">
+        <v>0.2</v>
+      </c>
+      <c r="E48">
+        <v>-0.7</v>
+      </c>
+      <c r="F48">
+        <v>0.5</v>
+      </c>
+      <c r="G48">
+        <v>-0.5</v>
+      </c>
+      <c r="H48">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49">
+        <v>0.1</v>
+      </c>
+      <c r="D49">
+        <v>0.2</v>
+      </c>
+      <c r="E49">
+        <v>0.6</v>
+      </c>
+      <c r="F49">
+        <v>0.6</v>
+      </c>
+      <c r="G49">
+        <v>-0.3</v>
+      </c>
+      <c r="H49">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50">
+        <v>-1.1</v>
+      </c>
+      <c r="D50">
+        <v>0.2</v>
+      </c>
+      <c r="E50">
+        <v>-5.7</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>-1.5</v>
+      </c>
+      <c r="H50">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51">
+        <v>-0.7</v>
+      </c>
+      <c r="D51">
+        <v>0.3</v>
+      </c>
+      <c r="E51">
+        <v>-2.6</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>-1.2</v>
+      </c>
+      <c r="H51">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52">
+        <v>-0.5</v>
+      </c>
+      <c r="D52">
+        <v>0.5</v>
+      </c>
+      <c r="E52">
+        <v>-1.1</v>
+      </c>
+      <c r="F52">
+        <v>0.3</v>
+      </c>
+      <c r="G52">
+        <v>-1.4</v>
+      </c>
+      <c r="H52">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C53">
+        <v>0.3</v>
+      </c>
+      <c r="D53">
+        <v>0.2</v>
+      </c>
+      <c r="E53">
+        <v>1.4</v>
+      </c>
+      <c r="F53">
+        <v>0.2</v>
+      </c>
+      <c r="G53">
+        <v>-0.1</v>
+      </c>
+      <c r="H53">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" t="s">
+        <v>58</v>
+      </c>
+      <c r="C54">
+        <v>-0.1</v>
+      </c>
+      <c r="D54">
+        <v>0.3</v>
+      </c>
+      <c r="E54">
+        <v>-0.3</v>
+      </c>
+      <c r="F54">
+        <v>0.8</v>
+      </c>
+      <c r="G54">
+        <v>-0.6</v>
+      </c>
+      <c r="H54">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="B57" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58" t="s">
+        <v>40</v>
+      </c>
+      <c r="C58">
+        <v>-0.2</v>
+      </c>
+      <c r="D58">
+        <v>0.1</v>
+      </c>
+      <c r="E58">
+        <v>-1.3</v>
+      </c>
+      <c r="F58">
+        <v>0.2</v>
+      </c>
+      <c r="G58">
+        <v>-0.4</v>
+      </c>
+      <c r="H58">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" t="s">
+        <v>41</v>
+      </c>
+      <c r="C59">
+        <v>-0</v>
+      </c>
+      <c r="D59">
+        <v>0.1</v>
+      </c>
+      <c r="E59">
+        <v>-0.2</v>
+      </c>
+      <c r="F59">
+        <v>0.8</v>
+      </c>
+      <c r="G59">
+        <v>-0.3</v>
+      </c>
+      <c r="H59">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60" t="s">
+        <v>42</v>
+      </c>
+      <c r="C60">
+        <v>-0.7</v>
+      </c>
+      <c r="D60">
+        <v>0.3</v>
+      </c>
+      <c r="E60">
+        <v>-2</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>-1.3</v>
+      </c>
+      <c r="H60">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B61" t="s">
+        <v>43</v>
+      </c>
+      <c r="C61">
+        <v>0.4</v>
+      </c>
+      <c r="D61">
+        <v>0.2</v>
+      </c>
+      <c r="E61">
+        <v>2.1</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" t="s">
+        <v>44</v>
+      </c>
+      <c r="C62">
+        <v>0.5</v>
+      </c>
+      <c r="D62">
+        <v>0.3</v>
+      </c>
+      <c r="E62">
+        <v>1.9</v>
+      </c>
+      <c r="F62">
+        <v>0.1</v>
+      </c>
+      <c r="G62">
+        <v>-0</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B63" t="s">
+        <v>45</v>
+      </c>
+      <c r="C63">
+        <v>-0.3</v>
+      </c>
+      <c r="D63">
+        <v>0.3</v>
+      </c>
+      <c r="E63">
+        <v>-1</v>
+      </c>
+      <c r="F63">
+        <v>0.3</v>
+      </c>
+      <c r="G63">
+        <v>-0.8</v>
+      </c>
+      <c r="H63">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B64" t="s">
+        <v>46</v>
+      </c>
+      <c r="C64">
+        <v>0.6</v>
+      </c>
+      <c r="D64">
+        <v>0.1</v>
+      </c>
+      <c r="E64">
+        <v>4.9</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0.4</v>
+      </c>
+      <c r="H64">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B65" t="s">
+        <v>47</v>
+      </c>
+      <c r="C65">
+        <v>0.5</v>
+      </c>
+      <c r="D65">
+        <v>0.1</v>
+      </c>
+      <c r="E65">
+        <v>4.4</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0.3</v>
+      </c>
+      <c r="H65">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B66" t="s">
         <v>48</v>
       </c>
-      <c r="C46">
+      <c r="C66">
+        <v>0.6</v>
+      </c>
+      <c r="D66">
+        <v>0.2</v>
+      </c>
+      <c r="E66">
+        <v>3.9</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>0.3</v>
+      </c>
+      <c r="H66">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B67" t="s">
+        <v>49</v>
+      </c>
+      <c r="C67">
+        <v>0.3</v>
+      </c>
+      <c r="D67">
+        <v>0.3</v>
+      </c>
+      <c r="E67">
+        <v>1.1</v>
+      </c>
+      <c r="F67">
+        <v>0.3</v>
+      </c>
+      <c r="G67">
+        <v>-0.2</v>
+      </c>
+      <c r="H67">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B68" t="s">
+        <v>50</v>
+      </c>
+      <c r="C68">
+        <v>0.2</v>
+      </c>
+      <c r="D68">
+        <v>0.1</v>
+      </c>
+      <c r="E68">
+        <v>2</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B69" t="s">
+        <v>51</v>
+      </c>
+      <c r="C69">
+        <v>-1.7</v>
+      </c>
+      <c r="D69">
+        <v>0.2</v>
+      </c>
+      <c r="E69">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>-2.1</v>
+      </c>
+      <c r="H69">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B70" t="s">
+        <v>52</v>
+      </c>
+      <c r="C70">
+        <v>-0.4</v>
+      </c>
+      <c r="D70">
+        <v>0.1</v>
+      </c>
+      <c r="E70">
+        <v>-3.1</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>-0.6</v>
+      </c>
+      <c r="H70">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B71" t="s">
+        <v>53</v>
+      </c>
+      <c r="C71">
+        <v>-0.6</v>
+      </c>
+      <c r="D71">
+        <v>0.1</v>
+      </c>
+      <c r="E71">
+        <v>-5.5</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>-0.8</v>
+      </c>
+      <c r="H71">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B72" t="s">
+        <v>54</v>
+      </c>
+      <c r="C72">
+        <v>-1.8</v>
+      </c>
+      <c r="D72">
+        <v>0.1</v>
+      </c>
+      <c r="E72">
+        <v>-14.2</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>-2</v>
+      </c>
+      <c r="H72">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B73" t="s">
+        <v>55</v>
+      </c>
+      <c r="C73">
+        <v>-0.3</v>
+      </c>
+      <c r="D73">
+        <v>0.1</v>
+      </c>
+      <c r="E73">
+        <v>-2.5</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>-0.6</v>
+      </c>
+      <c r="H73">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B74" t="s">
+        <v>56</v>
+      </c>
+      <c r="C74">
+        <v>-2.1</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="E74">
+        <v>-2.1</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>-4.2</v>
+      </c>
+      <c r="H74">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B75" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75">
+        <v>0.2</v>
+      </c>
+      <c r="D75">
+        <v>0.1</v>
+      </c>
+      <c r="E75">
+        <v>1.1</v>
+      </c>
+      <c r="F75">
+        <v>0.3</v>
+      </c>
+      <c r="G75">
+        <v>-0.1</v>
+      </c>
+      <c r="H75">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B76" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76">
+        <v>-1</v>
+      </c>
+      <c r="D76">
+        <v>0.3</v>
+      </c>
+      <c r="E76">
+        <v>-3.8</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>-1.5</v>
+      </c>
+      <c r="H76">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="B79" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B80" t="s">
+        <v>40</v>
+      </c>
+      <c r="C80">
+        <v>-1.9</v>
+      </c>
+      <c r="D80">
+        <v>0.2</v>
+      </c>
+      <c r="E80">
+        <v>-11.2</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>-2.2</v>
+      </c>
+      <c r="H80">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B81" t="s">
+        <v>41</v>
+      </c>
+      <c r="C81">
+        <v>0.1</v>
+      </c>
+      <c r="D81">
+        <v>0.1</v>
+      </c>
+      <c r="E81">
+        <v>0.7</v>
+      </c>
+      <c r="F81">
+        <v>0.5</v>
+      </c>
+      <c r="G81">
+        <v>-0.2</v>
+      </c>
+      <c r="H81">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B82" t="s">
+        <v>42</v>
+      </c>
+      <c r="C82">
+        <v>3.2</v>
+      </c>
+      <c r="D82">
+        <v>0.1</v>
+      </c>
+      <c r="E82">
+        <v>22.9</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>2.9</v>
+      </c>
+      <c r="H82">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B83" t="s">
+        <v>43</v>
+      </c>
+      <c r="C83">
+        <v>-0.3</v>
+      </c>
+      <c r="D83">
+        <v>0.2</v>
+      </c>
+      <c r="E83">
+        <v>-1.4</v>
+      </c>
+      <c r="F83">
+        <v>0.2</v>
+      </c>
+      <c r="G83">
+        <v>-0.8</v>
+      </c>
+      <c r="H83">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B84" t="s">
+        <v>44</v>
+      </c>
+      <c r="C84">
+        <v>0.2</v>
+      </c>
+      <c r="D84">
+        <v>0.4</v>
+      </c>
+      <c r="E84">
+        <v>0.5</v>
+      </c>
+      <c r="F84">
+        <v>0.6</v>
+      </c>
+      <c r="G84">
+        <v>-0.6</v>
+      </c>
+      <c r="H84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B85" t="s">
+        <v>45</v>
+      </c>
+      <c r="C85">
+        <v>0.1</v>
+      </c>
+      <c r="D85">
+        <v>0.4</v>
+      </c>
+      <c r="E85">
+        <v>0.2</v>
+      </c>
+      <c r="F85">
+        <v>0.8</v>
+      </c>
+      <c r="G85">
+        <v>-0.6</v>
+      </c>
+      <c r="H85">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B86" t="s">
+        <v>46</v>
+      </c>
+      <c r="C86">
+        <v>-0.1</v>
+      </c>
+      <c r="D86">
+        <v>0.2</v>
+      </c>
+      <c r="E86">
+        <v>-0.6</v>
+      </c>
+      <c r="F86">
+        <v>0.6</v>
+      </c>
+      <c r="G86">
+        <v>-0.4</v>
+      </c>
+      <c r="H86">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B87" t="s">
+        <v>47</v>
+      </c>
+      <c r="C87">
+        <v>-0.5</v>
+      </c>
+      <c r="D87">
+        <v>0.2</v>
+      </c>
+      <c r="E87">
+        <v>-3.1</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>-0.9</v>
+      </c>
+      <c r="H87">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B88" t="s">
+        <v>48</v>
+      </c>
+      <c r="C88">
+        <v>-0.8</v>
+      </c>
+      <c r="D88">
+        <v>0.4</v>
+      </c>
+      <c r="E88">
+        <v>-2.1</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>-1.5</v>
+      </c>
+      <c r="H88">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B89" t="s">
+        <v>49</v>
+      </c>
+      <c r="C89">
+        <v>-0.3</v>
+      </c>
+      <c r="D89">
+        <v>0.4</v>
+      </c>
+      <c r="E89">
+        <v>-0.8</v>
+      </c>
+      <c r="F89">
+        <v>0.4</v>
+      </c>
+      <c r="G89">
+        <v>-1</v>
+      </c>
+      <c r="H89">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B90" t="s">
+        <v>50</v>
+      </c>
+      <c r="C90">
+        <v>-0.1</v>
+      </c>
+      <c r="D90">
+        <v>0.1</v>
+      </c>
+      <c r="E90">
+        <v>-0.6</v>
+      </c>
+      <c r="F90">
+        <v>0.6</v>
+      </c>
+      <c r="G90">
+        <v>-0.3</v>
+      </c>
+      <c r="H90">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B91" t="s">
+        <v>51</v>
+      </c>
+      <c r="C91">
+        <v>-0.4</v>
+      </c>
+      <c r="D91">
+        <v>0.1</v>
+      </c>
+      <c r="E91">
+        <v>-3.1</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>-0.6</v>
+      </c>
+      <c r="H91">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B92" t="s">
+        <v>52</v>
+      </c>
+      <c r="C92">
+        <v>-0.4</v>
+      </c>
+      <c r="D92">
+        <v>0.1</v>
+      </c>
+      <c r="E92">
+        <v>-3.7</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>-0.6</v>
+      </c>
+      <c r="H92">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B93" t="s">
+        <v>53</v>
+      </c>
+      <c r="C93">
+        <v>-0.2</v>
+      </c>
+      <c r="D93">
+        <v>0.1</v>
+      </c>
+      <c r="E93">
+        <v>-1.5</v>
+      </c>
+      <c r="F93">
+        <v>0.1</v>
+      </c>
+      <c r="G93">
+        <v>-0.4</v>
+      </c>
+      <c r="H93">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B94" t="s">
+        <v>54</v>
+      </c>
+      <c r="C94">
+        <v>0.8</v>
+      </c>
+      <c r="D94">
+        <v>0.1</v>
+      </c>
+      <c r="E94">
+        <v>5.5</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>0.5</v>
+      </c>
+      <c r="H94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B95" t="s">
+        <v>55</v>
+      </c>
+      <c r="C95">
+        <v>-0.3</v>
+      </c>
+      <c r="D95">
+        <v>0.1</v>
+      </c>
+      <c r="E95">
+        <v>-2.2</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>-0.5</v>
+      </c>
+      <c r="H95">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B96" t="s">
+        <v>56</v>
+      </c>
+      <c r="C96">
+        <v>-0.1</v>
+      </c>
+      <c r="D96">
+        <v>0.4</v>
+      </c>
+      <c r="E96">
+        <v>-0.2</v>
+      </c>
+      <c r="F96">
+        <v>0.9</v>
+      </c>
+      <c r="G96">
+        <v>-0.8</v>
+      </c>
+      <c r="H96">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B97" t="s">
+        <v>57</v>
+      </c>
+      <c r="C97">
+        <v>-0.2</v>
+      </c>
+      <c r="D97">
+        <v>0.2</v>
+      </c>
+      <c r="E97">
+        <v>-1.2</v>
+      </c>
+      <c r="F97">
+        <v>0.2</v>
+      </c>
+      <c r="G97">
+        <v>-0.5</v>
+      </c>
+      <c r="H97">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B98" t="s">
+        <v>58</v>
+      </c>
+      <c r="C98">
+        <v>-0.7</v>
+      </c>
+      <c r="D98">
+        <v>0.2</v>
+      </c>
+      <c r="E98">
+        <v>-3.3</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>-1.2</v>
+      </c>
+      <c r="H98">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="B101" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B102" t="s">
+        <v>40</v>
+      </c>
+      <c r="C102">
+        <v>-2.8</v>
+      </c>
+      <c r="D102">
+        <v>0.3</v>
+      </c>
+      <c r="E102">
+        <v>-9.5</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>-3.4</v>
+      </c>
+      <c r="H102">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B103" t="s">
+        <v>41</v>
+      </c>
+      <c r="C103">
+        <v>0.3</v>
+      </c>
+      <c r="D103">
+        <v>0.4</v>
+      </c>
+      <c r="E103">
+        <v>0.8</v>
+      </c>
+      <c r="F103">
+        <v>0.4</v>
+      </c>
+      <c r="G103">
+        <v>-0.5</v>
+      </c>
+      <c r="H103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B104" t="s">
+        <v>42</v>
+      </c>
+      <c r="C104">
+        <v>4.3</v>
+      </c>
+      <c r="D104">
+        <v>0.3</v>
+      </c>
+      <c r="E104">
+        <v>15.8</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>3.7</v>
+      </c>
+      <c r="H104">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B105" t="s">
+        <v>43</v>
+      </c>
+      <c r="C105">
+        <v>-0.2</v>
+      </c>
+      <c r="D105">
+        <v>0.6</v>
+      </c>
+      <c r="E105">
+        <v>-0.2</v>
+      </c>
+      <c r="F105">
+        <v>0.8</v>
+      </c>
+      <c r="G105">
+        <v>-1.4</v>
+      </c>
+      <c r="H105">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B106" t="s">
+        <v>44</v>
+      </c>
+      <c r="C106">
+        <v>0.8</v>
+      </c>
+      <c r="D106">
+        <v>0.8</v>
+      </c>
+      <c r="E106">
+        <v>1.1</v>
+      </c>
+      <c r="F106">
+        <v>0.3</v>
+      </c>
+      <c r="G106">
+        <v>-0.7</v>
+      </c>
+      <c r="H106">
         <v>2.3</v>
       </c>
-      <c r="D46">
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B107" t="s">
+        <v>45</v>
+      </c>
+      <c r="C107">
+        <v>1.1</v>
+      </c>
+      <c r="D107">
+        <v>0.6</v>
+      </c>
+      <c r="E107">
+        <v>1.9</v>
+      </c>
+      <c r="F107">
+        <v>0.1</v>
+      </c>
+      <c r="G107">
+        <v>-0</v>
+      </c>
+      <c r="H107">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B108" t="s">
+        <v>46</v>
+      </c>
+      <c r="C108">
+        <v>0.2</v>
+      </c>
+      <c r="D108">
+        <v>0.2</v>
+      </c>
+      <c r="E108">
+        <v>0.7</v>
+      </c>
+      <c r="F108">
+        <v>0.5</v>
+      </c>
+      <c r="G108">
+        <v>-0.3</v>
+      </c>
+      <c r="H108">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B109" t="s">
+        <v>47</v>
+      </c>
+      <c r="C109">
+        <v>-0.2</v>
+      </c>
+      <c r="D109">
+        <v>0.3</v>
+      </c>
+      <c r="E109">
+        <v>-0.7</v>
+      </c>
+      <c r="F109">
+        <v>0.5</v>
+      </c>
+      <c r="G109">
+        <v>-0.7</v>
+      </c>
+      <c r="H109">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B110" t="s">
+        <v>48</v>
+      </c>
+      <c r="C110">
+        <v>-0.5</v>
+      </c>
+      <c r="D110">
+        <v>0.5</v>
+      </c>
+      <c r="E110">
+        <v>-1</v>
+      </c>
+      <c r="F110">
+        <v>0.3</v>
+      </c>
+      <c r="G110">
+        <v>-1.6</v>
+      </c>
+      <c r="H110">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B111" t="s">
+        <v>49</v>
+      </c>
+      <c r="C111">
+        <v>0.8</v>
+      </c>
+      <c r="D111">
+        <v>0.5</v>
+      </c>
+      <c r="E111">
+        <v>1.6</v>
+      </c>
+      <c r="F111">
+        <v>0.1</v>
+      </c>
+      <c r="G111">
+        <v>-0.2</v>
+      </c>
+      <c r="H111">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B112" t="s">
+        <v>50</v>
+      </c>
+      <c r="C112">
+        <v>-0.4</v>
+      </c>
+      <c r="D112">
+        <v>0.2</v>
+      </c>
+      <c r="E112">
+        <v>-1.8</v>
+      </c>
+      <c r="F112">
+        <v>0.1</v>
+      </c>
+      <c r="G112">
+        <v>-0.8</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B113" t="s">
+        <v>51</v>
+      </c>
+      <c r="C113">
+        <v>-1.2</v>
+      </c>
+      <c r="D113">
+        <v>0.2</v>
+      </c>
+      <c r="E113">
+        <v>-4.9</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>-1.6</v>
+      </c>
+      <c r="H113">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B114" t="s">
+        <v>52</v>
+      </c>
+      <c r="C114">
+        <v>-0.6</v>
+      </c>
+      <c r="D114">
+        <v>0.2</v>
+      </c>
+      <c r="E114">
+        <v>-3.3</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <v>-1</v>
+      </c>
+      <c r="H114">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B115" t="s">
+        <v>53</v>
+      </c>
+      <c r="C115">
+        <v>-0.3</v>
+      </c>
+      <c r="D115">
+        <v>0.2</v>
+      </c>
+      <c r="E115">
+        <v>-1.8</v>
+      </c>
+      <c r="F115">
+        <v>0.1</v>
+      </c>
+      <c r="G115">
+        <v>-0.7</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B116" t="s">
+        <v>54</v>
+      </c>
+      <c r="C116">
+        <v>-0.3</v>
+      </c>
+      <c r="D116">
+        <v>0.2</v>
+      </c>
+      <c r="E116">
+        <v>-1.4</v>
+      </c>
+      <c r="F116">
+        <v>0.2</v>
+      </c>
+      <c r="G116">
+        <v>-0.7</v>
+      </c>
+      <c r="H116">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B117" t="s">
+        <v>55</v>
+      </c>
+      <c r="C117">
+        <v>-0.9</v>
+      </c>
+      <c r="D117">
+        <v>0.3</v>
+      </c>
+      <c r="E117">
+        <v>-3.6</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>-1.4</v>
+      </c>
+      <c r="H117">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B118" t="s">
+        <v>56</v>
+      </c>
+      <c r="C118">
+        <v>0.5</v>
+      </c>
+      <c r="D118">
+        <v>0.7</v>
+      </c>
+      <c r="E118">
+        <v>0.7</v>
+      </c>
+      <c r="F118">
+        <v>0.5</v>
+      </c>
+      <c r="G118">
+        <v>-0.9</v>
+      </c>
+      <c r="H118">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B119" t="s">
+        <v>57</v>
+      </c>
+      <c r="C119">
+        <v>-1.1</v>
+      </c>
+      <c r="D119">
+        <v>0.4</v>
+      </c>
+      <c r="E119">
+        <v>-2.8</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <v>-1.9</v>
+      </c>
+      <c r="H119">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B120" t="s">
+        <v>58</v>
+      </c>
+      <c r="C120">
+        <v>-0.6</v>
+      </c>
+      <c r="D120">
+        <v>0.4</v>
+      </c>
+      <c r="E120">
+        <v>-1.4</v>
+      </c>
+      <c r="F120">
+        <v>0.2</v>
+      </c>
+      <c r="G120">
+        <v>-1.4</v>
+      </c>
+      <c r="H120">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="B123" s="1">
+        <v>0</v>
+      </c>
+      <c r="C123" s="1">
+        <v>1</v>
+      </c>
+      <c r="D123" s="1">
+        <v>2</v>
+      </c>
+      <c r="E123" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" s="1">
+        <v>0</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1</v>
+      </c>
+      <c r="C124" t="s">
+        <v>9</v>
+      </c>
+      <c r="D124" t="s">
+        <v>17</v>
+      </c>
+      <c r="E124" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" s="1">
+        <v>1</v>
+      </c>
+      <c r="B125" t="s">
+        <v>2</v>
+      </c>
+      <c r="C125" t="s">
+        <v>68</v>
+      </c>
+      <c r="D125" t="s">
+        <v>18</v>
+      </c>
+      <c r="E125" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" s="1">
+        <v>2</v>
+      </c>
+      <c r="B126" t="s">
+        <v>3</v>
+      </c>
+      <c r="C126" t="s">
+        <v>11</v>
+      </c>
+      <c r="D126" t="s">
+        <v>19</v>
+      </c>
+      <c r="E126" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" s="1">
+        <v>3</v>
+      </c>
+      <c r="B127" t="s">
+        <v>4</v>
+      </c>
+      <c r="C127" t="s">
+        <v>69</v>
+      </c>
+      <c r="D127" t="s">
+        <v>20</v>
+      </c>
+      <c r="E127" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" s="1">
+        <v>4</v>
+      </c>
+      <c r="B128" t="s">
+        <v>5</v>
+      </c>
+      <c r="C128" t="s">
+        <v>70</v>
+      </c>
+      <c r="D128" t="s">
+        <v>21</v>
+      </c>
+      <c r="E128" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" s="1">
+        <v>5</v>
+      </c>
+      <c r="B129" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" t="s">
+        <v>71</v>
+      </c>
+      <c r="D129" t="s">
+        <v>22</v>
+      </c>
+      <c r="E129" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" s="1">
+        <v>6</v>
+      </c>
+      <c r="B130" t="s">
+        <v>7</v>
+      </c>
+      <c r="C130" t="s">
+        <v>15</v>
+      </c>
+      <c r="D130" t="s">
+        <v>23</v>
+      </c>
+      <c r="E130" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" s="1">
+        <v>7</v>
+      </c>
+      <c r="B131" t="s">
+        <v>8</v>
+      </c>
+      <c r="C131" t="s">
+        <v>72</v>
+      </c>
+      <c r="D131" t="s">
+        <v>24</v>
+      </c>
+      <c r="E131" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="B134" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B135" t="s">
+        <v>40</v>
+      </c>
+      <c r="C135">
+        <v>-0.9</v>
+      </c>
+      <c r="D135">
+        <v>0.1</v>
+      </c>
+      <c r="E135">
+        <v>-8</v>
+      </c>
+      <c r="F135">
+        <v>0</v>
+      </c>
+      <c r="G135">
+        <v>-1.1</v>
+      </c>
+      <c r="H135">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B136" t="s">
+        <v>46</v>
+      </c>
+      <c r="C136">
+        <v>-0.2</v>
+      </c>
+      <c r="D136">
+        <v>0.1</v>
+      </c>
+      <c r="E136">
+        <v>-1.9</v>
+      </c>
+      <c r="F136">
+        <v>0.1</v>
+      </c>
+      <c r="G136">
+        <v>-0.5</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B137" t="s">
+        <v>48</v>
+      </c>
+      <c r="C137">
+        <v>-0.5</v>
+      </c>
+      <c r="D137">
+        <v>0.2</v>
+      </c>
+      <c r="E137">
+        <v>-3</v>
+      </c>
+      <c r="F137">
+        <v>0</v>
+      </c>
+      <c r="G137">
+        <v>-0.9</v>
+      </c>
+      <c r="H137">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B138" t="s">
+        <v>49</v>
+      </c>
+      <c r="C138">
+        <v>-0.2</v>
+      </c>
+      <c r="D138">
+        <v>0.3</v>
+      </c>
+      <c r="E138">
+        <v>-0.6</v>
+      </c>
+      <c r="F138">
+        <v>0.5</v>
+      </c>
+      <c r="G138">
+        <v>-0.8</v>
+      </c>
+      <c r="H138">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B139" t="s">
+        <v>50</v>
+      </c>
+      <c r="C139">
+        <v>0.3</v>
+      </c>
+      <c r="D139">
+        <v>0.1</v>
+      </c>
+      <c r="E139">
+        <v>2.7</v>
+      </c>
+      <c r="F139">
+        <v>0</v>
+      </c>
+      <c r="G139">
+        <v>0.1</v>
+      </c>
+      <c r="H139">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B140" t="s">
+        <v>51</v>
+      </c>
+      <c r="C140">
+        <v>1</v>
+      </c>
+      <c r="D140">
+        <v>0.2</v>
+      </c>
+      <c r="E140">
+        <v>6.7</v>
+      </c>
+      <c r="F140">
+        <v>0</v>
+      </c>
+      <c r="G140">
+        <v>0.7</v>
+      </c>
+      <c r="H140">
         <v>1.3</v>
       </c>
-      <c r="E46">
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B141" t="s">
+        <v>52</v>
+      </c>
+      <c r="C141">
+        <v>0.2</v>
+      </c>
+      <c r="D141">
+        <v>0.1</v>
+      </c>
+      <c r="E141">
+        <v>2.2</v>
+      </c>
+      <c r="F141">
+        <v>0</v>
+      </c>
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B142" t="s">
+        <v>54</v>
+      </c>
+      <c r="C142">
+        <v>1.3</v>
+      </c>
+      <c r="D142">
+        <v>0.1</v>
+      </c>
+      <c r="E142">
+        <v>11.5</v>
+      </c>
+      <c r="F142">
+        <v>0</v>
+      </c>
+      <c r="G142">
+        <v>1</v>
+      </c>
+      <c r="H142">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B143" t="s">
+        <v>55</v>
+      </c>
+      <c r="C143">
+        <v>0.5</v>
+      </c>
+      <c r="D143">
+        <v>0.1</v>
+      </c>
+      <c r="E143">
+        <v>3.7</v>
+      </c>
+      <c r="F143">
+        <v>0</v>
+      </c>
+      <c r="G143">
+        <v>0.2</v>
+      </c>
+      <c r="H143">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B144" t="s">
+        <v>56</v>
+      </c>
+      <c r="C144">
+        <v>2</v>
+      </c>
+      <c r="D144">
+        <v>0.8</v>
+      </c>
+      <c r="E144">
+        <v>2.7</v>
+      </c>
+      <c r="F144">
+        <v>0</v>
+      </c>
+      <c r="G144">
+        <v>0.5</v>
+      </c>
+      <c r="H144">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B145" t="s">
+        <v>58</v>
+      </c>
+      <c r="C145">
+        <v>0.4</v>
+      </c>
+      <c r="D145">
+        <v>0.2</v>
+      </c>
+      <c r="E145">
+        <v>2.1</v>
+      </c>
+      <c r="F145">
+        <v>0</v>
+      </c>
+      <c r="G145">
+        <v>0</v>
+      </c>
+      <c r="H145">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="B148" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H148" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B149" t="s">
+        <v>40</v>
+      </c>
+      <c r="C149">
+        <v>-1.4</v>
+      </c>
+      <c r="D149">
+        <v>0.1</v>
+      </c>
+      <c r="E149">
+        <v>-11.2</v>
+      </c>
+      <c r="F149">
+        <v>0</v>
+      </c>
+      <c r="G149">
+        <v>-1.6</v>
+      </c>
+      <c r="H149">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B150" t="s">
+        <v>46</v>
+      </c>
+      <c r="C150">
+        <v>-0.3</v>
+      </c>
+      <c r="D150">
+        <v>0.1</v>
+      </c>
+      <c r="E150">
+        <v>-2.6</v>
+      </c>
+      <c r="F150">
+        <v>0</v>
+      </c>
+      <c r="G150">
+        <v>-0.6</v>
+      </c>
+      <c r="H150">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B151" t="s">
+        <v>48</v>
+      </c>
+      <c r="C151">
+        <v>-0.8</v>
+      </c>
+      <c r="D151">
+        <v>0.2</v>
+      </c>
+      <c r="E151">
+        <v>-3.5</v>
+      </c>
+      <c r="F151">
+        <v>0</v>
+      </c>
+      <c r="G151">
+        <v>-1.2</v>
+      </c>
+      <c r="H151">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B152" t="s">
+        <v>49</v>
+      </c>
+      <c r="C152">
+        <v>0.2</v>
+      </c>
+      <c r="D152">
+        <v>0.3</v>
+      </c>
+      <c r="E152">
+        <v>0.5</v>
+      </c>
+      <c r="F152">
+        <v>0.6</v>
+      </c>
+      <c r="G152">
+        <v>-0.4</v>
+      </c>
+      <c r="H152">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B153" t="s">
+        <v>50</v>
+      </c>
+      <c r="C153">
+        <v>0.2</v>
+      </c>
+      <c r="D153">
+        <v>0.1</v>
+      </c>
+      <c r="E153">
         <v>1.8</v>
       </c>
-      <c r="F46">
-        <v>0.1</v>
-      </c>
-      <c r="G46">
+      <c r="F153">
+        <v>0.1</v>
+      </c>
+      <c r="G153">
+        <v>-0</v>
+      </c>
+      <c r="H153">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B154" t="s">
+        <v>51</v>
+      </c>
+      <c r="C154">
+        <v>1.3</v>
+      </c>
+      <c r="D154">
+        <v>0.2</v>
+      </c>
+      <c r="E154">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F154">
+        <v>0</v>
+      </c>
+      <c r="G154">
+        <v>1</v>
+      </c>
+      <c r="H154">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B155" t="s">
+        <v>52</v>
+      </c>
+      <c r="C155">
+        <v>0.1</v>
+      </c>
+      <c r="D155">
+        <v>0.1</v>
+      </c>
+      <c r="E155">
+        <v>1</v>
+      </c>
+      <c r="F155">
+        <v>0.3</v>
+      </c>
+      <c r="G155">
+        <v>-0.1</v>
+      </c>
+      <c r="H155">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B156" t="s">
+        <v>54</v>
+      </c>
+      <c r="C156">
+        <v>1.7</v>
+      </c>
+      <c r="D156">
+        <v>0.1</v>
+      </c>
+      <c r="E156">
+        <v>14.5</v>
+      </c>
+      <c r="F156">
+        <v>0</v>
+      </c>
+      <c r="G156">
+        <v>1.5</v>
+      </c>
+      <c r="H156">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B157" t="s">
+        <v>55</v>
+      </c>
+      <c r="C157">
+        <v>1.1</v>
+      </c>
+      <c r="D157">
+        <v>0.1</v>
+      </c>
+      <c r="E157">
+        <v>8</v>
+      </c>
+      <c r="F157">
+        <v>0</v>
+      </c>
+      <c r="G157">
+        <v>0.9</v>
+      </c>
+      <c r="H157">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="A158" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B158" t="s">
+        <v>56</v>
+      </c>
+      <c r="C158">
+        <v>2.2</v>
+      </c>
+      <c r="D158">
+        <v>0.8</v>
+      </c>
+      <c r="E158">
+        <v>2.9</v>
+      </c>
+      <c r="F158">
+        <v>0</v>
+      </c>
+      <c r="G158">
+        <v>0.7</v>
+      </c>
+      <c r="H158">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="A159" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B159" t="s">
+        <v>58</v>
+      </c>
+      <c r="C159">
+        <v>0.3</v>
+      </c>
+      <c r="D159">
+        <v>0.2</v>
+      </c>
+      <c r="E159">
+        <v>1.2</v>
+      </c>
+      <c r="F159">
+        <v>0.2</v>
+      </c>
+      <c r="G159">
         <v>-0.2</v>
       </c>
-      <c r="H46">
+      <c r="H159">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
+      <c r="A161" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
+      <c r="B162" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H162" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8">
+      <c r="A163" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B163" t="s">
+        <v>40</v>
+      </c>
+      <c r="C163">
+        <v>-3.9</v>
+      </c>
+      <c r="D163">
+        <v>0.4</v>
+      </c>
+      <c r="E163">
+        <v>-10.1</v>
+      </c>
+      <c r="F163">
+        <v>0</v>
+      </c>
+      <c r="G163">
+        <v>-4.6</v>
+      </c>
+      <c r="H163">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8">
+      <c r="A164" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B164" t="s">
+        <v>46</v>
+      </c>
+      <c r="C164">
+        <v>-0.5</v>
+      </c>
+      <c r="D164">
+        <v>0.4</v>
+      </c>
+      <c r="E164">
+        <v>-1.1</v>
+      </c>
+      <c r="F164">
+        <v>0.3</v>
+      </c>
+      <c r="G164">
+        <v>-1.2</v>
+      </c>
+      <c r="H164">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8">
+      <c r="A165" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B165" t="s">
+        <v>48</v>
+      </c>
+      <c r="C165">
+        <v>-0.4</v>
+      </c>
+      <c r="D165">
+        <v>0.6</v>
+      </c>
+      <c r="E165">
+        <v>-0.6</v>
+      </c>
+      <c r="F165">
+        <v>0.6</v>
+      </c>
+      <c r="G165">
+        <v>-1.6</v>
+      </c>
+      <c r="H165">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8">
+      <c r="A166" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B166" t="s">
+        <v>49</v>
+      </c>
+      <c r="C166">
+        <v>1</v>
+      </c>
+      <c r="D166">
+        <v>0.6</v>
+      </c>
+      <c r="E166">
+        <v>1.5</v>
+      </c>
+      <c r="F166">
+        <v>0.1</v>
+      </c>
+      <c r="G166">
+        <v>-0.3</v>
+      </c>
+      <c r="H166">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
+      <c r="A167" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B167" t="s">
+        <v>50</v>
+      </c>
+      <c r="C167">
+        <v>-0.9</v>
+      </c>
+      <c r="D167">
+        <v>0.4</v>
+      </c>
+      <c r="E167">
+        <v>-2.1</v>
+      </c>
+      <c r="F167">
+        <v>0</v>
+      </c>
+      <c r="G167">
+        <v>-1.7</v>
+      </c>
+      <c r="H167">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
+      <c r="A168" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B168" t="s">
+        <v>51</v>
+      </c>
+      <c r="C168">
+        <v>0.1</v>
+      </c>
+      <c r="D168">
+        <v>0.5</v>
+      </c>
+      <c r="E168">
+        <v>0.2</v>
+      </c>
+      <c r="F168">
+        <v>0.9</v>
+      </c>
+      <c r="G168">
+        <v>-0.8</v>
+      </c>
+      <c r="H168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
+      <c r="A169" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B169" t="s">
+        <v>52</v>
+      </c>
+      <c r="C169">
+        <v>0.7</v>
+      </c>
+      <c r="D169">
+        <v>0.3</v>
+      </c>
+      <c r="E169">
+        <v>2.4</v>
+      </c>
+      <c r="F169">
+        <v>0</v>
+      </c>
+      <c r="G169">
+        <v>0.1</v>
+      </c>
+      <c r="H169">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8">
+      <c r="A170" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B170" t="s">
+        <v>54</v>
+      </c>
+      <c r="C170">
+        <v>1.9</v>
+      </c>
+      <c r="D170">
+        <v>0.4</v>
+      </c>
+      <c r="E170">
+        <v>5.2</v>
+      </c>
+      <c r="F170">
+        <v>0</v>
+      </c>
+      <c r="G170">
+        <v>1.2</v>
+      </c>
+      <c r="H170">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8">
+      <c r="A171" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B171" t="s">
+        <v>55</v>
+      </c>
+      <c r="C171">
+        <v>-0.1</v>
+      </c>
+      <c r="D171">
+        <v>0.4</v>
+      </c>
+      <c r="E171">
+        <v>-0.3</v>
+      </c>
+      <c r="F171">
+        <v>0.7</v>
+      </c>
+      <c r="G171">
+        <v>-1</v>
+      </c>
+      <c r="H171">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
+      <c r="A172" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B172" t="s">
+        <v>56</v>
+      </c>
+      <c r="C172">
+        <v>2.8</v>
+      </c>
+      <c r="D172">
+        <v>1.1</v>
+      </c>
+      <c r="E172">
+        <v>2.6</v>
+      </c>
+      <c r="F172">
+        <v>0</v>
+      </c>
+      <c r="G172">
+        <v>0.7</v>
+      </c>
+      <c r="H172">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8">
+      <c r="A173" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B173" t="s">
+        <v>58</v>
+      </c>
+      <c r="C173">
+        <v>-0.9</v>
+      </c>
+      <c r="D173">
+        <v>0.8</v>
+      </c>
+      <c r="E173">
+        <v>-1.2</v>
+      </c>
+      <c r="F173">
+        <v>0.2</v>
+      </c>
+      <c r="G173">
+        <v>-2.4</v>
+      </c>
+      <c r="H173">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8">
+      <c r="A175" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
+      <c r="B176" s="1">
+        <v>0</v>
+      </c>
+      <c r="C176" s="1">
+        <v>1</v>
+      </c>
+      <c r="D176" s="1">
+        <v>2</v>
+      </c>
+      <c r="E176" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8">
+      <c r="A177" s="1">
+        <v>0</v>
+      </c>
+      <c r="B177" t="s">
+        <v>1</v>
+      </c>
+      <c r="C177" t="s">
+        <v>9</v>
+      </c>
+      <c r="D177" t="s">
+        <v>17</v>
+      </c>
+      <c r="E177" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8">
+      <c r="A178" s="1">
+        <v>1</v>
+      </c>
+      <c r="B178" t="s">
+        <v>2</v>
+      </c>
+      <c r="C178" t="s">
+        <v>86</v>
+      </c>
+      <c r="D178" t="s">
+        <v>18</v>
+      </c>
+      <c r="E178" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8">
+      <c r="A179" s="1">
+        <v>2</v>
+      </c>
+      <c r="B179" t="s">
+        <v>3</v>
+      </c>
+      <c r="C179" t="s">
+        <v>11</v>
+      </c>
+      <c r="D179" t="s">
+        <v>19</v>
+      </c>
+      <c r="E179" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8">
+      <c r="A180" s="1">
+        <v>3</v>
+      </c>
+      <c r="B180" t="s">
+        <v>4</v>
+      </c>
+      <c r="C180" t="s">
+        <v>87</v>
+      </c>
+      <c r="D180" t="s">
+        <v>20</v>
+      </c>
+      <c r="E180" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8">
+      <c r="A181" s="1">
+        <v>4</v>
+      </c>
+      <c r="B181" t="s">
+        <v>5</v>
+      </c>
+      <c r="C181" t="s">
+        <v>88</v>
+      </c>
+      <c r="D181" t="s">
+        <v>21</v>
+      </c>
+      <c r="E181" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8">
+      <c r="A182" s="1">
+        <v>5</v>
+      </c>
+      <c r="B182" t="s">
+        <v>6</v>
+      </c>
+      <c r="C182" t="s">
+        <v>89</v>
+      </c>
+      <c r="D182" t="s">
+        <v>22</v>
+      </c>
+      <c r="E182" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8">
+      <c r="A183" s="1">
+        <v>6</v>
+      </c>
+      <c r="B183" t="s">
+        <v>7</v>
+      </c>
+      <c r="C183" t="s">
+        <v>15</v>
+      </c>
+      <c r="D183" t="s">
+        <v>23</v>
+      </c>
+      <c r="E183" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8">
+      <c r="A184" s="1">
+        <v>7</v>
+      </c>
+      <c r="B184" t="s">
+        <v>8</v>
+      </c>
+      <c r="C184" t="s">
+        <v>72</v>
+      </c>
+      <c r="D184" t="s">
+        <v>24</v>
+      </c>
+      <c r="E184" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8">
+      <c r="A186" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8">
+      <c r="B187" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H187" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8">
+      <c r="A188" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B188" t="s">
+        <v>40</v>
+      </c>
+      <c r="C188">
+        <v>-1.4</v>
+      </c>
+      <c r="D188">
+        <v>0.1</v>
+      </c>
+      <c r="E188">
+        <v>-11.7</v>
+      </c>
+      <c r="F188">
+        <v>0</v>
+      </c>
+      <c r="G188">
+        <v>-1.6</v>
+      </c>
+      <c r="H188">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8">
+      <c r="A189" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B189" t="s">
+        <v>48</v>
+      </c>
+      <c r="C189">
+        <v>-0.7</v>
+      </c>
+      <c r="D189">
+        <v>0.2</v>
+      </c>
+      <c r="E189">
+        <v>-3.2</v>
+      </c>
+      <c r="F189">
+        <v>0</v>
+      </c>
+      <c r="G189">
+        <v>-1.1</v>
+      </c>
+      <c r="H189">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8">
+      <c r="A190" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B190" t="s">
+        <v>49</v>
+      </c>
+      <c r="C190">
+        <v>-0.2</v>
+      </c>
+      <c r="D190">
+        <v>0.3</v>
+      </c>
+      <c r="E190">
+        <v>-0.5</v>
+      </c>
+      <c r="F190">
+        <v>0.6</v>
+      </c>
+      <c r="G190">
+        <v>-0.8</v>
+      </c>
+      <c r="H190">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8">
+      <c r="A191" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B191" t="s">
+        <v>50</v>
+      </c>
+      <c r="C191">
+        <v>0.3</v>
+      </c>
+      <c r="D191">
+        <v>0.1</v>
+      </c>
+      <c r="E191">
+        <v>2.8</v>
+      </c>
+      <c r="F191">
+        <v>0</v>
+      </c>
+      <c r="G191">
+        <v>0.1</v>
+      </c>
+      <c r="H191">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8">
+      <c r="A192" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B192" t="s">
+        <v>51</v>
+      </c>
+      <c r="C192">
+        <v>1.1</v>
+      </c>
+      <c r="D192">
+        <v>0.2</v>
+      </c>
+      <c r="E192">
+        <v>6.7</v>
+      </c>
+      <c r="F192">
+        <v>0</v>
+      </c>
+      <c r="G192">
+        <v>0.8</v>
+      </c>
+      <c r="H192">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8">
+      <c r="A193" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B193" t="s">
+        <v>52</v>
+      </c>
+      <c r="C193">
+        <v>0.3</v>
+      </c>
+      <c r="D193">
+        <v>0.1</v>
+      </c>
+      <c r="E193">
+        <v>2.5</v>
+      </c>
+      <c r="F193">
+        <v>0</v>
+      </c>
+      <c r="G193">
+        <v>0.1</v>
+      </c>
+      <c r="H193">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8">
+      <c r="A194" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B194" t="s">
+        <v>54</v>
+      </c>
+      <c r="C194">
+        <v>1.3</v>
+      </c>
+      <c r="D194">
+        <v>0.1</v>
+      </c>
+      <c r="E194">
+        <v>11.5</v>
+      </c>
+      <c r="F194">
+        <v>0</v>
+      </c>
+      <c r="G194">
+        <v>1.1</v>
+      </c>
+      <c r="H194">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8">
+      <c r="A195" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B195" t="s">
+        <v>55</v>
+      </c>
+      <c r="C195">
+        <v>0.6</v>
+      </c>
+      <c r="D195">
+        <v>0.2</v>
+      </c>
+      <c r="E195">
+        <v>3.9</v>
+      </c>
+      <c r="F195">
+        <v>0</v>
+      </c>
+      <c r="G195">
+        <v>0.3</v>
+      </c>
+      <c r="H195">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8">
+      <c r="A196" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B196" t="s">
+        <v>56</v>
+      </c>
+      <c r="C196">
+        <v>2.1</v>
+      </c>
+      <c r="D196">
+        <v>0.8</v>
+      </c>
+      <c r="E196">
+        <v>2.7</v>
+      </c>
+      <c r="F196">
+        <v>0</v>
+      </c>
+      <c r="G196">
+        <v>0.5</v>
+      </c>
+      <c r="H196">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8">
+      <c r="A198" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8">
+      <c r="B199" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H199" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8">
+      <c r="A200" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B200" t="s">
+        <v>40</v>
+      </c>
+      <c r="C200">
+        <v>-2</v>
+      </c>
+      <c r="D200">
+        <v>0.1</v>
+      </c>
+      <c r="E200">
+        <v>-14.1</v>
+      </c>
+      <c r="F200">
+        <v>0</v>
+      </c>
+      <c r="G200">
+        <v>-2.2</v>
+      </c>
+      <c r="H200">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8">
+      <c r="A201" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B201" t="s">
+        <v>48</v>
+      </c>
+      <c r="C201">
+        <v>-0.8</v>
+      </c>
+      <c r="D201">
+        <v>0.3</v>
+      </c>
+      <c r="E201">
+        <v>-2.9</v>
+      </c>
+      <c r="F201">
+        <v>0</v>
+      </c>
+      <c r="G201">
+        <v>-1.3</v>
+      </c>
+      <c r="H201">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8">
+      <c r="A202" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B202" t="s">
+        <v>49</v>
+      </c>
+      <c r="C202">
+        <v>0.1</v>
+      </c>
+      <c r="D202">
+        <v>0.3</v>
+      </c>
+      <c r="E202">
+        <v>0.2</v>
+      </c>
+      <c r="F202">
+        <v>0.8</v>
+      </c>
+      <c r="G202">
+        <v>-0.6</v>
+      </c>
+      <c r="H202">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8">
+      <c r="A203" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B203" t="s">
+        <v>50</v>
+      </c>
+      <c r="C203">
+        <v>0.3</v>
+      </c>
+      <c r="D203">
+        <v>0.1</v>
+      </c>
+      <c r="E203">
+        <v>2.6</v>
+      </c>
+      <c r="F203">
+        <v>0</v>
+      </c>
+      <c r="G203">
+        <v>0.1</v>
+      </c>
+      <c r="H203">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8">
+      <c r="A204" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B204" t="s">
+        <v>51</v>
+      </c>
+      <c r="C204">
+        <v>1.4</v>
+      </c>
+      <c r="D204">
+        <v>0.2</v>
+      </c>
+      <c r="E204">
+        <v>8</v>
+      </c>
+      <c r="F204">
+        <v>0</v>
+      </c>
+      <c r="G204">
+        <v>1</v>
+      </c>
+      <c r="H204">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8">
+      <c r="A205" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B205" t="s">
+        <v>52</v>
+      </c>
+      <c r="C205">
+        <v>-0.1</v>
+      </c>
+      <c r="D205">
+        <v>0.1</v>
+      </c>
+      <c r="E205">
+        <v>-1</v>
+      </c>
+      <c r="F205">
+        <v>0.3</v>
+      </c>
+      <c r="G205">
+        <v>-0.4</v>
+      </c>
+      <c r="H205">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8">
+      <c r="A206" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B206" t="s">
+        <v>54</v>
+      </c>
+      <c r="C206">
+        <v>1.4</v>
+      </c>
+      <c r="D206">
+        <v>0.1</v>
+      </c>
+      <c r="E206">
+        <v>10.3</v>
+      </c>
+      <c r="F206">
+        <v>0</v>
+      </c>
+      <c r="G206">
+        <v>1.2</v>
+      </c>
+      <c r="H206">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8">
+      <c r="A207" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B207" t="s">
+        <v>55</v>
+      </c>
+      <c r="C207">
+        <v>1.3</v>
+      </c>
+      <c r="D207">
+        <v>0.2</v>
+      </c>
+      <c r="E207">
+        <v>7.9</v>
+      </c>
+      <c r="F207">
+        <v>0</v>
+      </c>
+      <c r="G207">
+        <v>1</v>
+      </c>
+      <c r="H207">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8">
+      <c r="A208" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B208" t="s">
+        <v>56</v>
+      </c>
+      <c r="C208">
+        <v>2</v>
+      </c>
+      <c r="D208">
+        <v>0.8</v>
+      </c>
+      <c r="E208">
+        <v>2.5</v>
+      </c>
+      <c r="F208">
+        <v>0</v>
+      </c>
+      <c r="G208">
+        <v>0.4</v>
+      </c>
+      <c r="H208">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8">
+      <c r="A210" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8">
+      <c r="B211" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G211" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H211" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8">
+      <c r="A212" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B212" t="s">
+        <v>40</v>
+      </c>
+      <c r="C212">
+        <v>-3.9</v>
+      </c>
+      <c r="D212">
+        <v>0.4</v>
+      </c>
+      <c r="E212">
+        <v>-10.1</v>
+      </c>
+      <c r="F212">
+        <v>0</v>
+      </c>
+      <c r="G212">
+        <v>-4.7</v>
+      </c>
+      <c r="H212">
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8">
+      <c r="A213" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B213" t="s">
+        <v>48</v>
+      </c>
+      <c r="C213">
+        <v>-0.5</v>
+      </c>
+      <c r="D213">
+        <v>0.8</v>
+      </c>
+      <c r="E213">
+        <v>-0.7</v>
+      </c>
+      <c r="F213">
+        <v>0.5</v>
+      </c>
+      <c r="G213">
+        <v>-2</v>
+      </c>
+      <c r="H213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8">
+      <c r="A214" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B214" t="s">
+        <v>49</v>
+      </c>
+      <c r="C214">
+        <v>0.6</v>
+      </c>
+      <c r="D214">
+        <v>0.8</v>
+      </c>
+      <c r="E214">
+        <v>0.8</v>
+      </c>
+      <c r="F214">
+        <v>0.4</v>
+      </c>
+      <c r="G214">
+        <v>-0.9</v>
+      </c>
+      <c r="H214">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8">
+      <c r="A215" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B215" t="s">
+        <v>50</v>
+      </c>
+      <c r="C215">
+        <v>-1</v>
+      </c>
+      <c r="D215">
+        <v>0.5</v>
+      </c>
+      <c r="E215">
+        <v>-2.1</v>
+      </c>
+      <c r="F215">
+        <v>0</v>
+      </c>
+      <c r="G215">
+        <v>-2</v>
+      </c>
+      <c r="H215">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8">
+      <c r="A216" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B216" t="s">
+        <v>51</v>
+      </c>
+      <c r="C216">
+        <v>0.5</v>
+      </c>
+      <c r="D216">
+        <v>0.5</v>
+      </c>
+      <c r="E216">
+        <v>1</v>
+      </c>
+      <c r="F216">
+        <v>0.3</v>
+      </c>
+      <c r="G216">
+        <v>-0.5</v>
+      </c>
+      <c r="H216">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8">
+      <c r="A217" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B217" t="s">
+        <v>52</v>
+      </c>
+      <c r="C217">
+        <v>0.5</v>
+      </c>
+      <c r="D217">
+        <v>0.4</v>
+      </c>
+      <c r="E217">
+        <v>1.3</v>
+      </c>
+      <c r="F217">
+        <v>0.2</v>
+      </c>
+      <c r="G217">
+        <v>-0.2</v>
+      </c>
+      <c r="H217">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8">
+      <c r="A218" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B218" t="s">
+        <v>54</v>
+      </c>
+      <c r="C218">
+        <v>1.3</v>
+      </c>
+      <c r="D218">
+        <v>0.4</v>
+      </c>
+      <c r="E218">
+        <v>3.5</v>
+      </c>
+      <c r="F218">
+        <v>0</v>
+      </c>
+      <c r="G218">
+        <v>0.6</v>
+      </c>
+      <c r="H218">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8">
+      <c r="A219" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B219" t="s">
+        <v>55</v>
+      </c>
+      <c r="C219">
+        <v>0.1</v>
+      </c>
+      <c r="D219">
+        <v>0.5</v>
+      </c>
+      <c r="E219">
+        <v>0.1</v>
+      </c>
+      <c r="F219">
+        <v>0.9</v>
+      </c>
+      <c r="G219">
+        <v>-0.9</v>
+      </c>
+      <c r="H219">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8">
+      <c r="A220" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B220" t="s">
+        <v>56</v>
+      </c>
+      <c r="C220">
+        <v>2.3</v>
+      </c>
+      <c r="D220">
+        <v>1.3</v>
+      </c>
+      <c r="E220">
+        <v>1.8</v>
+      </c>
+      <c r="F220">
+        <v>0.1</v>
+      </c>
+      <c r="G220">
+        <v>-0.2</v>
+      </c>
+      <c r="H220">
         <v>4.8</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8">
+      <c r="A222" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8">
+      <c r="B223" s="1">
+        <v>0</v>
+      </c>
+      <c r="C223" s="1">
+        <v>1</v>
+      </c>
+      <c r="D223" s="1">
+        <v>2</v>
+      </c>
+      <c r="E223" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8">
+      <c r="A224" s="1">
+        <v>0</v>
+      </c>
+      <c r="B224" t="s">
+        <v>1</v>
+      </c>
+      <c r="C224" t="s">
+        <v>103</v>
+      </c>
+      <c r="D224" t="s">
+        <v>17</v>
+      </c>
+      <c r="E224" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7">
+      <c r="A225" s="1">
+        <v>1</v>
+      </c>
+      <c r="B225" t="s">
+        <v>2</v>
+      </c>
+      <c r="C225" t="s">
+        <v>104</v>
+      </c>
+      <c r="D225" t="s">
+        <v>18</v>
+      </c>
+      <c r="E225" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7">
+      <c r="A226" s="1">
+        <v>2</v>
+      </c>
+      <c r="B226" t="s">
+        <v>3</v>
+      </c>
+      <c r="C226" t="s">
+        <v>11</v>
+      </c>
+      <c r="D226" t="s">
+        <v>19</v>
+      </c>
+      <c r="E226" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7">
+      <c r="A227" s="1">
+        <v>3</v>
+      </c>
+      <c r="B227" t="s">
+        <v>4</v>
+      </c>
+      <c r="C227" t="s">
+        <v>87</v>
+      </c>
+      <c r="D227" t="s">
+        <v>20</v>
+      </c>
+      <c r="E227" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228" s="1">
+        <v>4</v>
+      </c>
+      <c r="B228" t="s">
+        <v>5</v>
+      </c>
+      <c r="C228" t="s">
+        <v>105</v>
+      </c>
+      <c r="D228" t="s">
+        <v>21</v>
+      </c>
+      <c r="E228" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229" s="1">
+        <v>5</v>
+      </c>
+      <c r="B229" t="s">
+        <v>6</v>
+      </c>
+      <c r="C229" t="s">
+        <v>106</v>
+      </c>
+      <c r="D229" t="s">
+        <v>22</v>
+      </c>
+      <c r="E229" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7">
+      <c r="A230" s="1">
+        <v>6</v>
+      </c>
+      <c r="B230" t="s">
+        <v>7</v>
+      </c>
+      <c r="C230" t="s">
+        <v>15</v>
+      </c>
+      <c r="D230" t="s">
+        <v>23</v>
+      </c>
+      <c r="E230" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231" s="1">
+        <v>7</v>
+      </c>
+      <c r="B231" t="s">
+        <v>8</v>
+      </c>
+      <c r="C231" t="s">
+        <v>107</v>
+      </c>
+      <c r="D231" t="s">
+        <v>24</v>
+      </c>
+      <c r="E231" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7">
+      <c r="A233" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7">
+      <c r="B234" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F234" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G234" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B235">
+        <v>-4</v>
+      </c>
+      <c r="C235">
+        <v>0.2</v>
+      </c>
+      <c r="D235">
+        <v>-18.7</v>
+      </c>
+      <c r="E235">
+        <v>0</v>
+      </c>
+      <c r="F235">
+        <v>-4.4</v>
+      </c>
+      <c r="G235">
+        <v>-3.5</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7">
+      <c r="A236" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B236">
+        <v>0.5</v>
+      </c>
+      <c r="C236">
+        <v>0.1</v>
+      </c>
+      <c r="D236">
+        <v>3.2</v>
+      </c>
+      <c r="E236">
+        <v>0</v>
+      </c>
+      <c r="F236">
+        <v>0.2</v>
+      </c>
+      <c r="G236">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7">
+      <c r="A237" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B237">
+        <v>0.7</v>
+      </c>
+      <c r="C237">
+        <v>0.2</v>
+      </c>
+      <c r="D237">
+        <v>4.9</v>
+      </c>
+      <c r="E237">
+        <v>0</v>
+      </c>
+      <c r="F237">
+        <v>0.4</v>
+      </c>
+      <c r="G237">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7">
+      <c r="A238" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B238">
+        <v>0.3</v>
+      </c>
+      <c r="C238">
+        <v>0.1</v>
+      </c>
+      <c r="D238">
+        <v>2.4</v>
+      </c>
+      <c r="E238">
+        <v>0</v>
+      </c>
+      <c r="F238">
+        <v>0.1</v>
+      </c>
+      <c r="G238">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7">
+      <c r="A239" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B239">
+        <v>1.9</v>
+      </c>
+      <c r="C239">
+        <v>0.2</v>
+      </c>
+      <c r="D239">
+        <v>9.5</v>
+      </c>
+      <c r="E239">
+        <v>0</v>
+      </c>
+      <c r="F239">
+        <v>1.5</v>
+      </c>
+      <c r="G239">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B240">
+        <v>0.6</v>
+      </c>
+      <c r="C240">
+        <v>0.2</v>
+      </c>
+      <c r="D240">
+        <v>4.1</v>
+      </c>
+      <c r="E240">
+        <v>0</v>
+      </c>
+      <c r="F240">
+        <v>0.3</v>
+      </c>
+      <c r="G240">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B241">
+        <v>0.8</v>
+      </c>
+      <c r="C241">
+        <v>0.4</v>
+      </c>
+      <c r="D241">
+        <v>2.1</v>
+      </c>
+      <c r="E241">
+        <v>0</v>
+      </c>
+      <c r="F241">
+        <v>0</v>
+      </c>
+      <c r="G241">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7">
+      <c r="A243" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="B244" s="1">
+        <v>0</v>
+      </c>
+      <c r="C244" s="1">
+        <v>1</v>
+      </c>
+      <c r="D244" s="1">
+        <v>2</v>
+      </c>
+      <c r="E244" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245" s="1">
+        <v>0</v>
+      </c>
+      <c r="B245" t="s">
+        <v>1</v>
+      </c>
+      <c r="C245" t="s">
+        <v>103</v>
+      </c>
+      <c r="D245" t="s">
+        <v>17</v>
+      </c>
+      <c r="E245" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7">
+      <c r="A246" s="1">
+        <v>1</v>
+      </c>
+      <c r="B246" t="s">
+        <v>2</v>
+      </c>
+      <c r="C246" t="s">
+        <v>118</v>
+      </c>
+      <c r="D246" t="s">
+        <v>18</v>
+      </c>
+      <c r="E246" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7">
+      <c r="A247" s="1">
+        <v>2</v>
+      </c>
+      <c r="B247" t="s">
+        <v>3</v>
+      </c>
+      <c r="C247" t="s">
+        <v>11</v>
+      </c>
+      <c r="D247" t="s">
+        <v>19</v>
+      </c>
+      <c r="E247" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7">
+      <c r="A248" s="1">
+        <v>3</v>
+      </c>
+      <c r="B248" t="s">
+        <v>4</v>
+      </c>
+      <c r="C248" t="s">
+        <v>87</v>
+      </c>
+      <c r="D248" t="s">
+        <v>20</v>
+      </c>
+      <c r="E248" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7">
+      <c r="A249" s="1">
+        <v>4</v>
+      </c>
+      <c r="B249" t="s">
+        <v>5</v>
+      </c>
+      <c r="C249" t="s">
+        <v>105</v>
+      </c>
+      <c r="D249" t="s">
+        <v>21</v>
+      </c>
+      <c r="E249" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
+      <c r="A250" s="1">
+        <v>5</v>
+      </c>
+      <c r="B250" t="s">
+        <v>6</v>
+      </c>
+      <c r="C250" t="s">
+        <v>106</v>
+      </c>
+      <c r="D250" t="s">
+        <v>22</v>
+      </c>
+      <c r="E250" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="A251" s="1">
+        <v>6</v>
+      </c>
+      <c r="B251" t="s">
+        <v>7</v>
+      </c>
+      <c r="C251" t="s">
+        <v>15</v>
+      </c>
+      <c r="D251" t="s">
+        <v>23</v>
+      </c>
+      <c r="E251" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
+      <c r="A252" s="1">
+        <v>7</v>
+      </c>
+      <c r="B252" t="s">
+        <v>8</v>
+      </c>
+      <c r="C252" t="s">
+        <v>119</v>
+      </c>
+      <c r="D252" t="s">
+        <v>24</v>
+      </c>
+      <c r="E252" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7">
+      <c r="A254" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7">
+      <c r="B255" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F255" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G255" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7">
+      <c r="A256" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B256">
+        <v>-0.8</v>
+      </c>
+      <c r="C256">
+        <v>0.1</v>
+      </c>
+      <c r="D256">
+        <v>-8.4</v>
+      </c>
+      <c r="E256">
+        <v>0</v>
+      </c>
+      <c r="F256">
+        <v>-1</v>
+      </c>
+      <c r="G256">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
+      <c r="A257" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B257">
+        <v>-0.5</v>
+      </c>
+      <c r="C257">
+        <v>0.1</v>
+      </c>
+      <c r="D257">
+        <v>-3.4</v>
+      </c>
+      <c r="E257">
+        <v>0</v>
+      </c>
+      <c r="F257">
+        <v>-0.7</v>
+      </c>
+      <c r="G257">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
+      <c r="A258" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B258">
+        <v>-0.5</v>
+      </c>
+      <c r="C258">
+        <v>0.1</v>
+      </c>
+      <c r="D258">
+        <v>-4.5</v>
+      </c>
+      <c r="E258">
+        <v>0</v>
+      </c>
+      <c r="F258">
+        <v>-0.8</v>
+      </c>
+      <c r="G258">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
+      <c r="A259" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B259">
+        <v>-0.9</v>
+      </c>
+      <c r="C259">
+        <v>0.2</v>
+      </c>
+      <c r="D259">
+        <v>-5.1</v>
+      </c>
+      <c r="E259">
+        <v>0</v>
+      </c>
+      <c r="F259">
+        <v>-1.2</v>
+      </c>
+      <c r="G259">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
+      <c r="A260" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B260">
+        <v>0.2</v>
+      </c>
+      <c r="C260">
+        <v>0.1</v>
+      </c>
+      <c r="D260">
+        <v>2</v>
+      </c>
+      <c r="E260">
+        <v>0</v>
+      </c>
+      <c r="F260">
+        <v>0</v>
+      </c>
+      <c r="G260">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
+      <c r="A261" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B261">
+        <v>-1.1</v>
+      </c>
+      <c r="C261">
+        <v>0.2</v>
+      </c>
+      <c r="D261">
+        <v>-6.3</v>
+      </c>
+      <c r="E261">
+        <v>0</v>
+      </c>
+      <c r="F261">
+        <v>-1.5</v>
+      </c>
+      <c r="G261">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
+      <c r="A262" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B262">
+        <v>0.5</v>
+      </c>
+      <c r="C262">
+        <v>0.2</v>
+      </c>
+      <c r="D262">
+        <v>2.4</v>
+      </c>
+      <c r="E262">
+        <v>0</v>
+      </c>
+      <c r="F262">
+        <v>0.1</v>
+      </c>
+      <c r="G262">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
+      <c r="A264" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
+      <c r="B265" s="1">
+        <v>0</v>
+      </c>
+      <c r="C265" s="1">
+        <v>1</v>
+      </c>
+      <c r="D265" s="1">
+        <v>2</v>
+      </c>
+      <c r="E265" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
+      <c r="A266" s="1">
+        <v>0</v>
+      </c>
+      <c r="B266" t="s">
+        <v>1</v>
+      </c>
+      <c r="C266" t="s">
+        <v>103</v>
+      </c>
+      <c r="D266" t="s">
+        <v>17</v>
+      </c>
+      <c r="E266" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
+      <c r="A267" s="1">
+        <v>1</v>
+      </c>
+      <c r="B267" t="s">
+        <v>2</v>
+      </c>
+      <c r="C267" t="s">
+        <v>128</v>
+      </c>
+      <c r="D267" t="s">
+        <v>18</v>
+      </c>
+      <c r="E267" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7">
+      <c r="A268" s="1">
+        <v>2</v>
+      </c>
+      <c r="B268" t="s">
+        <v>3</v>
+      </c>
+      <c r="C268" t="s">
+        <v>11</v>
+      </c>
+      <c r="D268" t="s">
+        <v>19</v>
+      </c>
+      <c r="E268" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
+      <c r="A269" s="1">
+        <v>3</v>
+      </c>
+      <c r="B269" t="s">
+        <v>4</v>
+      </c>
+      <c r="C269" t="s">
+        <v>129</v>
+      </c>
+      <c r="D269" t="s">
+        <v>20</v>
+      </c>
+      <c r="E269" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
+      <c r="A270" s="1">
+        <v>4</v>
+      </c>
+      <c r="B270" t="s">
+        <v>5</v>
+      </c>
+      <c r="C270" t="s">
+        <v>130</v>
+      </c>
+      <c r="D270" t="s">
+        <v>21</v>
+      </c>
+      <c r="E270" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7">
+      <c r="A271" s="1">
+        <v>5</v>
+      </c>
+      <c r="B271" t="s">
+        <v>6</v>
+      </c>
+      <c r="C271" t="s">
+        <v>131</v>
+      </c>
+      <c r="D271" t="s">
+        <v>22</v>
+      </c>
+      <c r="E271" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
+      <c r="A272" s="1">
+        <v>6</v>
+      </c>
+      <c r="B272" t="s">
+        <v>7</v>
+      </c>
+      <c r="C272" t="s">
+        <v>15</v>
+      </c>
+      <c r="D272" t="s">
+        <v>23</v>
+      </c>
+      <c r="E272" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
+      <c r="A273" s="1">
+        <v>7</v>
+      </c>
+      <c r="B273" t="s">
+        <v>8</v>
+      </c>
+      <c r="C273" t="s">
+        <v>72</v>
+      </c>
+      <c r="D273" t="s">
+        <v>24</v>
+      </c>
+      <c r="E273" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
+      <c r="A275" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
+      <c r="B276" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E276" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F276" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G276" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
+      <c r="A277" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B277">
+        <v>-5.6</v>
+      </c>
+      <c r="C277">
+        <v>0.6</v>
+      </c>
+      <c r="D277">
+        <v>-9</v>
+      </c>
+      <c r="E277">
+        <v>0</v>
+      </c>
+      <c r="F277">
+        <v>-6.8</v>
+      </c>
+      <c r="G277">
+        <v>-4.4</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
+      <c r="A278" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B278">
+        <v>2.5</v>
+      </c>
+      <c r="C278">
+        <v>0.7</v>
+      </c>
+      <c r="D278">
+        <v>3.6</v>
+      </c>
+      <c r="E278">
+        <v>0</v>
+      </c>
+      <c r="F278">
+        <v>1.2</v>
+      </c>
+      <c r="G278">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
+      <c r="A279" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B279">
+        <v>2.8</v>
+      </c>
+      <c r="C279">
+        <v>0.6</v>
+      </c>
+      <c r="D279">
+        <v>4.6</v>
+      </c>
+      <c r="E279">
+        <v>0</v>
+      </c>
+      <c r="F279">
+        <v>1.6</v>
+      </c>
+      <c r="G279">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
+      <c r="A280" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B280">
+        <v>1.1</v>
+      </c>
+      <c r="C280">
+        <v>0.5</v>
+      </c>
+      <c r="D280">
+        <v>2.1</v>
+      </c>
+      <c r="E280">
+        <v>0</v>
+      </c>
+      <c r="F280">
+        <v>0.1</v>
+      </c>
+      <c r="G280">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="B283" s="1">
+        <v>0</v>
+      </c>
+      <c r="C283" s="1">
+        <v>1</v>
+      </c>
+      <c r="D283" s="1">
+        <v>2</v>
+      </c>
+      <c r="E283" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284" s="1">
+        <v>0</v>
+      </c>
+      <c r="B284" t="s">
+        <v>1</v>
+      </c>
+      <c r="C284" t="s">
+        <v>9</v>
+      </c>
+      <c r="D284" t="s">
+        <v>17</v>
+      </c>
+      <c r="E284" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285" s="1">
+        <v>1</v>
+      </c>
+      <c r="B285" t="s">
+        <v>2</v>
+      </c>
+      <c r="C285" t="s">
+        <v>141</v>
+      </c>
+      <c r="D285" t="s">
+        <v>18</v>
+      </c>
+      <c r="E285" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286" s="1">
+        <v>2</v>
+      </c>
+      <c r="B286" t="s">
+        <v>3</v>
+      </c>
+      <c r="C286" t="s">
+        <v>11</v>
+      </c>
+      <c r="D286" t="s">
+        <v>19</v>
+      </c>
+      <c r="E286" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287" s="1">
+        <v>3</v>
+      </c>
+      <c r="B287" t="s">
+        <v>4</v>
+      </c>
+      <c r="C287" t="s">
+        <v>142</v>
+      </c>
+      <c r="D287" t="s">
+        <v>20</v>
+      </c>
+      <c r="E287" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
+      <c r="A288" s="1">
+        <v>4</v>
+      </c>
+      <c r="B288" t="s">
+        <v>5</v>
+      </c>
+      <c r="C288" t="s">
+        <v>143</v>
+      </c>
+      <c r="D288" t="s">
+        <v>21</v>
+      </c>
+      <c r="E288" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8">
+      <c r="A289" s="1">
+        <v>5</v>
+      </c>
+      <c r="B289" t="s">
+        <v>6</v>
+      </c>
+      <c r="C289" t="s">
+        <v>144</v>
+      </c>
+      <c r="D289" t="s">
+        <v>22</v>
+      </c>
+      <c r="E289" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8">
+      <c r="A290" s="1">
+        <v>6</v>
+      </c>
+      <c r="B290" t="s">
+        <v>7</v>
+      </c>
+      <c r="C290" t="s">
+        <v>15</v>
+      </c>
+      <c r="D290" t="s">
+        <v>23</v>
+      </c>
+      <c r="E290" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8">
+      <c r="A291" s="1">
+        <v>7</v>
+      </c>
+      <c r="B291" t="s">
+        <v>8</v>
+      </c>
+      <c r="C291" t="s">
+        <v>16</v>
+      </c>
+      <c r="D291" t="s">
+        <v>24</v>
+      </c>
+      <c r="E291" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8">
+      <c r="A293" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8">
+      <c r="B294" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C294" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E294" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F294" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G294" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H294" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8">
+      <c r="A295" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B295" t="s">
+        <v>40</v>
+      </c>
+      <c r="C295">
+        <v>0.2</v>
+      </c>
+      <c r="D295">
+        <v>0.1</v>
+      </c>
+      <c r="E295">
+        <v>1.9</v>
+      </c>
+      <c r="F295">
+        <v>0.1</v>
+      </c>
+      <c r="G295">
+        <v>-0</v>
+      </c>
+      <c r="H295">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8">
+      <c r="A296" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B296" t="s">
+        <v>46</v>
+      </c>
+      <c r="C296">
+        <v>0.1</v>
+      </c>
+      <c r="D296">
+        <v>0.1</v>
+      </c>
+      <c r="E296">
+        <v>1.5</v>
+      </c>
+      <c r="F296">
+        <v>0.1</v>
+      </c>
+      <c r="G296">
+        <v>-0</v>
+      </c>
+      <c r="H296">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8">
+      <c r="A297" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B297" t="s">
+        <v>48</v>
+      </c>
+      <c r="C297">
+        <v>0.2</v>
+      </c>
+      <c r="D297">
+        <v>0.1</v>
+      </c>
+      <c r="E297">
+        <v>1.6</v>
+      </c>
+      <c r="F297">
+        <v>0.1</v>
+      </c>
+      <c r="G297">
+        <v>-0</v>
+      </c>
+      <c r="H297">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8">
+      <c r="A298" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B298" t="s">
+        <v>49</v>
+      </c>
+      <c r="C298">
+        <v>-0</v>
+      </c>
+      <c r="D298">
+        <v>0.2</v>
+      </c>
+      <c r="E298">
+        <v>-0.2</v>
+      </c>
+      <c r="F298">
+        <v>0.8</v>
+      </c>
+      <c r="G298">
+        <v>-0.5</v>
+      </c>
+      <c r="H298">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8">
+      <c r="A299" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B299" t="s">
+        <v>50</v>
+      </c>
+      <c r="C299">
+        <v>-0.1</v>
+      </c>
+      <c r="D299">
+        <v>0.1</v>
+      </c>
+      <c r="E299">
+        <v>-0.9</v>
+      </c>
+      <c r="F299">
+        <v>0.4</v>
+      </c>
+      <c r="G299">
+        <v>-0.3</v>
+      </c>
+      <c r="H299">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8">
+      <c r="A300" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B300" t="s">
+        <v>51</v>
+      </c>
+      <c r="C300">
+        <v>-0.5</v>
+      </c>
+      <c r="D300">
+        <v>0.1</v>
+      </c>
+      <c r="E300">
+        <v>-3.6</v>
+      </c>
+      <c r="F300">
+        <v>0</v>
+      </c>
+      <c r="G300">
+        <v>-0.8</v>
+      </c>
+      <c r="H300">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8">
+      <c r="A301" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B301" t="s">
+        <v>52</v>
+      </c>
+      <c r="C301">
+        <v>-0.1</v>
+      </c>
+      <c r="D301">
+        <v>0.1</v>
+      </c>
+      <c r="E301">
+        <v>-0.8</v>
+      </c>
+      <c r="F301">
+        <v>0.4</v>
+      </c>
+      <c r="G301">
+        <v>-0.3</v>
+      </c>
+      <c r="H301">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8">
+      <c r="A302" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B302" t="s">
+        <v>53</v>
+      </c>
+      <c r="C302">
+        <v>-0.2</v>
+      </c>
+      <c r="D302">
+        <v>0.1</v>
+      </c>
+      <c r="E302">
+        <v>-2.4</v>
+      </c>
+      <c r="F302">
+        <v>0</v>
+      </c>
+      <c r="G302">
+        <v>-0.4</v>
+      </c>
+      <c r="H302">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8">
+      <c r="A303" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B303" t="s">
+        <v>54</v>
+      </c>
+      <c r="C303">
+        <v>-0.9</v>
+      </c>
+      <c r="D303">
+        <v>0.1</v>
+      </c>
+      <c r="E303">
+        <v>-9.1</v>
+      </c>
+      <c r="F303">
+        <v>0</v>
+      </c>
+      <c r="G303">
+        <v>-1.1</v>
+      </c>
+      <c r="H303">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8">
+      <c r="A304" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B304" t="s">
+        <v>55</v>
+      </c>
+      <c r="C304">
+        <v>-0.1</v>
+      </c>
+      <c r="D304">
+        <v>0.1</v>
+      </c>
+      <c r="E304">
+        <v>-0.8</v>
+      </c>
+      <c r="F304">
+        <v>0.4</v>
+      </c>
+      <c r="G304">
+        <v>-0.4</v>
+      </c>
+      <c r="H304">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8">
+      <c r="A305" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B305" t="s">
+        <v>56</v>
+      </c>
+      <c r="C305">
+        <v>-1.4</v>
+      </c>
+      <c r="D305">
+        <v>0.5</v>
+      </c>
+      <c r="E305">
+        <v>-2.6</v>
+      </c>
+      <c r="F305">
+        <v>0</v>
+      </c>
+      <c r="G305">
+        <v>-2.4</v>
+      </c>
+      <c r="H305">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8">
+      <c r="A306" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B306" t="s">
+        <v>58</v>
+      </c>
+      <c r="C306">
+        <v>-0.5</v>
+      </c>
+      <c r="D306">
+        <v>0.2</v>
+      </c>
+      <c r="E306">
+        <v>-3.1</v>
+      </c>
+      <c r="F306">
+        <v>0</v>
+      </c>
+      <c r="G306">
+        <v>-0.9</v>
+      </c>
+      <c r="H306">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8">
+      <c r="A308" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8">
+      <c r="B309" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C309" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E309" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F309" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G309" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H309" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8">
+      <c r="A310" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B310" t="s">
+        <v>40</v>
+      </c>
+      <c r="C310">
+        <v>-1.6</v>
+      </c>
+      <c r="D310">
+        <v>0.1</v>
+      </c>
+      <c r="E310">
+        <v>-12.6</v>
+      </c>
+      <c r="F310">
+        <v>0</v>
+      </c>
+      <c r="G310">
+        <v>-1.8</v>
+      </c>
+      <c r="H310">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8">
+      <c r="A311" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B311" t="s">
+        <v>46</v>
+      </c>
+      <c r="C311">
+        <v>-0.3</v>
+      </c>
+      <c r="D311">
+        <v>0.1</v>
+      </c>
+      <c r="E311">
+        <v>-2.7</v>
+      </c>
+      <c r="F311">
+        <v>0</v>
+      </c>
+      <c r="G311">
+        <v>-0.5</v>
+      </c>
+      <c r="H311">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8">
+      <c r="A312" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B312" t="s">
+        <v>48</v>
+      </c>
+      <c r="C312">
+        <v>-0.6</v>
+      </c>
+      <c r="D312">
+        <v>0.2</v>
+      </c>
+      <c r="E312">
+        <v>-3.2</v>
+      </c>
+      <c r="F312">
+        <v>0</v>
+      </c>
+      <c r="G312">
+        <v>-1</v>
+      </c>
+      <c r="H312">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8">
+      <c r="A313" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B313" t="s">
+        <v>49</v>
+      </c>
+      <c r="C313">
+        <v>-0.3</v>
+      </c>
+      <c r="D313">
+        <v>0.3</v>
+      </c>
+      <c r="E313">
+        <v>-1.2</v>
+      </c>
+      <c r="F313">
+        <v>0.2</v>
+      </c>
+      <c r="G313">
+        <v>-0.8</v>
+      </c>
+      <c r="H313">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8">
+      <c r="A314" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B314" t="s">
+        <v>50</v>
+      </c>
+      <c r="C314">
+        <v>0.3</v>
+      </c>
+      <c r="D314">
+        <v>0.1</v>
+      </c>
+      <c r="E314">
+        <v>3.8</v>
+      </c>
+      <c r="F314">
+        <v>0</v>
+      </c>
+      <c r="G314">
+        <v>0.2</v>
+      </c>
+      <c r="H314">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8">
+      <c r="A315" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B315" t="s">
+        <v>51</v>
+      </c>
+      <c r="C315">
+        <v>0.6</v>
+      </c>
+      <c r="D315">
+        <v>0.1</v>
+      </c>
+      <c r="E315">
+        <v>5.6</v>
+      </c>
+      <c r="F315">
+        <v>0</v>
+      </c>
+      <c r="G315">
+        <v>0.4</v>
+      </c>
+      <c r="H315">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8">
+      <c r="A316" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B316" t="s">
+        <v>52</v>
+      </c>
+      <c r="C316">
+        <v>0.2</v>
+      </c>
+      <c r="D316">
+        <v>0.1</v>
+      </c>
+      <c r="E316">
+        <v>2.2</v>
+      </c>
+      <c r="F316">
+        <v>0</v>
+      </c>
+      <c r="G316">
+        <v>0</v>
+      </c>
+      <c r="H316">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8">
+      <c r="A317" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B317" t="s">
+        <v>53</v>
+      </c>
+      <c r="C317">
+        <v>0.1</v>
+      </c>
+      <c r="D317">
+        <v>0.1</v>
+      </c>
+      <c r="E317">
+        <v>0.7</v>
+      </c>
+      <c r="F317">
+        <v>0.5</v>
+      </c>
+      <c r="G317">
+        <v>-0.1</v>
+      </c>
+      <c r="H317">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8">
+      <c r="A318" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B318" t="s">
+        <v>54</v>
+      </c>
+      <c r="C318">
+        <v>1.3</v>
+      </c>
+      <c r="D318">
+        <v>0.1</v>
+      </c>
+      <c r="E318">
+        <v>12.3</v>
+      </c>
+      <c r="F318">
+        <v>0</v>
+      </c>
+      <c r="G318">
+        <v>1.1</v>
+      </c>
+      <c r="H318">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8">
+      <c r="A319" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B319" t="s">
+        <v>55</v>
+      </c>
+      <c r="C319">
+        <v>0.7</v>
+      </c>
+      <c r="D319">
+        <v>0.1</v>
+      </c>
+      <c r="E319">
+        <v>7</v>
+      </c>
+      <c r="F319">
+        <v>0</v>
+      </c>
+      <c r="G319">
+        <v>0.5</v>
+      </c>
+      <c r="H319">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8">
+      <c r="A320" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B320" t="s">
+        <v>56</v>
+      </c>
+      <c r="C320">
+        <v>0.3</v>
+      </c>
+      <c r="D320">
+        <v>0.2</v>
+      </c>
+      <c r="E320">
+        <v>1.5</v>
+      </c>
+      <c r="F320">
+        <v>0.1</v>
+      </c>
+      <c r="G320">
+        <v>-0.1</v>
+      </c>
+      <c r="H320">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8">
+      <c r="A321" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B321" t="s">
+        <v>58</v>
+      </c>
+      <c r="C321">
+        <v>-0</v>
+      </c>
+      <c r="D321">
+        <v>0.1</v>
+      </c>
+      <c r="E321">
+        <v>-0.1</v>
+      </c>
+      <c r="F321">
+        <v>0.9</v>
+      </c>
+      <c r="G321">
+        <v>-0.3</v>
+      </c>
+      <c r="H321">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8">
+      <c r="A323" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8">
+      <c r="B324" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E324" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F324" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G324" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H324" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8">
+      <c r="A325" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B325" t="s">
+        <v>40</v>
+      </c>
+      <c r="C325">
+        <v>-1.3</v>
+      </c>
+      <c r="D325">
+        <v>0.1</v>
+      </c>
+      <c r="E325">
+        <v>-10.1</v>
+      </c>
+      <c r="F325">
+        <v>0</v>
+      </c>
+      <c r="G325">
+        <v>-1.5</v>
+      </c>
+      <c r="H325">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8">
+      <c r="A326" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B326" t="s">
+        <v>46</v>
+      </c>
+      <c r="C326">
+        <v>-0.1</v>
+      </c>
+      <c r="D326">
+        <v>0.1</v>
+      </c>
+      <c r="E326">
+        <v>-1.2</v>
+      </c>
+      <c r="F326">
+        <v>0.2</v>
+      </c>
+      <c r="G326">
+        <v>-0.4</v>
+      </c>
+      <c r="H326">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8">
+      <c r="A327" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B327" t="s">
+        <v>48</v>
+      </c>
+      <c r="C327">
+        <v>-0.7</v>
+      </c>
+      <c r="D327">
+        <v>0.2</v>
+      </c>
+      <c r="E327">
+        <v>-3</v>
+      </c>
+      <c r="F327">
+        <v>0</v>
+      </c>
+      <c r="G327">
+        <v>-1.1</v>
+      </c>
+      <c r="H327">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8">
+      <c r="A328" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B328" t="s">
+        <v>49</v>
+      </c>
+      <c r="C328">
+        <v>0.2</v>
+      </c>
+      <c r="D328">
+        <v>0.3</v>
+      </c>
+      <c r="E328">
+        <v>0.7</v>
+      </c>
+      <c r="F328">
+        <v>0.5</v>
+      </c>
+      <c r="G328">
+        <v>-0.3</v>
+      </c>
+      <c r="H328">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8">
+      <c r="A329" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B329" t="s">
+        <v>50</v>
+      </c>
+      <c r="C329">
+        <v>0.2</v>
+      </c>
+      <c r="D329">
+        <v>0.1</v>
+      </c>
+      <c r="E329">
+        <v>1.8</v>
+      </c>
+      <c r="F329">
+        <v>0.1</v>
+      </c>
+      <c r="G329">
+        <v>-0</v>
+      </c>
+      <c r="H329">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8">
+      <c r="A330" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B330" t="s">
+        <v>51</v>
+      </c>
+      <c r="C330">
+        <v>0.6</v>
+      </c>
+      <c r="D330">
+        <v>0.1</v>
+      </c>
+      <c r="E330">
+        <v>5.1</v>
+      </c>
+      <c r="F330">
+        <v>0</v>
+      </c>
+      <c r="G330">
+        <v>0.4</v>
+      </c>
+      <c r="H330">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8">
+      <c r="A331" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B331" t="s">
+        <v>52</v>
+      </c>
+      <c r="C331">
+        <v>-0.1</v>
+      </c>
+      <c r="D331">
+        <v>0.1</v>
+      </c>
+      <c r="E331">
+        <v>-1.2</v>
+      </c>
+      <c r="F331">
+        <v>0.2</v>
+      </c>
+      <c r="G331">
+        <v>-0.3</v>
+      </c>
+      <c r="H331">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8">
+      <c r="A332" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B332" t="s">
+        <v>53</v>
+      </c>
+      <c r="C332">
+        <v>-0.1</v>
+      </c>
+      <c r="D332">
+        <v>0.1</v>
+      </c>
+      <c r="E332">
+        <v>-1</v>
+      </c>
+      <c r="F332">
+        <v>0.3</v>
+      </c>
+      <c r="G332">
+        <v>-0.3</v>
+      </c>
+      <c r="H332">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8">
+      <c r="A333" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B333" t="s">
+        <v>54</v>
+      </c>
+      <c r="C333">
+        <v>0.5</v>
+      </c>
+      <c r="D333">
+        <v>0.1</v>
+      </c>
+      <c r="E333">
+        <v>4.9</v>
+      </c>
+      <c r="F333">
+        <v>0</v>
+      </c>
+      <c r="G333">
+        <v>0.3</v>
+      </c>
+      <c r="H333">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8">
+      <c r="A334" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B334" t="s">
+        <v>55</v>
+      </c>
+      <c r="C334">
+        <v>1</v>
+      </c>
+      <c r="D334">
+        <v>0.1</v>
+      </c>
+      <c r="E334">
+        <v>9.1</v>
+      </c>
+      <c r="F334">
+        <v>0</v>
+      </c>
+      <c r="G334">
+        <v>0.8</v>
+      </c>
+      <c r="H334">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8">
+      <c r="A335" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B335" t="s">
+        <v>56</v>
+      </c>
+      <c r="C335">
+        <v>-0</v>
+      </c>
+      <c r="D335">
+        <v>0.3</v>
+      </c>
+      <c r="E335">
+        <v>-0.1</v>
+      </c>
+      <c r="F335">
+        <v>1</v>
+      </c>
+      <c r="G335">
+        <v>-0.6</v>
+      </c>
+      <c r="H335">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8">
+      <c r="A336" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B336" t="s">
+        <v>58</v>
+      </c>
+      <c r="C336">
+        <v>-0.3</v>
+      </c>
+      <c r="D336">
+        <v>0.2</v>
+      </c>
+      <c r="E336">
+        <v>-1.8</v>
+      </c>
+      <c r="F336">
+        <v>0.1</v>
+      </c>
+      <c r="G336">
+        <v>-0.6</v>
+      </c>
+      <c r="H336">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8">
+      <c r="A338" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8">
+      <c r="B339" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D339" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E339" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F339" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G339" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H339" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8">
+      <c r="A340" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B340" t="s">
+        <v>40</v>
+      </c>
+      <c r="C340">
+        <v>-1.6</v>
+      </c>
+      <c r="D340">
+        <v>0.1</v>
+      </c>
+      <c r="E340">
+        <v>-11.7</v>
+      </c>
+      <c r="F340">
+        <v>0</v>
+      </c>
+      <c r="G340">
+        <v>-1.9</v>
+      </c>
+      <c r="H340">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8">
+      <c r="A341" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B341" t="s">
+        <v>46</v>
+      </c>
+      <c r="C341">
+        <v>0.2</v>
+      </c>
+      <c r="D341">
+        <v>0.1</v>
+      </c>
+      <c r="E341">
+        <v>1.7</v>
+      </c>
+      <c r="F341">
+        <v>0.1</v>
+      </c>
+      <c r="G341">
+        <v>-0</v>
+      </c>
+      <c r="H341">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8">
+      <c r="A342" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B342" t="s">
+        <v>48</v>
+      </c>
+      <c r="C342">
+        <v>0.1</v>
+      </c>
+      <c r="D342">
+        <v>0.2</v>
+      </c>
+      <c r="E342">
+        <v>0.6</v>
+      </c>
+      <c r="F342">
+        <v>0.5</v>
+      </c>
+      <c r="G342">
+        <v>-0.2</v>
+      </c>
+      <c r="H342">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8">
+      <c r="A343" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B343" t="s">
+        <v>49</v>
+      </c>
+      <c r="C343">
+        <v>0.3</v>
+      </c>
+      <c r="D343">
+        <v>0.3</v>
+      </c>
+      <c r="E343">
+        <v>1.1</v>
+      </c>
+      <c r="F343">
+        <v>0.3</v>
+      </c>
+      <c r="G343">
+        <v>-0.2</v>
+      </c>
+      <c r="H343">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8">
+      <c r="A344" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B344" t="s">
+        <v>50</v>
+      </c>
+      <c r="C344">
+        <v>0.1</v>
+      </c>
+      <c r="D344">
+        <v>0.1</v>
+      </c>
+      <c r="E344">
+        <v>0.9</v>
+      </c>
+      <c r="F344">
+        <v>0.4</v>
+      </c>
+      <c r="G344">
+        <v>-0.1</v>
+      </c>
+      <c r="H344">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8">
+      <c r="A345" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B345" t="s">
+        <v>51</v>
+      </c>
+      <c r="C345">
+        <v>0.2</v>
+      </c>
+      <c r="D345">
+        <v>0.1</v>
+      </c>
+      <c r="E345">
+        <v>1.1</v>
+      </c>
+      <c r="F345">
+        <v>0.3</v>
+      </c>
+      <c r="G345">
+        <v>-0.1</v>
+      </c>
+      <c r="H345">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8">
+      <c r="A346" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B346" t="s">
+        <v>52</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>0.1</v>
+      </c>
+      <c r="E346">
+        <v>0.2</v>
+      </c>
+      <c r="F346">
+        <v>0.8</v>
+      </c>
+      <c r="G346">
+        <v>-0.2</v>
+      </c>
+      <c r="H346">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8">
+      <c r="A347" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B347" t="s">
+        <v>53</v>
+      </c>
+      <c r="C347">
+        <v>0.1</v>
+      </c>
+      <c r="D347">
+        <v>0.1</v>
+      </c>
+      <c r="E347">
+        <v>0.9</v>
+      </c>
+      <c r="F347">
+        <v>0.4</v>
+      </c>
+      <c r="G347">
+        <v>-0.1</v>
+      </c>
+      <c r="H347">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8">
+      <c r="A348" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B348" t="s">
+        <v>54</v>
+      </c>
+      <c r="C348">
+        <v>0.8</v>
+      </c>
+      <c r="D348">
+        <v>0.1</v>
+      </c>
+      <c r="E348">
+        <v>7.1</v>
+      </c>
+      <c r="F348">
+        <v>0</v>
+      </c>
+      <c r="G348">
+        <v>0.6</v>
+      </c>
+      <c r="H348">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8">
+      <c r="A349" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B349" t="s">
+        <v>55</v>
+      </c>
+      <c r="C349">
+        <v>0.2</v>
+      </c>
+      <c r="D349">
+        <v>0.1</v>
+      </c>
+      <c r="E349">
+        <v>1.3</v>
+      </c>
+      <c r="F349">
+        <v>0.2</v>
+      </c>
+      <c r="G349">
+        <v>-0.1</v>
+      </c>
+      <c r="H349">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8">
+      <c r="A350" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B350" t="s">
+        <v>56</v>
+      </c>
+      <c r="C350">
+        <v>0.2</v>
+      </c>
+      <c r="D350">
+        <v>0.3</v>
+      </c>
+      <c r="E350">
+        <v>0.6</v>
+      </c>
+      <c r="F350">
+        <v>0.5</v>
+      </c>
+      <c r="G350">
+        <v>-0.3</v>
+      </c>
+      <c r="H350">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8">
+      <c r="A351" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B351" t="s">
+        <v>58</v>
+      </c>
+      <c r="C351">
+        <v>0.2</v>
+      </c>
+      <c r="D351">
+        <v>0.1</v>
+      </c>
+      <c r="E351">
+        <v>1.1</v>
+      </c>
+      <c r="F351">
+        <v>0.3</v>
+      </c>
+      <c r="G351">
+        <v>-0.1</v>
+      </c>
+      <c r="H351">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8">
+      <c r="A353" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8">
+      <c r="B354" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E354" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F354" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G354" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H354" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8">
+      <c r="A355" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B355" t="s">
+        <v>40</v>
+      </c>
+      <c r="C355">
+        <v>-1.3</v>
+      </c>
+      <c r="D355">
+        <v>0.1</v>
+      </c>
+      <c r="E355">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="F355">
+        <v>0</v>
+      </c>
+      <c r="G355">
+        <v>-1.6</v>
+      </c>
+      <c r="H355">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8">
+      <c r="A356" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B356" t="s">
+        <v>46</v>
+      </c>
+      <c r="C356">
+        <v>-0</v>
+      </c>
+      <c r="D356">
+        <v>0.1</v>
+      </c>
+      <c r="E356">
+        <v>-0.2</v>
+      </c>
+      <c r="F356">
+        <v>0.8</v>
+      </c>
+      <c r="G356">
+        <v>-0.3</v>
+      </c>
+      <c r="H356">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8">
+      <c r="A357" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B357" t="s">
+        <v>48</v>
+      </c>
+      <c r="C357">
+        <v>-0.5</v>
+      </c>
+      <c r="D357">
+        <v>0.2</v>
+      </c>
+      <c r="E357">
+        <v>-2.3</v>
+      </c>
+      <c r="F357">
+        <v>0</v>
+      </c>
+      <c r="G357">
+        <v>-1</v>
+      </c>
+      <c r="H357">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8">
+      <c r="A358" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B358" t="s">
+        <v>49</v>
+      </c>
+      <c r="C358">
+        <v>-0.2</v>
+      </c>
+      <c r="D358">
+        <v>0.3</v>
+      </c>
+      <c r="E358">
+        <v>-0.6</v>
+      </c>
+      <c r="F358">
+        <v>0.6</v>
+      </c>
+      <c r="G358">
+        <v>-0.8</v>
+      </c>
+      <c r="H358">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8">
+      <c r="A359" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B359" t="s">
+        <v>50</v>
+      </c>
+      <c r="C359">
+        <v>0.3</v>
+      </c>
+      <c r="D359">
+        <v>0.1</v>
+      </c>
+      <c r="E359">
+        <v>2.6</v>
+      </c>
+      <c r="F359">
+        <v>0</v>
+      </c>
+      <c r="G359">
+        <v>0.1</v>
+      </c>
+      <c r="H359">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8">
+      <c r="A360" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B360" t="s">
+        <v>51</v>
+      </c>
+      <c r="C360">
+        <v>0.6</v>
+      </c>
+      <c r="D360">
+        <v>0.1</v>
+      </c>
+      <c r="E360">
+        <v>5</v>
+      </c>
+      <c r="F360">
+        <v>0</v>
+      </c>
+      <c r="G360">
+        <v>0.4</v>
+      </c>
+      <c r="H360">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8">
+      <c r="A361" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B361" t="s">
+        <v>52</v>
+      </c>
+      <c r="C361">
+        <v>0.1</v>
+      </c>
+      <c r="D361">
+        <v>0.1</v>
+      </c>
+      <c r="E361">
+        <v>0.5</v>
+      </c>
+      <c r="F361">
+        <v>0.6</v>
+      </c>
+      <c r="G361">
+        <v>-0.2</v>
+      </c>
+      <c r="H361">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8">
+      <c r="A362" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B362" t="s">
+        <v>53</v>
+      </c>
+      <c r="C362">
+        <v>-0</v>
+      </c>
+      <c r="D362">
+        <v>0.1</v>
+      </c>
+      <c r="E362">
+        <v>-0.4</v>
+      </c>
+      <c r="F362">
+        <v>0.7</v>
+      </c>
+      <c r="G362">
+        <v>-0.3</v>
+      </c>
+      <c r="H362">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8">
+      <c r="A363" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B363" t="s">
+        <v>54</v>
+      </c>
+      <c r="C363">
+        <v>0.1</v>
+      </c>
+      <c r="D363">
+        <v>0.1</v>
+      </c>
+      <c r="E363">
+        <v>0.9</v>
+      </c>
+      <c r="F363">
+        <v>0.4</v>
+      </c>
+      <c r="G363">
+        <v>-0.1</v>
+      </c>
+      <c r="H363">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8">
+      <c r="A364" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B364" t="s">
+        <v>55</v>
+      </c>
+      <c r="C364">
+        <v>0.5</v>
+      </c>
+      <c r="D364">
+        <v>0.1</v>
+      </c>
+      <c r="E364">
+        <v>3.4</v>
+      </c>
+      <c r="F364">
+        <v>0</v>
+      </c>
+      <c r="G364">
+        <v>0.2</v>
+      </c>
+      <c r="H364">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8">
+      <c r="A365" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B365" t="s">
+        <v>56</v>
+      </c>
+      <c r="C365">
+        <v>-0.6</v>
+      </c>
+      <c r="D365">
+        <v>0.4</v>
+      </c>
+      <c r="E365">
+        <v>-1.5</v>
+      </c>
+      <c r="F365">
+        <v>0.1</v>
+      </c>
+      <c r="G365">
+        <v>-1.3</v>
+      </c>
+      <c r="H365">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8">
+      <c r="A366" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B366" t="s">
+        <v>58</v>
+      </c>
+      <c r="C366">
+        <v>-0</v>
+      </c>
+      <c r="D366">
+        <v>0.2</v>
+      </c>
+      <c r="E366">
+        <v>-0.1</v>
+      </c>
+      <c r="F366">
+        <v>1</v>
+      </c>
+      <c r="G366">
+        <v>-0.4</v>
+      </c>
+      <c r="H366">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8">
+      <c r="A368" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8">
+      <c r="B369" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C369" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D369" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E369" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F369" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G369" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H369" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8">
+      <c r="A370" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B370" t="s">
+        <v>40</v>
+      </c>
+      <c r="C370">
+        <v>-3.3</v>
+      </c>
+      <c r="D370">
+        <v>0.3</v>
+      </c>
+      <c r="E370">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="F370">
+        <v>0</v>
+      </c>
+      <c r="G370">
+        <v>-3.9</v>
+      </c>
+      <c r="H370">
+        <v>-2.6</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8">
+      <c r="A371" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B371" t="s">
+        <v>46</v>
+      </c>
+      <c r="C371">
+        <v>-0.7</v>
+      </c>
+      <c r="D371">
+        <v>0.3</v>
+      </c>
+      <c r="E371">
+        <v>-2.2</v>
+      </c>
+      <c r="F371">
+        <v>0</v>
+      </c>
+      <c r="G371">
+        <v>-1.4</v>
+      </c>
+      <c r="H371">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8">
+      <c r="A372" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B372" t="s">
+        <v>48</v>
+      </c>
+      <c r="C372">
+        <v>-0.4</v>
+      </c>
+      <c r="D372">
+        <v>0.5</v>
+      </c>
+      <c r="E372">
+        <v>-0.7</v>
+      </c>
+      <c r="F372">
+        <v>0.5</v>
+      </c>
+      <c r="G372">
+        <v>-1.4</v>
+      </c>
+      <c r="H372">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8">
+      <c r="A373" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B373" t="s">
+        <v>49</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>0.6</v>
+      </c>
+      <c r="E373">
+        <v>0.1</v>
+      </c>
+      <c r="F373">
+        <v>0.9</v>
+      </c>
+      <c r="G373">
+        <v>-1.2</v>
+      </c>
+      <c r="H373">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8">
+      <c r="A374" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B374" t="s">
+        <v>50</v>
+      </c>
+      <c r="C374">
+        <v>-0.8</v>
+      </c>
+      <c r="D374">
+        <v>0.3</v>
+      </c>
+      <c r="E374">
+        <v>-2.5</v>
+      </c>
+      <c r="F374">
+        <v>0</v>
+      </c>
+      <c r="G374">
+        <v>-1.4</v>
+      </c>
+      <c r="H374">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8">
+      <c r="A375" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B375" t="s">
+        <v>51</v>
+      </c>
+      <c r="C375">
+        <v>-0.1</v>
+      </c>
+      <c r="D375">
+        <v>0.3</v>
+      </c>
+      <c r="E375">
+        <v>-0.4</v>
+      </c>
+      <c r="F375">
+        <v>0.7</v>
+      </c>
+      <c r="G375">
+        <v>-0.7</v>
+      </c>
+      <c r="H375">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8">
+      <c r="A376" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B376" t="s">
+        <v>52</v>
+      </c>
+      <c r="C376">
+        <v>0.7</v>
+      </c>
+      <c r="D376">
+        <v>0.2</v>
+      </c>
+      <c r="E376">
+        <v>2.9</v>
+      </c>
+      <c r="F376">
+        <v>0</v>
+      </c>
+      <c r="G376">
+        <v>0.2</v>
+      </c>
+      <c r="H376">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8">
+      <c r="A377" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B377" t="s">
+        <v>53</v>
+      </c>
+      <c r="C377">
+        <v>-0.4</v>
+      </c>
+      <c r="D377">
+        <v>0.2</v>
+      </c>
+      <c r="E377">
+        <v>-1.6</v>
+      </c>
+      <c r="F377">
+        <v>0.1</v>
+      </c>
+      <c r="G377">
+        <v>-0.9</v>
+      </c>
+      <c r="H377">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8">
+      <c r="A378" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B378" t="s">
+        <v>54</v>
+      </c>
+      <c r="C378">
+        <v>1.3</v>
+      </c>
+      <c r="D378">
+        <v>0.3</v>
+      </c>
+      <c r="E378">
+        <v>4.4</v>
+      </c>
+      <c r="F378">
+        <v>0</v>
+      </c>
+      <c r="G378">
+        <v>0.7</v>
+      </c>
+      <c r="H378">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8">
+      <c r="A379" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B379" t="s">
+        <v>55</v>
+      </c>
+      <c r="C379">
+        <v>-0.3</v>
+      </c>
+      <c r="D379">
+        <v>0.3</v>
+      </c>
+      <c r="E379">
+        <v>-1</v>
+      </c>
+      <c r="F379">
+        <v>0.3</v>
+      </c>
+      <c r="G379">
+        <v>-1</v>
+      </c>
+      <c r="H379">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8">
+      <c r="A380" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B380" t="s">
+        <v>56</v>
+      </c>
+      <c r="C380">
+        <v>0.3</v>
+      </c>
+      <c r="D380">
+        <v>0.8</v>
+      </c>
+      <c r="E380">
+        <v>0.3</v>
+      </c>
+      <c r="F380">
+        <v>0.7</v>
+      </c>
+      <c r="G380">
+        <v>-1.3</v>
+      </c>
+      <c r="H380">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8">
+      <c r="A381" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B381" t="s">
+        <v>58</v>
+      </c>
+      <c r="C381">
+        <v>-0.5</v>
+      </c>
+      <c r="D381">
+        <v>0.4</v>
+      </c>
+      <c r="E381">
+        <v>-1.3</v>
+      </c>
+      <c r="F381">
+        <v>0.2</v>
+      </c>
+      <c r="G381">
+        <v>-1.3</v>
+      </c>
+      <c r="H381">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/assets_output/07_multinomial_logistic_regression.xlsx
+++ b/assets_output/07_multinomial_logistic_regression.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="186">
   <si>
     <t>MNLogit: 'Entry point into BAHSA services (pathway type and level)', table 0</t>
   </si>
@@ -49,7 +49,7 @@
     <t>y</t>
   </si>
   <si>
-    <t>2026-05-17 15:54</t>
+    <t>2026-05-18 18:16</t>
   </si>
   <si>
     <t>4355</t>
@@ -449,6 +449,9 @@
   </si>
   <si>
     <t>after_rt_ret_within_2y</t>
+  </si>
+  <si>
+    <t>2026-05-18 18:17</t>
   </si>
   <si>
     <t>730</t>
@@ -9897,7 +9900,7 @@
         <v>18</v>
       </c>
       <c r="E451" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="452" spans="1:7">
@@ -9908,13 +9911,13 @@
         <v>3</v>
       </c>
       <c r="C452" t="s">
-        <v>11</v>
+        <v>145</v>
       </c>
       <c r="D452" t="s">
         <v>19</v>
       </c>
       <c r="E452" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="453" spans="1:7">
@@ -9925,13 +9928,13 @@
         <v>4</v>
       </c>
       <c r="C453" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D453" t="s">
         <v>20</v>
       </c>
       <c r="E453" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="454" spans="1:7">
@@ -9942,13 +9945,13 @@
         <v>5</v>
       </c>
       <c r="C454" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D454" t="s">
         <v>21</v>
       </c>
       <c r="E454" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="455" spans="1:7">
@@ -9959,13 +9962,13 @@
         <v>6</v>
       </c>
       <c r="C455" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D455" t="s">
         <v>22</v>
       </c>
       <c r="E455" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="456" spans="1:7">
@@ -9982,7 +9985,7 @@
         <v>23</v>
       </c>
       <c r="E456" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="457" spans="1:7">
@@ -10004,7 +10007,7 @@
     </row>
     <row r="459" spans="1:7">
       <c r="A459" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="460" spans="1:7">
@@ -10052,7 +10055,7 @@
     </row>
     <row r="462" spans="1:7">
       <c r="A462" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B462">
         <v>2.5</v>
@@ -10121,7 +10124,7 @@
     </row>
     <row r="466" spans="1:6">
       <c r="A466" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="467" spans="1:6">
@@ -10163,7 +10166,7 @@
     </row>
     <row r="469" spans="1:6">
       <c r="A469" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B469">
         <v>0</v>
@@ -10223,7 +10226,7 @@
     </row>
     <row r="473" spans="1:6">
       <c r="A473" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="474" spans="1:6">
@@ -10265,13 +10268,13 @@
         <v>2</v>
       </c>
       <c r="C476" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D476" t="s">
         <v>18</v>
       </c>
       <c r="E476" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="477" spans="1:6">
@@ -10282,13 +10285,13 @@
         <v>3</v>
       </c>
       <c r="C477" t="s">
-        <v>11</v>
+        <v>145</v>
       </c>
       <c r="D477" t="s">
         <v>19</v>
       </c>
       <c r="E477" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="478" spans="1:6">
@@ -10299,13 +10302,13 @@
         <v>4</v>
       </c>
       <c r="C478" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D478" t="s">
         <v>20</v>
       </c>
       <c r="E478" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="479" spans="1:6">
@@ -10316,13 +10319,13 @@
         <v>5</v>
       </c>
       <c r="C479" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D479" t="s">
         <v>21</v>
       </c>
       <c r="E479" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="480" spans="1:6">
@@ -10333,13 +10336,13 @@
         <v>6</v>
       </c>
       <c r="C480" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D480" t="s">
         <v>22</v>
       </c>
       <c r="E480" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="481" spans="1:8">
@@ -10356,7 +10359,7 @@
         <v>23</v>
       </c>
       <c r="E481" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="482" spans="1:8">
@@ -10378,12 +10381,12 @@
     </row>
     <row r="484" spans="1:8">
       <c r="A484" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="485" spans="1:8">
       <c r="B485" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>34</v>
@@ -10718,12 +10721,12 @@
     </row>
     <row r="499" spans="1:8">
       <c r="A499" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="500" spans="1:8">
       <c r="B500" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C500" s="1" t="s">
         <v>34</v>
@@ -11058,12 +11061,12 @@
     </row>
     <row r="514" spans="1:8">
       <c r="A514" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="515" spans="1:8">
       <c r="B515" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C515" s="1" t="s">
         <v>34</v>
@@ -11398,12 +11401,12 @@
     </row>
     <row r="529" spans="1:8">
       <c r="A529" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="530" spans="1:8">
       <c r="B530" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C530" s="1" t="s">
         <v>34</v>
@@ -11738,12 +11741,12 @@
     </row>
     <row r="544" spans="1:8">
       <c r="A544" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="545" spans="1:8">
       <c r="B545" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C545" s="1" t="s">
         <v>34</v>
@@ -12078,12 +12081,12 @@
     </row>
     <row r="559" spans="1:8">
       <c r="A559" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="560" spans="1:8">
       <c r="B560" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C560" s="1" t="s">
         <v>34</v>
@@ -12418,7 +12421,7 @@
     </row>
     <row r="574" spans="1:8">
       <c r="A574" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="575" spans="1:8">
@@ -12673,7 +12676,7 @@
     </row>
     <row r="588" spans="1:7">
       <c r="A588" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B588" s="1" t="s">
         <v>40</v>
@@ -12906,7 +12909,7 @@
     </row>
     <row r="600" spans="1:7">
       <c r="A600" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B600" s="1" t="s">
         <v>40</v>
@@ -13139,7 +13142,7 @@
     </row>
     <row r="612" spans="1:7">
       <c r="A612" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B612" s="1" t="s">
         <v>40</v>
@@ -13363,7 +13366,7 @@
     </row>
     <row r="624" spans="1:7">
       <c r="A624" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B624" s="1" t="s">
         <v>40</v>

--- a/assets_output/07_multinomial_logistic_regression.xlsx
+++ b/assets_output/07_multinomial_logistic_regression.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="186">
   <si>
     <t>MNLogit: 'Entry point into BAHSA services (pathway type and level)', table 0</t>
   </si>
@@ -49,7 +49,7 @@
     <t>y</t>
   </si>
   <si>
-    <t>2026-05-22 14:15</t>
+    <t>2026-05-22 18:13</t>
   </si>
   <si>
     <t>3391</t>
@@ -371,6 +371,9 @@
   </si>
   <si>
     <t>multiple_returns</t>
+  </si>
+  <si>
+    <t>2026-05-22 18:14</t>
   </si>
   <si>
     <t>6</t>
@@ -8870,7 +8873,7 @@
         <v>18</v>
       </c>
       <c r="E389" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="390" spans="1:7">
@@ -8881,13 +8884,13 @@
         <v>3</v>
       </c>
       <c r="C390" t="s">
-        <v>11</v>
+        <v>119</v>
       </c>
       <c r="D390" t="s">
         <v>19</v>
       </c>
       <c r="E390" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="391" spans="1:7">
@@ -8904,7 +8907,7 @@
         <v>20</v>
       </c>
       <c r="E391" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="392" spans="1:7">
@@ -8915,13 +8918,13 @@
         <v>5</v>
       </c>
       <c r="C392" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D392" t="s">
         <v>21</v>
       </c>
       <c r="E392" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="393" spans="1:7">
@@ -8932,13 +8935,13 @@
         <v>6</v>
       </c>
       <c r="C393" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D393" t="s">
         <v>22</v>
       </c>
       <c r="E393" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="394" spans="1:7">
@@ -8955,7 +8958,7 @@
         <v>23</v>
       </c>
       <c r="E394" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="395" spans="1:7">
@@ -8966,7 +8969,7 @@
         <v>8</v>
       </c>
       <c r="C395" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D395" t="s">
         <v>24</v>
@@ -8977,7 +8980,7 @@
     </row>
     <row r="397" spans="1:7">
       <c r="A397" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="398" spans="1:7">
@@ -8988,10 +8991,10 @@
         <v>35</v>
       </c>
       <c r="D398" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F398" s="1" t="s">
         <v>38</v>
@@ -9163,7 +9166,7 @@
     </row>
     <row r="407" spans="1:7">
       <c r="A407" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="408" spans="1:7">
@@ -9330,7 +9333,7 @@
     </row>
     <row r="418" spans="1:7">
       <c r="A418" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="419" spans="1:7">
@@ -9372,13 +9375,13 @@
         <v>2</v>
       </c>
       <c r="C421" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D421" t="s">
         <v>18</v>
       </c>
       <c r="E421" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="422" spans="1:7">
@@ -9389,13 +9392,13 @@
         <v>3</v>
       </c>
       <c r="C422" t="s">
-        <v>11</v>
+        <v>119</v>
       </c>
       <c r="D422" t="s">
         <v>19</v>
       </c>
       <c r="E422" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="423" spans="1:7">
@@ -9412,7 +9415,7 @@
         <v>20</v>
       </c>
       <c r="E423" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="424" spans="1:7">
@@ -9423,13 +9426,13 @@
         <v>5</v>
       </c>
       <c r="C424" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D424" t="s">
         <v>21</v>
       </c>
       <c r="E424" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="425" spans="1:7">
@@ -9440,13 +9443,13 @@
         <v>6</v>
       </c>
       <c r="C425" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D425" t="s">
         <v>22</v>
       </c>
       <c r="E425" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="426" spans="1:7">
@@ -9463,7 +9466,7 @@
         <v>23</v>
       </c>
       <c r="E426" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="427" spans="1:7">
@@ -9474,7 +9477,7 @@
         <v>8</v>
       </c>
       <c r="C427" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D427" t="s">
         <v>24</v>
@@ -9485,7 +9488,7 @@
     </row>
     <row r="429" spans="1:7">
       <c r="A429" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="430" spans="1:7">
@@ -9496,10 +9499,10 @@
         <v>35</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F430" s="1" t="s">
         <v>38</v>
@@ -9671,7 +9674,7 @@
     </row>
     <row r="439" spans="1:7">
       <c r="A439" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="440" spans="1:7">
@@ -9838,7 +9841,7 @@
     </row>
     <row r="450" spans="1:7">
       <c r="A450" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="451" spans="1:7">
@@ -9880,13 +9883,13 @@
         <v>2</v>
       </c>
       <c r="C453" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D453" t="s">
         <v>18</v>
       </c>
       <c r="E453" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="454" spans="1:7">
@@ -9897,13 +9900,13 @@
         <v>3</v>
       </c>
       <c r="C454" t="s">
-        <v>11</v>
+        <v>119</v>
       </c>
       <c r="D454" t="s">
         <v>19</v>
       </c>
       <c r="E454" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="455" spans="1:7">
@@ -9914,13 +9917,13 @@
         <v>4</v>
       </c>
       <c r="C455" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D455" t="s">
         <v>20</v>
       </c>
       <c r="E455" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="456" spans="1:7">
@@ -9931,13 +9934,13 @@
         <v>5</v>
       </c>
       <c r="C456" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D456" t="s">
         <v>21</v>
       </c>
       <c r="E456" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="457" spans="1:7">
@@ -9948,13 +9951,13 @@
         <v>6</v>
       </c>
       <c r="C457" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D457" t="s">
         <v>22</v>
       </c>
       <c r="E457" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="458" spans="1:7">
@@ -9971,7 +9974,7 @@
         <v>23</v>
       </c>
       <c r="E458" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="459" spans="1:7">
@@ -9993,7 +9996,7 @@
     </row>
     <row r="461" spans="1:7">
       <c r="A461" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="462" spans="1:7">
@@ -10004,10 +10007,10 @@
         <v>35</v>
       </c>
       <c r="D462" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E462" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F462" s="1" t="s">
         <v>38</v>
@@ -10041,7 +10044,7 @@
     </row>
     <row r="464" spans="1:7">
       <c r="A464" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B464">
         <v>2.4</v>
@@ -10110,7 +10113,7 @@
     </row>
     <row r="468" spans="1:7">
       <c r="A468" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="469" spans="1:7">
@@ -10152,7 +10155,7 @@
     </row>
     <row r="471" spans="1:7">
       <c r="A471" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B471">
         <v>0</v>
@@ -10214,7 +10217,7 @@
     </row>
     <row r="476" spans="1:7">
       <c r="A476" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="477" spans="1:7">
@@ -10256,13 +10259,13 @@
         <v>2</v>
       </c>
       <c r="C479" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D479" t="s">
         <v>18</v>
       </c>
       <c r="E479" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="480" spans="1:7">
@@ -10273,13 +10276,13 @@
         <v>3</v>
       </c>
       <c r="C480" t="s">
-        <v>11</v>
+        <v>119</v>
       </c>
       <c r="D480" t="s">
         <v>19</v>
       </c>
       <c r="E480" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="481" spans="1:8">
@@ -10290,13 +10293,13 @@
         <v>4</v>
       </c>
       <c r="C481" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D481" t="s">
         <v>20</v>
       </c>
       <c r="E481" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="482" spans="1:8">
@@ -10307,13 +10310,13 @@
         <v>5</v>
       </c>
       <c r="C482" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D482" t="s">
         <v>21</v>
       </c>
       <c r="E482" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="483" spans="1:8">
@@ -10324,13 +10327,13 @@
         <v>6</v>
       </c>
       <c r="C483" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D483" t="s">
         <v>22</v>
       </c>
       <c r="E483" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="484" spans="1:8">
@@ -10347,7 +10350,7 @@
         <v>23</v>
       </c>
       <c r="E484" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="485" spans="1:8">
@@ -10369,12 +10372,12 @@
     </row>
     <row r="487" spans="1:8">
       <c r="A487" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="488" spans="1:8">
       <c r="B488" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C488" s="1" t="s">
         <v>34</v>
@@ -10709,12 +10712,12 @@
     </row>
     <row r="502" spans="1:8">
       <c r="A502" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="503" spans="1:8">
       <c r="B503" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C503" s="1" t="s">
         <v>34</v>
@@ -11049,12 +11052,12 @@
     </row>
     <row r="517" spans="1:8">
       <c r="A517" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="518" spans="1:8">
       <c r="B518" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C518" s="1" t="s">
         <v>34</v>
@@ -11389,12 +11392,12 @@
     </row>
     <row r="532" spans="1:8">
       <c r="A532" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="533" spans="1:8">
       <c r="B533" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C533" s="1" t="s">
         <v>34</v>
@@ -11729,12 +11732,12 @@
     </row>
     <row r="547" spans="1:8">
       <c r="A547" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="548" spans="1:8">
       <c r="B548" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C548" s="1" t="s">
         <v>34</v>
@@ -12069,12 +12072,12 @@
     </row>
     <row r="562" spans="1:8">
       <c r="A562" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="563" spans="1:8">
       <c r="B563" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C563" s="1" t="s">
         <v>34</v>
@@ -12409,7 +12412,7 @@
     </row>
     <row r="577" spans="1:7">
       <c r="A577" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="578" spans="1:7">
@@ -12661,7 +12664,7 @@
     </row>
     <row r="591" spans="1:7">
       <c r="A591" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B591" s="1" t="s">
         <v>40</v>
@@ -12888,7 +12891,7 @@
     </row>
     <row r="603" spans="1:7">
       <c r="A603" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B603" s="1" t="s">
         <v>40</v>
@@ -13118,7 +13121,7 @@
     </row>
     <row r="615" spans="1:7">
       <c r="A615" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B615" s="1" t="s">
         <v>40</v>
@@ -13342,7 +13345,7 @@
     </row>
     <row r="627" spans="1:7">
       <c r="A627" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B627" s="1" t="s">
         <v>40</v>

--- a/assets_output/07_multinomial_logistic_regression.xlsx
+++ b/assets_output/07_multinomial_logistic_regression.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="186">
   <si>
     <t>MNLogit: 'Entry point into BAHSA services (pathway type and level)', table 0</t>
   </si>
@@ -49,7 +49,7 @@
     <t>y</t>
   </si>
   <si>
-    <t>2026-05-22 18:13</t>
+    <t>2026-05-22 18:29</t>
   </si>
   <si>
     <t>3391</t>
@@ -373,9 +373,6 @@
     <t>multiple_returns</t>
   </si>
   <si>
-    <t>2026-05-22 18:14</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
@@ -494,6 +491,9 @@
   </si>
   <si>
     <t>pl_outcome</t>
+  </si>
+  <si>
+    <t>2026-05-22 18:30</t>
   </si>
   <si>
     <t>4219</t>
@@ -929,7 +929,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H650"/>
+  <dimension ref="A1:H647"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -8873,7 +8873,7 @@
         <v>18</v>
       </c>
       <c r="E389" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="390" spans="1:7">
@@ -8884,13 +8884,13 @@
         <v>3</v>
       </c>
       <c r="C390" t="s">
-        <v>119</v>
+        <v>11</v>
       </c>
       <c r="D390" t="s">
         <v>19</v>
       </c>
       <c r="E390" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="391" spans="1:7">
@@ -8907,7 +8907,7 @@
         <v>20</v>
       </c>
       <c r="E391" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="392" spans="1:7">
@@ -8918,13 +8918,13 @@
         <v>5</v>
       </c>
       <c r="C392" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D392" t="s">
         <v>21</v>
       </c>
       <c r="E392" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="393" spans="1:7">
@@ -8935,13 +8935,13 @@
         <v>6</v>
       </c>
       <c r="C393" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D393" t="s">
         <v>22</v>
       </c>
       <c r="E393" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="394" spans="1:7">
@@ -8958,7 +8958,7 @@
         <v>23</v>
       </c>
       <c r="E394" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="395" spans="1:7">
@@ -8969,7 +8969,7 @@
         <v>8</v>
       </c>
       <c r="C395" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D395" t="s">
         <v>24</v>
@@ -8980,7 +8980,7 @@
     </row>
     <row r="397" spans="1:7">
       <c r="A397" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="398" spans="1:7">
@@ -8991,10 +8991,10 @@
         <v>35</v>
       </c>
       <c r="D398" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E398" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="E398" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="F398" s="1" t="s">
         <v>38</v>
@@ -9166,7 +9166,7 @@
     </row>
     <row r="407" spans="1:7">
       <c r="A407" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="408" spans="1:7">
@@ -9268,12 +9268,27 @@
     </row>
     <row r="413" spans="1:7">
       <c r="A413" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
+      </c>
+      <c r="B413">
+        <v>0</v>
+      </c>
+      <c r="C413" t="s">
+        <v>69</v>
+      </c>
+      <c r="D413">
+        <v>2</v>
+      </c>
+      <c r="E413">
+        <v>1.5</v>
+      </c>
+      <c r="F413">
+        <v>2.8</v>
       </c>
     </row>
     <row r="414" spans="1:7">
       <c r="A414" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B414">
         <v>0</v>
@@ -9282,18 +9297,18 @@
         <v>69</v>
       </c>
       <c r="D414">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="E414">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F414">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="415" spans="1:7">
       <c r="A415" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B415">
         <v>0</v>
@@ -9302,83 +9317,80 @@
         <v>69</v>
       </c>
       <c r="D415">
-        <v>2.3</v>
+        <v>5.8</v>
       </c>
       <c r="E415">
+        <v>3.8</v>
+      </c>
+      <c r="F415">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7">
+      <c r="A417" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7">
+      <c r="B418" s="1">
+        <v>0</v>
+      </c>
+      <c r="C418" s="1">
         <v>1</v>
       </c>
-      <c r="F415">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="416" spans="1:7">
-      <c r="A416" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B416">
-        <v>0</v>
-      </c>
-      <c r="C416" t="s">
-        <v>69</v>
-      </c>
-      <c r="D416">
-        <v>5.8</v>
-      </c>
-      <c r="E416">
-        <v>3.8</v>
-      </c>
-      <c r="F416">
-        <v>8.9</v>
-      </c>
-    </row>
-    <row r="418" spans="1:7">
-      <c r="A418" t="s">
-        <v>133</v>
+      <c r="D418" s="1">
+        <v>2</v>
+      </c>
+      <c r="E418" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="419" spans="1:7">
-      <c r="B419" s="1">
-        <v>0</v>
-      </c>
-      <c r="C419" s="1">
+      <c r="A419" s="1">
+        <v>0</v>
+      </c>
+      <c r="B419" t="s">
         <v>1</v>
       </c>
-      <c r="D419" s="1">
-        <v>2</v>
-      </c>
-      <c r="E419" s="1">
-        <v>3</v>
+      <c r="C419" t="s">
+        <v>117</v>
+      </c>
+      <c r="D419" t="s">
+        <v>17</v>
+      </c>
+      <c r="E419" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="420" spans="1:7">
       <c r="A420" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B420" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C420" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="D420" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E420" t="s">
-        <v>25</v>
+        <v>135</v>
       </c>
     </row>
     <row r="421" spans="1:7">
       <c r="A421" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B421" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C421" t="s">
-        <v>134</v>
+        <v>11</v>
       </c>
       <c r="D421" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E421" t="s">
         <v>136</v>
@@ -9386,16 +9398,16 @@
     </row>
     <row r="422" spans="1:7">
       <c r="A422" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B422" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C422" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D422" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E422" t="s">
         <v>137</v>
@@ -9403,16 +9415,16 @@
     </row>
     <row r="423" spans="1:7">
       <c r="A423" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B423" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C423" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="D423" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E423" t="s">
         <v>138</v>
@@ -9420,16 +9432,16 @@
     </row>
     <row r="424" spans="1:7">
       <c r="A424" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B424" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C424" t="s">
         <v>120</v>
       </c>
       <c r="D424" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E424" t="s">
         <v>139</v>
@@ -9437,16 +9449,16 @@
     </row>
     <row r="425" spans="1:7">
       <c r="A425" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B425" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C425" t="s">
-        <v>121</v>
+        <v>15</v>
       </c>
       <c r="D425" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E425" t="s">
         <v>140</v>
@@ -9454,249 +9466,252 @@
     </row>
     <row r="426" spans="1:7">
       <c r="A426" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B426" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C426" t="s">
+        <v>134</v>
+      </c>
+      <c r="D426" t="s">
+        <v>24</v>
+      </c>
+      <c r="E426" t="s">
         <v>15</v>
       </c>
-      <c r="D426" t="s">
-        <v>23</v>
-      </c>
-      <c r="E426" t="s">
+    </row>
+    <row r="428" spans="1:7">
+      <c r="A428" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="427" spans="1:7">
-      <c r="A427" s="1">
-        <v>7</v>
-      </c>
-      <c r="B427" t="s">
-        <v>8</v>
-      </c>
-      <c r="C427" t="s">
-        <v>135</v>
-      </c>
-      <c r="D427" t="s">
-        <v>24</v>
-      </c>
-      <c r="E427" t="s">
-        <v>15</v>
-      </c>
-    </row>
     <row r="429" spans="1:7">
-      <c r="A429" t="s">
-        <v>142</v>
+      <c r="B429" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C429" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D429" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E429" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F429" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G429" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="430" spans="1:7">
-      <c r="B430" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C430" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D430" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E430" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F430" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G430" s="1" t="s">
-        <v>39</v>
+      <c r="A430" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B430">
+        <v>-0.8</v>
+      </c>
+      <c r="C430">
+        <v>0.1</v>
+      </c>
+      <c r="D430">
+        <v>-7.4</v>
+      </c>
+      <c r="E430">
+        <v>0</v>
+      </c>
+      <c r="F430">
+        <v>-1</v>
+      </c>
+      <c r="G430">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="431" spans="1:7">
       <c r="A431" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B431">
-        <v>-0.8</v>
+        <v>-0.6</v>
       </c>
       <c r="C431">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D431">
-        <v>-7.4</v>
+        <v>-3.7</v>
       </c>
       <c r="E431">
         <v>0</v>
       </c>
       <c r="F431">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
       <c r="G431">
-        <v>-0.6</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="432" spans="1:7">
       <c r="A432" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B432">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="C432">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D432">
-        <v>-3.7</v>
+        <v>-3.5</v>
       </c>
       <c r="E432">
         <v>0</v>
       </c>
       <c r="F432">
-        <v>-0.9</v>
+        <v>-0.7</v>
       </c>
       <c r="G432">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="433" spans="1:7">
       <c r="A433" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B433">
-        <v>-0.5</v>
+        <v>-1.1</v>
       </c>
       <c r="C433">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D433">
-        <v>-3.5</v>
+        <v>-5.3</v>
       </c>
       <c r="E433">
         <v>0</v>
       </c>
       <c r="F433">
+        <v>-1.5</v>
+      </c>
+      <c r="G433">
         <v>-0.7</v>
-      </c>
-      <c r="G433">
-        <v>-0.2</v>
       </c>
     </row>
     <row r="434" spans="1:7">
       <c r="A434" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B434">
-        <v>-1.1</v>
+        <v>0.3</v>
       </c>
       <c r="C434">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D434">
-        <v>-5.3</v>
+        <v>2.5</v>
       </c>
       <c r="E434">
         <v>0</v>
       </c>
       <c r="F434">
-        <v>-1.5</v>
+        <v>0.1</v>
       </c>
       <c r="G434">
-        <v>-0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="435" spans="1:7">
       <c r="A435" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B435">
-        <v>0.3</v>
+        <v>-1.2</v>
       </c>
       <c r="C435">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D435">
-        <v>2.5</v>
+        <v>-5.7</v>
       </c>
       <c r="E435">
         <v>0</v>
       </c>
       <c r="F435">
-        <v>0.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G435">
-        <v>0.6</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="436" spans="1:7">
       <c r="A436" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B436">
-        <v>-1.2</v>
+        <v>0.6</v>
       </c>
       <c r="C436">
         <v>0.2</v>
       </c>
       <c r="D436">
-        <v>-5.7</v>
+        <v>2.9</v>
       </c>
       <c r="E436">
         <v>0</v>
       </c>
       <c r="F436">
-        <v>-1.6</v>
+        <v>0.2</v>
       </c>
       <c r="G436">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="437" spans="1:7">
-      <c r="A437" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B437">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7">
+      <c r="A438" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7">
+      <c r="B439" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C439" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D439" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E439" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F439" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7">
+      <c r="A440" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B440">
+        <v>0</v>
+      </c>
+      <c r="C440" t="s">
+        <v>69</v>
+      </c>
+      <c r="D440">
+        <v>0.5</v>
+      </c>
+      <c r="E440">
+        <v>0.4</v>
+      </c>
+      <c r="F440">
         <v>0.6</v>
-      </c>
-      <c r="C437">
-        <v>0.2</v>
-      </c>
-      <c r="D437">
-        <v>2.9</v>
-      </c>
-      <c r="E437">
-        <v>0</v>
-      </c>
-      <c r="F437">
-        <v>0.2</v>
-      </c>
-      <c r="G437">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="439" spans="1:7">
-      <c r="A439" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="440" spans="1:7">
-      <c r="B440" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C440" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D440" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E440" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F440" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="441" spans="1:7">
       <c r="A441" s="1" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B441">
         <v>0</v>
@@ -9705,18 +9720,18 @@
         <v>69</v>
       </c>
       <c r="D441">
+        <v>0.6</v>
+      </c>
+      <c r="E441">
         <v>0.5</v>
       </c>
-      <c r="E441">
-        <v>0.4</v>
-      </c>
       <c r="F441">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="442" spans="1:7">
       <c r="A442" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B442">
         <v>0</v>
@@ -9728,7 +9743,7 @@
         <v>0.6</v>
       </c>
       <c r="E442">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F442">
         <v>0.8</v>
@@ -9736,7 +9751,7 @@
     </row>
     <row r="443" spans="1:7">
       <c r="A443" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B443">
         <v>0</v>
@@ -9745,18 +9760,18 @@
         <v>69</v>
       </c>
       <c r="D443">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E443">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F443">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="444" spans="1:7">
       <c r="A444" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B444">
         <v>0</v>
@@ -9765,18 +9780,18 @@
         <v>69</v>
       </c>
       <c r="D444">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="E444">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="F444">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="445" spans="1:7">
       <c r="A445" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B445">
         <v>0</v>
@@ -9785,18 +9800,18 @@
         <v>69</v>
       </c>
       <c r="D445">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E445">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F445">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="446" spans="1:7">
       <c r="A446" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B446">
         <v>0</v>
@@ -9805,357 +9820,369 @@
         <v>69</v>
       </c>
       <c r="D446">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="E446">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="F446">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="447" spans="1:7">
-      <c r="A447" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B447">
-        <v>0</v>
-      </c>
-      <c r="C447" t="s">
-        <v>69</v>
-      </c>
-      <c r="D447">
-        <v>0.3</v>
-      </c>
-      <c r="E447">
-        <v>0.2</v>
-      </c>
-      <c r="F447">
         <v>0.5</v>
       </c>
     </row>
     <row r="448" spans="1:7">
-      <c r="A448" s="1" t="s">
-        <v>54</v>
+      <c r="A448" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7">
+      <c r="B449" s="1">
+        <v>0</v>
+      </c>
+      <c r="C449" s="1">
+        <v>1</v>
+      </c>
+      <c r="D449" s="1">
+        <v>2</v>
+      </c>
+      <c r="E449" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="450" spans="1:7">
-      <c r="A450" t="s">
+      <c r="A450" s="1">
+        <v>0</v>
+      </c>
+      <c r="B450" t="s">
+        <v>1</v>
+      </c>
+      <c r="C450" t="s">
+        <v>117</v>
+      </c>
+      <c r="D450" t="s">
+        <v>17</v>
+      </c>
+      <c r="E450" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7">
+      <c r="A451" s="1">
+        <v>1</v>
+      </c>
+      <c r="B451" t="s">
+        <v>2</v>
+      </c>
+      <c r="C451" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="451" spans="1:7">
-      <c r="B451" s="1">
-        <v>0</v>
-      </c>
-      <c r="C451" s="1">
-        <v>1</v>
-      </c>
-      <c r="D451" s="1">
-        <v>2</v>
-      </c>
-      <c r="E451" s="1">
-        <v>3</v>
+      <c r="D451" t="s">
+        <v>18</v>
+      </c>
+      <c r="E451" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="452" spans="1:7">
       <c r="A452" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B452" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C452" t="s">
-        <v>117</v>
+        <v>11</v>
       </c>
       <c r="D452" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E452" t="s">
-        <v>25</v>
+        <v>149</v>
       </c>
     </row>
     <row r="453" spans="1:7">
       <c r="A453" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B453" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C453" t="s">
         <v>145</v>
       </c>
       <c r="D453" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E453" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="454" spans="1:7">
       <c r="A454" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B454" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C454" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="D454" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E454" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="455" spans="1:7">
       <c r="A455" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B455" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C455" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D455" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E455" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="456" spans="1:7">
       <c r="A456" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B456" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C456" t="s">
-        <v>147</v>
+        <v>15</v>
       </c>
       <c r="D456" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E456" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="457" spans="1:7">
       <c r="A457" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B457" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C457" t="s">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="D457" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E457" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="458" spans="1:7">
-      <c r="A458" s="1">
-        <v>6</v>
-      </c>
-      <c r="B458" t="s">
-        <v>7</v>
-      </c>
-      <c r="C458" t="s">
         <v>15</v>
       </c>
-      <c r="D458" t="s">
-        <v>23</v>
-      </c>
-      <c r="E458" t="s">
+    </row>
+    <row r="459" spans="1:7">
+      <c r="A459" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="459" spans="1:7">
-      <c r="A459" s="1">
-        <v>7</v>
-      </c>
-      <c r="B459" t="s">
-        <v>8</v>
-      </c>
-      <c r="C459" t="s">
-        <v>81</v>
-      </c>
-      <c r="D459" t="s">
-        <v>24</v>
-      </c>
-      <c r="E459" t="s">
-        <v>15</v>
+    <row r="460" spans="1:7">
+      <c r="B460" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C460" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D460" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E460" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F460" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G460" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="461" spans="1:7">
-      <c r="A461" t="s">
+      <c r="A461" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B461">
+        <v>-5.4</v>
+      </c>
+      <c r="C461">
+        <v>0.6</v>
+      </c>
+      <c r="D461">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="E461">
+        <v>0</v>
+      </c>
+      <c r="F461">
+        <v>-6.7</v>
+      </c>
+      <c r="G461">
+        <v>-4.1</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7">
+      <c r="A462" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="462" spans="1:7">
-      <c r="B462" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C462" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D462" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E462" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F462" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G462" s="1" t="s">
-        <v>39</v>
+      <c r="B462">
+        <v>2.4</v>
+      </c>
+      <c r="C462">
+        <v>0.7</v>
+      </c>
+      <c r="D462">
+        <v>3.4</v>
+      </c>
+      <c r="E462">
+        <v>0</v>
+      </c>
+      <c r="F462">
+        <v>1</v>
+      </c>
+      <c r="G462">
+        <v>3.8</v>
       </c>
     </row>
     <row r="463" spans="1:7">
       <c r="A463" s="1" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B463">
-        <v>-5.4</v>
+        <v>2.7</v>
       </c>
       <c r="C463">
         <v>0.6</v>
       </c>
       <c r="D463">
-        <v>-8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="E463">
         <v>0</v>
       </c>
       <c r="F463">
-        <v>-6.7</v>
+        <v>1.4</v>
       </c>
       <c r="G463">
-        <v>-4.1</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="464" spans="1:7">
       <c r="A464" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B464">
+        <v>1.1</v>
+      </c>
+      <c r="C464">
+        <v>0.6</v>
+      </c>
+      <c r="D464">
+        <v>1.9</v>
+      </c>
+      <c r="E464">
+        <v>0.1</v>
+      </c>
+      <c r="F464">
+        <v>-0</v>
+      </c>
+      <c r="G464">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="466" spans="1:6">
+      <c r="A466" t="s">
         <v>156</v>
       </c>
-      <c r="B464">
-        <v>2.4</v>
-      </c>
-      <c r="C464">
-        <v>0.7</v>
-      </c>
-      <c r="D464">
-        <v>3.4</v>
-      </c>
-      <c r="E464">
-        <v>0</v>
-      </c>
-      <c r="F464">
+    </row>
+    <row r="467" spans="1:6">
+      <c r="B467" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C467" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D467" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E467" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F467" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="468" spans="1:6">
+      <c r="A468" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B468">
+        <v>0</v>
+      </c>
+      <c r="C468" t="s">
+        <v>69</v>
+      </c>
+      <c r="D468">
+        <v>0</v>
+      </c>
+      <c r="E468">
+        <v>0</v>
+      </c>
+      <c r="F468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:6">
+      <c r="A469" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B469">
+        <v>0</v>
+      </c>
+      <c r="C469" t="s">
+        <v>69</v>
+      </c>
+      <c r="D469">
+        <v>11</v>
+      </c>
+      <c r="E469">
+        <v>2.8</v>
+      </c>
+      <c r="F469">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="470" spans="1:6">
+      <c r="A470" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B470">
+        <v>0.1</v>
+      </c>
+      <c r="D470">
+        <v>3</v>
+      </c>
+      <c r="E470">
         <v>1</v>
       </c>
-      <c r="G464">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="465" spans="1:7">
-      <c r="A465" s="1" t="s">
+      <c r="F470">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="471" spans="1:6">
+      <c r="A471" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="B465">
-        <v>2.7</v>
-      </c>
-      <c r="C465">
-        <v>0.6</v>
-      </c>
-      <c r="D465">
-        <v>4.2</v>
-      </c>
-      <c r="E465">
-        <v>0</v>
-      </c>
-      <c r="F465">
-        <v>1.4</v>
-      </c>
-      <c r="G465">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="466" spans="1:7">
-      <c r="A466" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B466">
-        <v>1.1</v>
-      </c>
-      <c r="C466">
-        <v>0.6</v>
-      </c>
-      <c r="D466">
-        <v>1.9</v>
-      </c>
-      <c r="E466">
-        <v>0.1</v>
-      </c>
-      <c r="F466">
-        <v>-0</v>
-      </c>
-      <c r="G466">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="468" spans="1:7">
-      <c r="A468" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="469" spans="1:7">
-      <c r="B469" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C469" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D469" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E469" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F469" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="470" spans="1:7">
-      <c r="A470" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B470">
-        <v>0</v>
-      </c>
-      <c r="C470" t="s">
-        <v>69</v>
-      </c>
-      <c r="D470">
-        <v>0</v>
-      </c>
-      <c r="E470">
-        <v>0</v>
-      </c>
-      <c r="F470">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="471" spans="1:7">
-      <c r="A471" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="B471">
         <v>0</v>
@@ -10164,330 +10191,366 @@
         <v>69</v>
       </c>
       <c r="D471">
-        <v>11</v>
+        <v>14.4</v>
       </c>
       <c r="E471">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="F471">
-        <v>43.4</v>
-      </c>
-    </row>
-    <row r="472" spans="1:7">
-      <c r="A472" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B472">
-        <v>0.1</v>
-      </c>
-      <c r="D472">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="473" spans="1:6">
+      <c r="A473" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="474" spans="1:6">
+      <c r="B474" s="1">
+        <v>0</v>
+      </c>
+      <c r="C474" s="1">
+        <v>1</v>
+      </c>
+      <c r="D474" s="1">
+        <v>2</v>
+      </c>
+      <c r="E474" s="1">
         <v>3</v>
       </c>
-      <c r="E472">
+    </row>
+    <row r="475" spans="1:6">
+      <c r="A475" s="1">
+        <v>0</v>
+      </c>
+      <c r="B475" t="s">
         <v>1</v>
       </c>
-      <c r="F472">
-        <v>9.1</v>
-      </c>
-    </row>
-    <row r="473" spans="1:7">
-      <c r="A473" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="474" spans="1:7">
-      <c r="A474" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B474">
-        <v>0</v>
-      </c>
-      <c r="C474" t="s">
-        <v>69</v>
-      </c>
-      <c r="D474">
-        <v>14.4</v>
-      </c>
-      <c r="E474">
-        <v>4.1</v>
-      </c>
-      <c r="F474">
-        <v>50.6</v>
-      </c>
-    </row>
-    <row r="476" spans="1:7">
-      <c r="A476" t="s">
+      <c r="C475" t="s">
+        <v>9</v>
+      </c>
+      <c r="D475" t="s">
+        <v>17</v>
+      </c>
+      <c r="E475" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="476" spans="1:6">
+      <c r="A476" s="1">
+        <v>1</v>
+      </c>
+      <c r="B476" t="s">
+        <v>2</v>
+      </c>
+      <c r="C476" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="477" spans="1:7">
-      <c r="B477" s="1">
-        <v>0</v>
-      </c>
-      <c r="C477" s="1">
-        <v>1</v>
-      </c>
-      <c r="D477" s="1">
+      <c r="D476" t="s">
+        <v>18</v>
+      </c>
+      <c r="E476" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="477" spans="1:6">
+      <c r="A477" s="1">
         <v>2</v>
       </c>
-      <c r="E477" s="1">
+      <c r="B477" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="478" spans="1:7">
+      <c r="C477" t="s">
+        <v>159</v>
+      </c>
+      <c r="D477" t="s">
+        <v>19</v>
+      </c>
+      <c r="E477" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="478" spans="1:6">
       <c r="A478" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B478" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C478" t="s">
-        <v>9</v>
+        <v>160</v>
       </c>
       <c r="D478" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E478" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="479" spans="1:7">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="479" spans="1:6">
       <c r="A479" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B479" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C479" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D479" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E479" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="480" spans="1:7">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="480" spans="1:6">
       <c r="A480" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B480" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C480" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="D480" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E480" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="481" spans="1:8">
       <c r="A481" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B481" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C481" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="D481" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E481" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="482" spans="1:8">
       <c r="A482" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B482" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C482" t="s">
-        <v>161</v>
+        <v>16</v>
       </c>
       <c r="D482" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E482" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="483" spans="1:8">
-      <c r="A483" s="1">
-        <v>5</v>
-      </c>
-      <c r="B483" t="s">
-        <v>6</v>
-      </c>
-      <c r="C483" t="s">
-        <v>162</v>
-      </c>
-      <c r="D483" t="s">
-        <v>22</v>
-      </c>
-      <c r="E483" t="s">
-        <v>167</v>
+        <v>15</v>
       </c>
     </row>
     <row r="484" spans="1:8">
-      <c r="A484" s="1">
-        <v>6</v>
-      </c>
-      <c r="B484" t="s">
-        <v>7</v>
-      </c>
-      <c r="C484" t="s">
-        <v>15</v>
-      </c>
-      <c r="D484" t="s">
-        <v>23</v>
-      </c>
-      <c r="E484" t="s">
-        <v>168</v>
+      <c r="A484" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="485" spans="1:8">
-      <c r="A485" s="1">
-        <v>7</v>
-      </c>
-      <c r="B485" t="s">
-        <v>8</v>
-      </c>
-      <c r="C485" t="s">
-        <v>16</v>
-      </c>
-      <c r="D485" t="s">
-        <v>24</v>
-      </c>
-      <c r="E485" t="s">
-        <v>15</v>
+      <c r="B485" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C485" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D485" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E485" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F485" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G485" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H485" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="486" spans="1:8">
+      <c r="A486" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B486" t="s">
+        <v>40</v>
+      </c>
+      <c r="C486">
+        <v>0.2</v>
+      </c>
+      <c r="D486">
+        <v>0.1</v>
+      </c>
+      <c r="E486">
+        <v>1.3</v>
+      </c>
+      <c r="F486">
+        <v>0.2</v>
+      </c>
+      <c r="G486">
+        <v>-0.1</v>
+      </c>
+      <c r="H486">
+        <v>0.4</v>
       </c>
     </row>
     <row r="487" spans="1:8">
-      <c r="A487" t="s">
-        <v>169</v>
+      <c r="A487" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B487" t="s">
+        <v>46</v>
+      </c>
+      <c r="C487">
+        <v>0.2</v>
+      </c>
+      <c r="D487">
+        <v>0.1</v>
+      </c>
+      <c r="E487">
+        <v>1.5</v>
+      </c>
+      <c r="F487">
+        <v>0.1</v>
+      </c>
+      <c r="G487">
+        <v>-0.1</v>
+      </c>
+      <c r="H487">
+        <v>0.4</v>
       </c>
     </row>
     <row r="488" spans="1:8">
-      <c r="B488" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C488" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D488" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E488" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F488" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G488" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H488" s="1" t="s">
-        <v>39</v>
+      <c r="A488" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B488" t="s">
+        <v>48</v>
+      </c>
+      <c r="C488">
+        <v>0.2</v>
+      </c>
+      <c r="D488">
+        <v>0.2</v>
+      </c>
+      <c r="E488">
+        <v>1.2</v>
+      </c>
+      <c r="F488">
+        <v>0.2</v>
+      </c>
+      <c r="G488">
+        <v>-0.1</v>
+      </c>
+      <c r="H488">
+        <v>0.5</v>
       </c>
     </row>
     <row r="489" spans="1:8">
       <c r="A489" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B489" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C489">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="D489">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E489">
-        <v>1.3</v>
+        <v>-0.8</v>
       </c>
       <c r="F489">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G489">
-        <v>-0.1</v>
+        <v>-0.7</v>
       </c>
       <c r="H489">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="490" spans="1:8">
       <c r="A490" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B490" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C490">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="D490">
         <v>0.1</v>
       </c>
       <c r="E490">
-        <v>1.5</v>
+        <v>-0.6</v>
       </c>
       <c r="F490">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G490">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="H490">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="491" spans="1:8">
       <c r="A491" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B491" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C491">
-        <v>0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="D491">
         <v>0.2</v>
       </c>
       <c r="E491">
-        <v>1.2</v>
+        <v>-3.3</v>
       </c>
       <c r="F491">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G491">
-        <v>-0.1</v>
+        <v>-0.9</v>
       </c>
       <c r="H491">
-        <v>0.5</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="492" spans="1:8">
       <c r="A492" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B492" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C492">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="D492">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E492">
         <v>-0.8</v>
@@ -10496,33 +10559,33 @@
         <v>0.4</v>
       </c>
       <c r="G492">
-        <v>-0.7</v>
+        <v>-0.3</v>
       </c>
       <c r="H492">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="493" spans="1:8">
       <c r="A493" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B493" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C493">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D493">
         <v>0.1</v>
       </c>
       <c r="E493">
-        <v>-0.6</v>
+        <v>-1.4</v>
       </c>
       <c r="F493">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="G493">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="H493">
         <v>0.1</v>
@@ -10530,926 +10593,926 @@
     </row>
     <row r="494" spans="1:8">
       <c r="A494" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B494" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C494">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="D494">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E494">
-        <v>-3.3</v>
+        <v>-8.9</v>
       </c>
       <c r="F494">
         <v>0</v>
       </c>
       <c r="G494">
-        <v>-0.9</v>
+        <v>-1.2</v>
       </c>
       <c r="H494">
-        <v>-0.2</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="495" spans="1:8">
       <c r="A495" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B495" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C495">
         <v>-0.1</v>
       </c>
       <c r="D495">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E495">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="F495">
         <v>0.4</v>
       </c>
       <c r="G495">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="H495">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="496" spans="1:8">
       <c r="A496" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B496" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C496">
-        <v>-0.2</v>
+        <v>-1.1</v>
       </c>
       <c r="D496">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="E496">
-        <v>-1.4</v>
+        <v>-1.9</v>
       </c>
       <c r="F496">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G496">
-        <v>-0.4</v>
+        <v>-2.1</v>
       </c>
       <c r="H496">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="497" spans="1:8">
       <c r="A497" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B497" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C497">
+        <v>-0.6</v>
+      </c>
+      <c r="D497">
+        <v>0.2</v>
+      </c>
+      <c r="E497">
+        <v>-2.7</v>
+      </c>
+      <c r="F497">
+        <v>0</v>
+      </c>
+      <c r="G497">
         <v>-1</v>
       </c>
-      <c r="D497">
-        <v>0.1</v>
-      </c>
-      <c r="E497">
-        <v>-8.9</v>
-      </c>
-      <c r="F497">
-        <v>0</v>
-      </c>
-      <c r="G497">
-        <v>-1.2</v>
-      </c>
       <c r="H497">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="498" spans="1:8">
-      <c r="A498" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B498" t="s">
-        <v>55</v>
-      </c>
-      <c r="C498">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="499" spans="1:8">
+      <c r="A499" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="500" spans="1:8">
+      <c r="B500" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C500" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D500" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E500" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F500" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G500" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H500" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="501" spans="1:8">
+      <c r="A501" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B501" t="s">
+        <v>40</v>
+      </c>
+      <c r="C501">
+        <v>-1.6</v>
+      </c>
+      <c r="D501">
+        <v>0.1</v>
+      </c>
+      <c r="E501">
+        <v>-11.5</v>
+      </c>
+      <c r="F501">
+        <v>0</v>
+      </c>
+      <c r="G501">
+        <v>-1.9</v>
+      </c>
+      <c r="H501">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="502" spans="1:8">
+      <c r="A502" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B502" t="s">
+        <v>46</v>
+      </c>
+      <c r="C502">
+        <v>-0.2</v>
+      </c>
+      <c r="D502">
+        <v>0.1</v>
+      </c>
+      <c r="E502">
+        <v>-1.7</v>
+      </c>
+      <c r="F502">
+        <v>0.1</v>
+      </c>
+      <c r="G502">
+        <v>-0.4</v>
+      </c>
+      <c r="H502">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503" spans="1:8">
+      <c r="A503" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B503" t="s">
+        <v>48</v>
+      </c>
+      <c r="C503">
+        <v>-0.5</v>
+      </c>
+      <c r="D503">
+        <v>0.2</v>
+      </c>
+      <c r="E503">
+        <v>-2.3</v>
+      </c>
+      <c r="F503">
+        <v>0</v>
+      </c>
+      <c r="G503">
+        <v>-1</v>
+      </c>
+      <c r="H503">
         <v>-0.1</v>
-      </c>
-      <c r="D498">
-        <v>0.2</v>
-      </c>
-      <c r="E498">
-        <v>-0.9</v>
-      </c>
-      <c r="F498">
-        <v>0.4</v>
-      </c>
-      <c r="G498">
-        <v>-0.5</v>
-      </c>
-      <c r="H498">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="499" spans="1:8">
-      <c r="A499" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B499" t="s">
-        <v>56</v>
-      </c>
-      <c r="C499">
-        <v>-1.1</v>
-      </c>
-      <c r="D499">
-        <v>0.5</v>
-      </c>
-      <c r="E499">
-        <v>-1.9</v>
-      </c>
-      <c r="F499">
-        <v>0.1</v>
-      </c>
-      <c r="G499">
-        <v>-2.1</v>
-      </c>
-      <c r="H499">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="500" spans="1:8">
-      <c r="A500" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B500" t="s">
-        <v>58</v>
-      </c>
-      <c r="C500">
-        <v>-0.6</v>
-      </c>
-      <c r="D500">
-        <v>0.2</v>
-      </c>
-      <c r="E500">
-        <v>-2.7</v>
-      </c>
-      <c r="F500">
-        <v>0</v>
-      </c>
-      <c r="G500">
-        <v>-1</v>
-      </c>
-      <c r="H500">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="502" spans="1:8">
-      <c r="A502" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="503" spans="1:8">
-      <c r="B503" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C503" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D503" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E503" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F503" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G503" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H503" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="504" spans="1:8">
       <c r="A504" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B504" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C504">
-        <v>-1.6</v>
+        <v>-0.2</v>
       </c>
       <c r="D504">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E504">
-        <v>-11.5</v>
+        <v>-0.8</v>
       </c>
       <c r="F504">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G504">
-        <v>-1.9</v>
+        <v>-0.8</v>
       </c>
       <c r="H504">
-        <v>-1.3</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="505" spans="1:8">
       <c r="A505" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B505" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C505">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D505">
         <v>0.1</v>
       </c>
       <c r="E505">
-        <v>-1.7</v>
+        <v>3.9</v>
       </c>
       <c r="F505">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G505">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H505">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="506" spans="1:8">
       <c r="A506" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B506" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C506">
-        <v>-0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D506">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E506">
-        <v>-2.3</v>
+        <v>5.2</v>
       </c>
       <c r="F506">
         <v>0</v>
       </c>
       <c r="G506">
-        <v>-1</v>
+        <v>0.4</v>
       </c>
       <c r="H506">
-        <v>-0.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="507" spans="1:8">
       <c r="A507" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B507" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C507">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="D507">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E507">
-        <v>-0.8</v>
+        <v>1.9</v>
       </c>
       <c r="F507">
+        <v>0.1</v>
+      </c>
+      <c r="G507">
+        <v>-0</v>
+      </c>
+      <c r="H507">
         <v>0.4</v>
-      </c>
-      <c r="G507">
-        <v>-0.8</v>
-      </c>
-      <c r="H507">
-        <v>0.3</v>
       </c>
     </row>
     <row r="508" spans="1:8">
       <c r="A508" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B508" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C508">
+        <v>0</v>
+      </c>
+      <c r="D508">
+        <v>0.1</v>
+      </c>
+      <c r="E508">
         <v>0.4</v>
       </c>
-      <c r="D508">
-        <v>0.1</v>
-      </c>
-      <c r="E508">
-        <v>3.9</v>
-      </c>
       <c r="F508">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G508">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="H508">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="509" spans="1:8">
       <c r="A509" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B509" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C509">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="D509">
         <v>0.1</v>
       </c>
       <c r="E509">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="F509">
         <v>0</v>
       </c>
       <c r="G509">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="H509">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="510" spans="1:8">
       <c r="A510" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B510" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C510">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="D510">
         <v>0.1</v>
       </c>
       <c r="E510">
-        <v>1.9</v>
+        <v>6.7</v>
       </c>
       <c r="F510">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G510">
-        <v>-0</v>
+        <v>0.5</v>
       </c>
       <c r="H510">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="511" spans="1:8">
       <c r="A511" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B511" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C511">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D511">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E511">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="F511">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="G511">
         <v>-0.2</v>
       </c>
       <c r="H511">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="512" spans="1:8">
       <c r="A512" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B512" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C512">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="D512">
         <v>0.1</v>
       </c>
       <c r="E512">
-        <v>10.5</v>
+        <v>0.4</v>
       </c>
       <c r="F512">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G512">
-        <v>1</v>
+        <v>-0.2</v>
       </c>
       <c r="H512">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="513" spans="1:8">
-      <c r="A513" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B513" t="s">
-        <v>55</v>
-      </c>
-      <c r="C513">
-        <v>0.8</v>
-      </c>
-      <c r="D513">
-        <v>0.1</v>
-      </c>
-      <c r="E513">
-        <v>6.7</v>
-      </c>
-      <c r="F513">
-        <v>0</v>
-      </c>
-      <c r="G513">
-        <v>0.5</v>
-      </c>
-      <c r="H513">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="514" spans="1:8">
-      <c r="A514" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B514" t="s">
-        <v>56</v>
-      </c>
-      <c r="C514">
+      <c r="A514" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="515" spans="1:8">
+      <c r="B515" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C515" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D515" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E515" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F515" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G515" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H515" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="516" spans="1:8">
+      <c r="A516" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B516" t="s">
+        <v>40</v>
+      </c>
+      <c r="C516">
+        <v>-1.3</v>
+      </c>
+      <c r="D516">
+        <v>0.1</v>
+      </c>
+      <c r="E516">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="F516">
+        <v>0</v>
+      </c>
+      <c r="G516">
+        <v>-1.6</v>
+      </c>
+      <c r="H516">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="517" spans="1:8">
+      <c r="A517" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B517" t="s">
+        <v>46</v>
+      </c>
+      <c r="C517">
+        <v>-0.1</v>
+      </c>
+      <c r="D517">
+        <v>0.1</v>
+      </c>
+      <c r="E517">
+        <v>-0.5</v>
+      </c>
+      <c r="F517">
+        <v>0.7</v>
+      </c>
+      <c r="G517">
+        <v>-0.3</v>
+      </c>
+      <c r="H517">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="518" spans="1:8">
+      <c r="A518" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B518" t="s">
+        <v>48</v>
+      </c>
+      <c r="C518">
+        <v>-0.8</v>
+      </c>
+      <c r="D518">
         <v>0.3</v>
       </c>
-      <c r="D514">
-        <v>0.3</v>
-      </c>
-      <c r="E514">
-        <v>1.2</v>
-      </c>
-      <c r="F514">
-        <v>0.2</v>
-      </c>
-      <c r="G514">
+      <c r="E518">
+        <v>-2.7</v>
+      </c>
+      <c r="F518">
+        <v>0</v>
+      </c>
+      <c r="G518">
+        <v>-1.3</v>
+      </c>
+      <c r="H518">
         <v>-0.2</v>
-      </c>
-      <c r="H514">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="515" spans="1:8">
-      <c r="A515" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B515" t="s">
-        <v>58</v>
-      </c>
-      <c r="C515">
-        <v>0.1</v>
-      </c>
-      <c r="D515">
-        <v>0.1</v>
-      </c>
-      <c r="E515">
-        <v>0.4</v>
-      </c>
-      <c r="F515">
-        <v>0.7</v>
-      </c>
-      <c r="G515">
-        <v>-0.2</v>
-      </c>
-      <c r="H515">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="517" spans="1:8">
-      <c r="A517" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="518" spans="1:8">
-      <c r="B518" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C518" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D518" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E518" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F518" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G518" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H518" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="519" spans="1:8">
       <c r="A519" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B519" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C519">
-        <v>-1.3</v>
+        <v>-0.1</v>
       </c>
       <c r="D519">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E519">
-        <v>-8.699999999999999</v>
+        <v>-0.2</v>
       </c>
       <c r="F519">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="G519">
-        <v>-1.6</v>
+        <v>-0.7</v>
       </c>
       <c r="H519">
-        <v>-1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="520" spans="1:8">
       <c r="A520" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B520" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C520">
+        <v>0.1</v>
+      </c>
+      <c r="D520">
+        <v>0.1</v>
+      </c>
+      <c r="E520">
+        <v>0.8</v>
+      </c>
+      <c r="F520">
+        <v>0.4</v>
+      </c>
+      <c r="G520">
         <v>-0.1</v>
       </c>
-      <c r="D520">
-        <v>0.1</v>
-      </c>
-      <c r="E520">
-        <v>-0.5</v>
-      </c>
-      <c r="F520">
-        <v>0.7</v>
-      </c>
-      <c r="G520">
-        <v>-0.3</v>
-      </c>
       <c r="H520">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="521" spans="1:8">
       <c r="A521" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B521" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C521">
-        <v>-0.8</v>
+        <v>0.7</v>
       </c>
       <c r="D521">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E521">
-        <v>-2.7</v>
+        <v>5.1</v>
       </c>
       <c r="F521">
         <v>0</v>
       </c>
       <c r="G521">
-        <v>-1.3</v>
+        <v>0.4</v>
       </c>
       <c r="H521">
-        <v>-0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="522" spans="1:8">
       <c r="A522" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B522" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C522">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D522">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E522">
-        <v>-0.2</v>
+        <v>-2</v>
       </c>
       <c r="F522">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G522">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="H522">
-        <v>0.6</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="523" spans="1:8">
       <c r="A523" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B523" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C523">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D523">
         <v>0.1</v>
       </c>
       <c r="E523">
-        <v>0.8</v>
+        <v>-1.3</v>
       </c>
       <c r="F523">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G523">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="H523">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="524" spans="1:8">
       <c r="A524" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B524" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C524">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="D524">
         <v>0.1</v>
       </c>
       <c r="E524">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="F524">
         <v>0</v>
       </c>
       <c r="G524">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H524">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="525" spans="1:8">
       <c r="A525" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B525" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C525">
-        <v>-0.2</v>
+        <v>1</v>
       </c>
       <c r="D525">
         <v>0.1</v>
       </c>
       <c r="E525">
-        <v>-2</v>
+        <v>7.6</v>
       </c>
       <c r="F525">
         <v>0</v>
       </c>
       <c r="G525">
-        <v>-0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H525">
-        <v>-0</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="526" spans="1:8">
       <c r="A526" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B526" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C526">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="D526">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E526">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
       <c r="F526">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G526">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="H526">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="527" spans="1:8">
       <c r="A527" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B527" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C527">
+        <v>-0.2</v>
+      </c>
+      <c r="D527">
+        <v>0.2</v>
+      </c>
+      <c r="E527">
+        <v>-1.2</v>
+      </c>
+      <c r="F527">
+        <v>0.2</v>
+      </c>
+      <c r="G527">
+        <v>-0.6</v>
+      </c>
+      <c r="H527">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="529" spans="1:8">
+      <c r="A529" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="530" spans="1:8">
+      <c r="B530" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C530" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D530" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E530" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F530" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G530" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H530" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="531" spans="1:8">
+      <c r="A531" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B531" t="s">
+        <v>40</v>
+      </c>
+      <c r="C531">
+        <v>-1.5</v>
+      </c>
+      <c r="D531">
+        <v>0.2</v>
+      </c>
+      <c r="E531">
+        <v>-10.1</v>
+      </c>
+      <c r="F531">
+        <v>0</v>
+      </c>
+      <c r="G531">
+        <v>-1.8</v>
+      </c>
+      <c r="H531">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="532" spans="1:8">
+      <c r="A532" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B532" t="s">
+        <v>46</v>
+      </c>
+      <c r="C532">
+        <v>0.1</v>
+      </c>
+      <c r="D532">
+        <v>0.1</v>
+      </c>
+      <c r="E532">
+        <v>1.2</v>
+      </c>
+      <c r="F532">
+        <v>0.2</v>
+      </c>
+      <c r="G532">
+        <v>-0.1</v>
+      </c>
+      <c r="H532">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="533" spans="1:8">
+      <c r="A533" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B533" t="s">
+        <v>48</v>
+      </c>
+      <c r="C533">
+        <v>0.1</v>
+      </c>
+      <c r="D533">
+        <v>0.2</v>
+      </c>
+      <c r="E533">
         <v>0.5</v>
       </c>
-      <c r="D527">
-        <v>0.1</v>
-      </c>
-      <c r="E527">
-        <v>4</v>
-      </c>
-      <c r="F527">
-        <v>0</v>
-      </c>
-      <c r="G527">
-        <v>0.3</v>
-      </c>
-      <c r="H527">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="528" spans="1:8">
-      <c r="A528" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B528" t="s">
-        <v>55</v>
-      </c>
-      <c r="C528">
-        <v>1</v>
-      </c>
-      <c r="D528">
-        <v>0.1</v>
-      </c>
-      <c r="E528">
-        <v>7.6</v>
-      </c>
-      <c r="F528">
-        <v>0</v>
-      </c>
-      <c r="G528">
-        <v>0.7</v>
-      </c>
-      <c r="H528">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="529" spans="1:8">
-      <c r="A529" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B529" t="s">
-        <v>56</v>
-      </c>
-      <c r="C529">
-        <v>0</v>
-      </c>
-      <c r="D529">
-        <v>0.3</v>
-      </c>
-      <c r="E529">
-        <v>0</v>
-      </c>
-      <c r="F529">
-        <v>1</v>
-      </c>
-      <c r="G529">
-        <v>-0.6</v>
-      </c>
-      <c r="H529">
+      <c r="F533">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="530" spans="1:8">
-      <c r="A530" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B530" t="s">
-        <v>58</v>
-      </c>
-      <c r="C530">
-        <v>-0.2</v>
-      </c>
-      <c r="D530">
-        <v>0.2</v>
-      </c>
-      <c r="E530">
-        <v>-1.2</v>
-      </c>
-      <c r="F530">
-        <v>0.2</v>
-      </c>
-      <c r="G530">
-        <v>-0.6</v>
-      </c>
-      <c r="H530">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="532" spans="1:8">
-      <c r="A532" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="533" spans="1:8">
-      <c r="B533" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C533" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D533" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E533" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F533" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G533" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H533" s="1" t="s">
-        <v>39</v>
+      <c r="G533">
+        <v>-0.3</v>
+      </c>
+      <c r="H533">
+        <v>0.5</v>
       </c>
     </row>
     <row r="534" spans="1:8">
       <c r="A534" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B534" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C534">
-        <v>-1.5</v>
+        <v>0.1</v>
       </c>
       <c r="D534">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E534">
-        <v>-10.1</v>
+        <v>0.4</v>
       </c>
       <c r="F534">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G534">
-        <v>-1.8</v>
+        <v>-0.5</v>
       </c>
       <c r="H534">
-        <v>-1.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="535" spans="1:8">
       <c r="A535" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B535" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C535">
         <v>0.1</v>
@@ -11458,39 +11521,39 @@
         <v>0.1</v>
       </c>
       <c r="E535">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="F535">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G535">
         <v>-0.1</v>
       </c>
       <c r="H535">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="536" spans="1:8">
       <c r="A536" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B536" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C536">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D536">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E536">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="F536">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="G536">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="H536">
         <v>0.5</v>
@@ -11498,36 +11561,36 @@
     </row>
     <row r="537" spans="1:8">
       <c r="A537" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B537" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C537">
         <v>0.1</v>
       </c>
       <c r="D537">
+        <v>0.1</v>
+      </c>
+      <c r="E537">
+        <v>0.5</v>
+      </c>
+      <c r="F537">
+        <v>0.6</v>
+      </c>
+      <c r="G537">
+        <v>-0.2</v>
+      </c>
+      <c r="H537">
         <v>0.3</v>
-      </c>
-      <c r="E537">
-        <v>0.4</v>
-      </c>
-      <c r="F537">
-        <v>0.7</v>
-      </c>
-      <c r="G537">
-        <v>-0.5</v>
-      </c>
-      <c r="H537">
-        <v>0.7</v>
       </c>
     </row>
     <row r="538" spans="1:8">
       <c r="A538" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B538" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C538">
         <v>0.1</v>
@@ -11536,13 +11599,13 @@
         <v>0.1</v>
       </c>
       <c r="E538">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F538">
         <v>0.5</v>
       </c>
       <c r="G538">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="H538">
         <v>0.3</v>
@@ -11550,36 +11613,36 @@
     </row>
     <row r="539" spans="1:8">
       <c r="A539" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B539" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C539">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="D539">
         <v>0.1</v>
       </c>
       <c r="E539">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="F539">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G539">
-        <v>-0.1</v>
+        <v>0.5</v>
       </c>
       <c r="H539">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="540" spans="1:8">
       <c r="A540" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B540" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C540">
         <v>0.1</v>
@@ -11588,615 +11651,615 @@
         <v>0.1</v>
       </c>
       <c r="E540">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F540">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G540">
         <v>-0.2</v>
       </c>
       <c r="H540">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="541" spans="1:8">
       <c r="A541" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B541" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C541">
         <v>0.1</v>
       </c>
       <c r="D541">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E541">
+        <v>0.5</v>
+      </c>
+      <c r="F541">
         <v>0.6</v>
       </c>
-      <c r="F541">
-        <v>0.5</v>
-      </c>
       <c r="G541">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="H541">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="542" spans="1:8">
       <c r="A542" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B542" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C542">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="D542">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E542">
-        <v>5.9</v>
+        <v>1.4</v>
       </c>
       <c r="F542">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G542">
-        <v>0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="H542">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="544" spans="1:8">
+      <c r="A544" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="545" spans="1:8">
+      <c r="B545" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C545" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D545" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E545" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F545" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G545" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H545" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="546" spans="1:8">
+      <c r="A546" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B546" t="s">
+        <v>40</v>
+      </c>
+      <c r="C546">
+        <v>-1.3</v>
+      </c>
+      <c r="D546">
+        <v>0.2</v>
+      </c>
+      <c r="E546">
+        <v>-8.6</v>
+      </c>
+      <c r="F546">
+        <v>0</v>
+      </c>
+      <c r="G546">
+        <v>-1.6</v>
+      </c>
+      <c r="H546">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="547" spans="1:8">
+      <c r="A547" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B547" t="s">
+        <v>46</v>
+      </c>
+      <c r="C547">
+        <v>-0</v>
+      </c>
+      <c r="D547">
+        <v>0.1</v>
+      </c>
+      <c r="E547">
+        <v>-0</v>
+      </c>
+      <c r="F547">
         <v>1</v>
       </c>
-    </row>
-    <row r="543" spans="1:8">
-      <c r="A543" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B543" t="s">
-        <v>55</v>
-      </c>
-      <c r="C543">
-        <v>0.1</v>
-      </c>
-      <c r="D543">
-        <v>0.1</v>
-      </c>
-      <c r="E543">
-        <v>0.8</v>
-      </c>
-      <c r="F543">
-        <v>0.4</v>
-      </c>
-      <c r="G543">
-        <v>-0.2</v>
-      </c>
-      <c r="H543">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="544" spans="1:8">
-      <c r="A544" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B544" t="s">
-        <v>56</v>
-      </c>
-      <c r="C544">
-        <v>0.1</v>
-      </c>
-      <c r="D544">
+      <c r="G547">
+        <v>-0.3</v>
+      </c>
+      <c r="H547">
         <v>0.3</v>
       </c>
-      <c r="E544">
-        <v>0.5</v>
-      </c>
-      <c r="F544">
-        <v>0.6</v>
-      </c>
-      <c r="G544">
-        <v>-0.4</v>
-      </c>
-      <c r="H544">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="545" spans="1:8">
-      <c r="A545" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B545" t="s">
-        <v>58</v>
-      </c>
-      <c r="C545">
-        <v>0.2</v>
-      </c>
-      <c r="D545">
-        <v>0.2</v>
-      </c>
-      <c r="E545">
-        <v>1.4</v>
-      </c>
-      <c r="F545">
-        <v>0.2</v>
-      </c>
-      <c r="G545">
-        <v>-0.1</v>
-      </c>
-      <c r="H545">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="547" spans="1:8">
-      <c r="A547" t="s">
-        <v>177</v>
-      </c>
     </row>
     <row r="548" spans="1:8">
-      <c r="B548" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C548" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D548" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E548" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F548" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G548" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H548" s="1" t="s">
-        <v>39</v>
+      <c r="A548" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B548" t="s">
+        <v>48</v>
+      </c>
+      <c r="C548">
+        <v>-0.5</v>
+      </c>
+      <c r="D548">
+        <v>0.3</v>
+      </c>
+      <c r="E548">
+        <v>-1.8</v>
+      </c>
+      <c r="F548">
+        <v>0.1</v>
+      </c>
+      <c r="G548">
+        <v>-1</v>
+      </c>
+      <c r="H548">
+        <v>0</v>
       </c>
     </row>
     <row r="549" spans="1:8">
       <c r="A549" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B549" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C549">
-        <v>-1.3</v>
+        <v>-0.2</v>
       </c>
       <c r="D549">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E549">
-        <v>-8.6</v>
+        <v>-0.6</v>
       </c>
       <c r="F549">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="G549">
-        <v>-1.6</v>
+        <v>-0.9</v>
       </c>
       <c r="H549">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="550" spans="1:8">
       <c r="A550" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B550" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C550">
-        <v>-0</v>
+        <v>0.3</v>
       </c>
       <c r="D550">
         <v>0.1</v>
       </c>
       <c r="E550">
-        <v>-0</v>
+        <v>2.4</v>
       </c>
       <c r="F550">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G550">
-        <v>-0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H550">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="551" spans="1:8">
       <c r="A551" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B551" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C551">
-        <v>-0.5</v>
+        <v>0.7</v>
       </c>
       <c r="D551">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E551">
-        <v>-1.8</v>
+        <v>4.8</v>
       </c>
       <c r="F551">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G551">
-        <v>-1</v>
+        <v>0.4</v>
       </c>
       <c r="H551">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="552" spans="1:8">
       <c r="A552" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B552" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C552">
+        <v>0</v>
+      </c>
+      <c r="D552">
+        <v>0.1</v>
+      </c>
+      <c r="E552">
+        <v>0.2</v>
+      </c>
+      <c r="F552">
+        <v>0.9</v>
+      </c>
+      <c r="G552">
         <v>-0.2</v>
       </c>
-      <c r="D552">
+      <c r="H552">
         <v>0.3</v>
-      </c>
-      <c r="E552">
-        <v>-0.6</v>
-      </c>
-      <c r="F552">
-        <v>0.6</v>
-      </c>
-      <c r="G552">
-        <v>-0.9</v>
-      </c>
-      <c r="H552">
-        <v>0.5</v>
       </c>
     </row>
     <row r="553" spans="1:8">
       <c r="A553" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B553" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C553">
-        <v>0.3</v>
+        <v>-0</v>
       </c>
       <c r="D553">
         <v>0.1</v>
       </c>
       <c r="E553">
-        <v>2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="F553">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="G553">
-        <v>0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="H553">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="554" spans="1:8">
       <c r="A554" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B554" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C554">
-        <v>0.7</v>
+        <v>-0</v>
       </c>
       <c r="D554">
         <v>0.1</v>
       </c>
       <c r="E554">
-        <v>4.8</v>
+        <v>-0.1</v>
       </c>
       <c r="F554">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="G554">
-        <v>0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="H554">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="555" spans="1:8">
       <c r="A555" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B555" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C555">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D555">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E555">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="F555">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="G555">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H555">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="556" spans="1:8">
       <c r="A556" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B556" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C556">
-        <v>-0</v>
+        <v>-0.4</v>
       </c>
       <c r="D556">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="E556">
-        <v>-0.2</v>
+        <v>-1.1</v>
       </c>
       <c r="F556">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="G556">
-        <v>-0.3</v>
+        <v>-1.2</v>
       </c>
       <c r="H556">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="557" spans="1:8">
       <c r="A557" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B557" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C557">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D557">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E557">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="F557">
         <v>0.9</v>
       </c>
       <c r="G557">
+        <v>-0.4</v>
+      </c>
+      <c r="H557">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="559" spans="1:8">
+      <c r="A559" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="560" spans="1:8">
+      <c r="B560" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C560" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D560" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E560" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F560" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G560" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H560" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="561" spans="1:8">
+      <c r="A561" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B561" t="s">
+        <v>40</v>
+      </c>
+      <c r="C561">
+        <v>-3.7</v>
+      </c>
+      <c r="D561">
+        <v>0.4</v>
+      </c>
+      <c r="E561">
+        <v>-8.6</v>
+      </c>
+      <c r="F561">
+        <v>0</v>
+      </c>
+      <c r="G561">
+        <v>-4.5</v>
+      </c>
+      <c r="H561">
+        <v>-2.8</v>
+      </c>
+    </row>
+    <row r="562" spans="1:8">
+      <c r="A562" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B562" t="s">
+        <v>46</v>
+      </c>
+      <c r="C562">
+        <v>-1</v>
+      </c>
+      <c r="D562">
+        <v>0.4</v>
+      </c>
+      <c r="E562">
+        <v>-2.4</v>
+      </c>
+      <c r="F562">
+        <v>0</v>
+      </c>
+      <c r="G562">
+        <v>-1.8</v>
+      </c>
+      <c r="H562">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="563" spans="1:8">
+      <c r="A563" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B563" t="s">
+        <v>48</v>
+      </c>
+      <c r="C563">
+        <v>-0.2</v>
+      </c>
+      <c r="D563">
+        <v>0.6</v>
+      </c>
+      <c r="E563">
         <v>-0.3</v>
       </c>
-      <c r="H557">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="558" spans="1:8">
-      <c r="A558" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B558" t="s">
-        <v>55</v>
-      </c>
-      <c r="C558">
-        <v>0.4</v>
-      </c>
-      <c r="D558">
-        <v>0.2</v>
-      </c>
-      <c r="E558">
-        <v>2.6</v>
-      </c>
-      <c r="F558">
-        <v>0</v>
-      </c>
-      <c r="G558">
-        <v>0.1</v>
-      </c>
-      <c r="H558">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="559" spans="1:8">
-      <c r="A559" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B559" t="s">
-        <v>56</v>
-      </c>
-      <c r="C559">
-        <v>-0.4</v>
-      </c>
-      <c r="D559">
-        <v>0.4</v>
-      </c>
-      <c r="E559">
-        <v>-1.1</v>
-      </c>
-      <c r="F559">
-        <v>0.3</v>
-      </c>
-      <c r="G559">
-        <v>-1.2</v>
-      </c>
-      <c r="H559">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="560" spans="1:8">
-      <c r="A560" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B560" t="s">
-        <v>58</v>
-      </c>
-      <c r="C560">
-        <v>0</v>
-      </c>
-      <c r="D560">
-        <v>0.2</v>
-      </c>
-      <c r="E560">
-        <v>0.1</v>
-      </c>
-      <c r="F560">
-        <v>0.9</v>
-      </c>
-      <c r="G560">
-        <v>-0.4</v>
-      </c>
-      <c r="H560">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="562" spans="1:8">
-      <c r="A562" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="563" spans="1:8">
-      <c r="B563" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C563" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D563" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E563" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F563" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G563" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H563" s="1" t="s">
-        <v>39</v>
+      <c r="F563">
+        <v>0.8</v>
+      </c>
+      <c r="G563">
+        <v>-1.4</v>
+      </c>
+      <c r="H563">
+        <v>1</v>
       </c>
     </row>
     <row r="564" spans="1:8">
       <c r="A564" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B564" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C564">
-        <v>-3.7</v>
+        <v>-0.3</v>
       </c>
       <c r="D564">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E564">
-        <v>-8.6</v>
+        <v>-0.3</v>
       </c>
       <c r="F564">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G564">
-        <v>-4.5</v>
+        <v>-1.7</v>
       </c>
       <c r="H564">
-        <v>-2.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="565" spans="1:8">
       <c r="A565" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B565" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C565">
-        <v>-1</v>
+        <v>-0.6</v>
       </c>
       <c r="D565">
         <v>0.4</v>
       </c>
       <c r="E565">
-        <v>-2.4</v>
+        <v>-1.7</v>
       </c>
       <c r="F565">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G565">
-        <v>-1.8</v>
+        <v>-1.3</v>
       </c>
       <c r="H565">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="566" spans="1:8">
       <c r="A566" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B566" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C566">
-        <v>-0.2</v>
+        <v>-0</v>
       </c>
       <c r="D566">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E566">
-        <v>-0.3</v>
+        <v>-0</v>
       </c>
       <c r="F566">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G566">
-        <v>-1.4</v>
+        <v>-0.7</v>
       </c>
       <c r="H566">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="567" spans="1:8">
       <c r="A567" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B567" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C567">
-        <v>-0.3</v>
+        <v>0.7</v>
       </c>
       <c r="D567">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="E567">
-        <v>-0.3</v>
+        <v>2.6</v>
       </c>
       <c r="F567">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G567">
-        <v>-1.7</v>
+        <v>0.2</v>
       </c>
       <c r="H567">
         <v>1.2</v>
@@ -12204,16 +12267,16 @@
     </row>
     <row r="568" spans="1:8">
       <c r="A568" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B568" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C568">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="D568">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E568">
         <v>-1.7</v>
@@ -12222,7 +12285,7 @@
         <v>0.1</v>
       </c>
       <c r="G568">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="H568">
         <v>0.1</v>
@@ -12230,253 +12293,232 @@
     </row>
     <row r="569" spans="1:8">
       <c r="A569" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B569" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C569">
-        <v>-0</v>
+        <v>1.7</v>
       </c>
       <c r="D569">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E569">
-        <v>-0</v>
+        <v>4.4</v>
       </c>
       <c r="F569">
+        <v>0</v>
+      </c>
+      <c r="G569">
         <v>1</v>
       </c>
-      <c r="G569">
-        <v>-0.7</v>
-      </c>
       <c r="H569">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="570" spans="1:8">
       <c r="A570" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B570" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C570">
-        <v>0.7</v>
+        <v>-0.6</v>
       </c>
       <c r="D570">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E570">
-        <v>2.6</v>
+        <v>-1.4</v>
       </c>
       <c r="F570">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G570">
-        <v>0.2</v>
+        <v>-1.3</v>
       </c>
       <c r="H570">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="571" spans="1:8">
       <c r="A571" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B571" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C571">
-        <v>-0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D571">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E571">
-        <v>-1.7</v>
+        <v>0.7</v>
       </c>
       <c r="F571">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G571">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="H571">
-        <v>0.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="572" spans="1:8">
       <c r="A572" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B572" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C572">
-        <v>1.7</v>
+        <v>-0.3</v>
       </c>
       <c r="D572">
         <v>0.4</v>
       </c>
       <c r="E572">
-        <v>4.4</v>
+        <v>-0.6</v>
       </c>
       <c r="F572">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G572">
-        <v>1</v>
+        <v>-1.1</v>
       </c>
       <c r="H572">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="573" spans="1:8">
-      <c r="A573" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B573" t="s">
-        <v>55</v>
-      </c>
-      <c r="C573">
-        <v>-0.6</v>
-      </c>
-      <c r="D573">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="574" spans="1:8">
+      <c r="A574" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="575" spans="1:8">
+      <c r="C575" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D575" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E575" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F575" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G575" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="576" spans="1:8">
+      <c r="A576" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B576" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C576">
+        <v>0</v>
+      </c>
+      <c r="D576" t="s">
+        <v>69</v>
+      </c>
+      <c r="E576">
+        <v>0</v>
+      </c>
+      <c r="F576">
+        <v>0</v>
+      </c>
+      <c r="G576">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="577" spans="1:7">
+      <c r="A577" s="1"/>
+      <c r="B577" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C577">
+        <v>0.1</v>
+      </c>
+      <c r="E577">
+        <v>0.5</v>
+      </c>
+      <c r="F577">
+        <v>0.3</v>
+      </c>
+      <c r="G577">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="578" spans="1:7">
+      <c r="A578" s="1"/>
+      <c r="B578" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C578">
+        <v>0</v>
+      </c>
+      <c r="D578" t="s">
+        <v>69</v>
+      </c>
+      <c r="E578">
         <v>0.4</v>
       </c>
-      <c r="E573">
-        <v>-1.4</v>
-      </c>
-      <c r="F573">
-        <v>0.2</v>
-      </c>
-      <c r="G573">
-        <v>-1.3</v>
-      </c>
-      <c r="H573">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="574" spans="1:8">
-      <c r="A574" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B574" t="s">
-        <v>56</v>
-      </c>
-      <c r="C574">
+      <c r="F578">
+        <v>0.2</v>
+      </c>
+      <c r="G578">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="579" spans="1:7">
+      <c r="A579" s="1"/>
+      <c r="B579" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C579">
+        <v>0.1</v>
+      </c>
+      <c r="E579">
         <v>0.6</v>
       </c>
-      <c r="D574">
-        <v>0.8</v>
-      </c>
-      <c r="E574">
-        <v>0.7</v>
-      </c>
-      <c r="F574">
-        <v>0.5</v>
-      </c>
-      <c r="G574">
-        <v>-1.1</v>
-      </c>
-      <c r="H574">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="575" spans="1:8">
-      <c r="A575" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B575" t="s">
-        <v>58</v>
-      </c>
-      <c r="C575">
-        <v>-0.3</v>
-      </c>
-      <c r="D575">
+      <c r="F579">
         <v>0.4</v>
       </c>
-      <c r="E575">
-        <v>-0.6</v>
-      </c>
-      <c r="F575">
-        <v>0.5</v>
-      </c>
-      <c r="G575">
-        <v>-1.1</v>
-      </c>
-      <c r="H575">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="577" spans="1:7">
-      <c r="A577" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="578" spans="1:7">
-      <c r="C578" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D578" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E578" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F578" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G578" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="579" spans="1:7">
-      <c r="A579" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B579" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C579">
-        <v>0</v>
-      </c>
-      <c r="D579" t="s">
-        <v>69</v>
-      </c>
-      <c r="E579">
-        <v>0</v>
-      </c>
-      <c r="F579">
-        <v>0</v>
-      </c>
       <c r="G579">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="580" spans="1:7">
       <c r="A580" s="1"/>
       <c r="B580" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C580">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="E580">
+        <v>1</v>
+      </c>
+      <c r="F580">
         <v>0.5</v>
       </c>
-      <c r="F580">
-        <v>0.3</v>
-      </c>
       <c r="G580">
-        <v>1.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="581" spans="1:7">
       <c r="A581" s="1"/>
       <c r="B581" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C581">
         <v>0</v>
@@ -12485,300 +12527,300 @@
         <v>69</v>
       </c>
       <c r="E581">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="F581">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="G581">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="582" spans="1:7">
       <c r="A582" s="1"/>
       <c r="B582" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C582">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="E582">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F582">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G582">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="583" spans="1:7">
       <c r="A583" s="1"/>
       <c r="B583" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C583">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="E583">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F583">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G583">
-        <v>2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="584" spans="1:7">
       <c r="A584" s="1"/>
       <c r="B584" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C584">
-        <v>0</v>
-      </c>
-      <c r="D584" t="s">
-        <v>69</v>
+        <v>0.5</v>
       </c>
       <c r="E584">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="F584">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="G584">
-        <v>3.3</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="585" spans="1:7">
       <c r="A585" s="1"/>
       <c r="B585" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C585">
-        <v>0.5</v>
+        <v>0</v>
+      </c>
+      <c r="D585" t="s">
+        <v>69</v>
       </c>
       <c r="E585">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="F585">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="G585">
-        <v>1.8</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="586" spans="1:7">
       <c r="A586" s="1"/>
       <c r="B586" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C586">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="E586">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F586">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G586">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="587" spans="1:7">
       <c r="A587" s="1"/>
       <c r="B587" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C587">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E587">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="F587">
         <v>0.3</v>
       </c>
       <c r="G587">
-        <v>9.199999999999999</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="588" spans="1:7">
-      <c r="A588" s="1"/>
+      <c r="A588" s="1" t="s">
+        <v>182</v>
+      </c>
       <c r="B588" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C588">
-        <v>0</v>
-      </c>
-      <c r="D588" t="s">
-        <v>69</v>
+        <v>0.2</v>
       </c>
       <c r="E588">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="F588">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="G588">
-        <v>12.1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="589" spans="1:7">
       <c r="A589" s="1"/>
       <c r="B589" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C589">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E589">
+        <v>0.9</v>
+      </c>
+      <c r="F589">
         <v>0.8</v>
       </c>
-      <c r="F589">
-        <v>0.2</v>
-      </c>
       <c r="G589">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="590" spans="1:7">
       <c r="A590" s="1"/>
       <c r="B590" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C590">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="E590">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="F590">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="G590">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="591" spans="1:7">
-      <c r="A591" s="1" t="s">
-        <v>182</v>
-      </c>
+      <c r="A591" s="1"/>
       <c r="B591" s="1" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C591">
         <v>0.2</v>
       </c>
       <c r="E591">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="F591">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G591">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="592" spans="1:7">
       <c r="A592" s="1"/>
       <c r="B592" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C592">
-        <v>0.5</v>
+        <v>0</v>
+      </c>
+      <c r="D592" t="s">
+        <v>69</v>
       </c>
       <c r="E592">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="F592">
+        <v>0.4</v>
+      </c>
+      <c r="G592">
         <v>0.8</v>
-      </c>
-      <c r="G592">
-        <v>1.2</v>
       </c>
     </row>
     <row r="593" spans="1:7">
       <c r="A593" s="1"/>
       <c r="B593" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C593">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="E593">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="F593">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G593">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="594" spans="1:7">
       <c r="A594" s="1"/>
       <c r="B594" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C594">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="D594" t="s">
+        <v>69</v>
       </c>
       <c r="E594">
+        <v>0.6</v>
+      </c>
+      <c r="F594">
+        <v>0.4</v>
+      </c>
+      <c r="G594">
         <v>0.9</v>
-      </c>
-      <c r="F594">
-        <v>0.7</v>
-      </c>
-      <c r="G594">
-        <v>1.1</v>
       </c>
     </row>
     <row r="595" spans="1:7">
       <c r="A595" s="1"/>
       <c r="B595" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C595">
-        <v>0</v>
-      </c>
-      <c r="D595" t="s">
-        <v>69</v>
+        <v>0.4</v>
       </c>
       <c r="E595">
+        <v>0.9</v>
+      </c>
+      <c r="F595">
         <v>0.6</v>
       </c>
-      <c r="F595">
-        <v>0.4</v>
-      </c>
       <c r="G595">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="596" spans="1:7">
       <c r="A596" s="1"/>
       <c r="B596" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C596">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E596">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="F596">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="G596">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="597" spans="1:7">
       <c r="A597" s="1"/>
       <c r="B597" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C597">
         <v>0</v>
@@ -12787,55 +12829,57 @@
         <v>69</v>
       </c>
       <c r="E597">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F597">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G597">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="598" spans="1:7">
       <c r="A598" s="1"/>
       <c r="B598" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C598">
         <v>0.4</v>
       </c>
       <c r="E598">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F598">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G598">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="599" spans="1:7">
       <c r="A599" s="1"/>
       <c r="B599" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C599">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E599">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="F599">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="G599">
-        <v>1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="600" spans="1:7">
-      <c r="A600" s="1"/>
+      <c r="A600" s="1" t="s">
+        <v>183</v>
+      </c>
       <c r="B600" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C600">
         <v>0</v>
@@ -12844,78 +12888,76 @@
         <v>69</v>
       </c>
       <c r="E600">
+        <v>0.3</v>
+      </c>
+      <c r="F600">
+        <v>0.2</v>
+      </c>
+      <c r="G600">
         <v>0.4</v>
-      </c>
-      <c r="F600">
-        <v>0.3</v>
-      </c>
-      <c r="G600">
-        <v>0.5</v>
       </c>
     </row>
     <row r="601" spans="1:7">
       <c r="A601" s="1"/>
       <c r="B601" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C601">
-        <v>0.4</v>
+        <v>0</v>
+      </c>
+      <c r="D601" t="s">
+        <v>69</v>
       </c>
       <c r="E601">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="F601">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="G601">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="602" spans="1:7">
       <c r="A602" s="1"/>
       <c r="B602" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C602">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E602">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F602">
+        <v>0.8</v>
+      </c>
+      <c r="G602">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="603" spans="1:7">
+      <c r="A603" s="1"/>
+      <c r="B603" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C603">
         <v>0.9</v>
       </c>
-      <c r="G602">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="603" spans="1:7">
-      <c r="A603" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B603" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C603">
-        <v>0</v>
-      </c>
-      <c r="D603" t="s">
-        <v>69</v>
-      </c>
       <c r="E603">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="F603">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="G603">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="604" spans="1:7">
       <c r="A604" s="1"/>
       <c r="B604" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C604">
         <v>0</v>
@@ -12924,22 +12966,22 @@
         <v>69</v>
       </c>
       <c r="E604">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="F604">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="G604">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="605" spans="1:7">
       <c r="A605" s="1"/>
       <c r="B605" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C605">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E605">
         <v>1</v>
@@ -12954,7 +12996,7 @@
     <row r="606" spans="1:7">
       <c r="A606" s="1"/>
       <c r="B606" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C606">
         <v>0.9</v>
@@ -12966,13 +13008,13 @@
         <v>0.7</v>
       </c>
       <c r="G606">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="607" spans="1:7">
       <c r="A607" s="1"/>
       <c r="B607" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C607">
         <v>0</v>
@@ -12981,37 +13023,37 @@
         <v>69</v>
       </c>
       <c r="E607">
+        <v>1.5</v>
+      </c>
+      <c r="F607">
+        <v>1.1</v>
+      </c>
+      <c r="G607">
         <v>2</v>
-      </c>
-      <c r="F607">
-        <v>1.5</v>
-      </c>
-      <c r="G607">
-        <v>2.7</v>
       </c>
     </row>
     <row r="608" spans="1:7">
       <c r="A608" s="1"/>
       <c r="B608" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C608">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="E608">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F608">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="G608">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="609" spans="1:7">
       <c r="A609" s="1"/>
       <c r="B609" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C609">
         <v>0.9</v>
@@ -13020,204 +13062,201 @@
         <v>1</v>
       </c>
       <c r="F609">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G609">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="610" spans="1:7">
       <c r="A610" s="1"/>
       <c r="B610" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C610">
-        <v>0</v>
-      </c>
-      <c r="D610" t="s">
-        <v>69</v>
+        <v>0.6</v>
       </c>
       <c r="E610">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F610">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="G610">
-        <v>2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="611" spans="1:7">
       <c r="A611" s="1"/>
       <c r="B611" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C611">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E611">
         <v>0.6</v>
       </c>
       <c r="F611">
+        <v>0.4</v>
+      </c>
+      <c r="G611">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="612" spans="1:7">
+      <c r="A612" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B612" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C612">
+        <v>0</v>
+      </c>
+      <c r="D612" t="s">
+        <v>69</v>
+      </c>
+      <c r="E612">
+        <v>0.2</v>
+      </c>
+      <c r="F612">
+        <v>0.2</v>
+      </c>
+      <c r="G612">
         <v>0.3</v>
-      </c>
-      <c r="G611">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="612" spans="1:7">
-      <c r="A612" s="1"/>
-      <c r="B612" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C612">
-        <v>0.9</v>
-      </c>
-      <c r="E612">
-        <v>1</v>
-      </c>
-      <c r="F612">
-        <v>0.8</v>
-      </c>
-      <c r="G612">
-        <v>1.3</v>
       </c>
     </row>
     <row r="613" spans="1:7">
       <c r="A613" s="1"/>
       <c r="B613" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C613">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E613">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="F613">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="G613">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="614" spans="1:7">
       <c r="A614" s="1"/>
       <c r="B614" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C614">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E614">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="F614">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="G614">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="615" spans="1:7">
-      <c r="A615" s="1" t="s">
-        <v>184</v>
-      </c>
+      <c r="A615" s="1"/>
       <c r="B615" s="1" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C615">
-        <v>0</v>
-      </c>
-      <c r="D615" t="s">
-        <v>69</v>
+        <v>0.5</v>
       </c>
       <c r="E615">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="F615">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G615">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="616" spans="1:7">
       <c r="A616" s="1"/>
       <c r="B616" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C616">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E616">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F616">
         <v>0.9</v>
       </c>
       <c r="G616">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="617" spans="1:7">
       <c r="A617" s="1"/>
       <c r="B617" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C617">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E617">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="F617">
         <v>0.9</v>
       </c>
       <c r="G617">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="618" spans="1:7">
       <c r="A618" s="1"/>
       <c r="B618" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C618">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E618">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="F618">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G618">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="619" spans="1:7">
       <c r="A619" s="1"/>
       <c r="B619" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C619">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E619">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="F619">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G619">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="620" spans="1:7">
       <c r="A620" s="1"/>
       <c r="B620" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C620">
         <v>0.6</v>
@@ -13226,52 +13265,55 @@
         <v>1.1</v>
       </c>
       <c r="F620">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G620">
-        <v>1.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="621" spans="1:7">
       <c r="A621" s="1"/>
       <c r="B621" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C621">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="D621" t="s">
+        <v>69</v>
       </c>
       <c r="E621">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="F621">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="G621">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="622" spans="1:7">
       <c r="A622" s="1"/>
       <c r="B622" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C622">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E622">
         <v>1.1</v>
       </c>
       <c r="F622">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G622">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="623" spans="1:7">
       <c r="A623" s="1"/>
       <c r="B623" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C623">
         <v>0.6</v>
@@ -13283,13 +13325,15 @@
         <v>0.7</v>
       </c>
       <c r="G623">
-        <v>2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="624" spans="1:7">
-      <c r="A624" s="1"/>
+      <c r="A624" s="1" t="s">
+        <v>185</v>
+      </c>
       <c r="B624" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C624">
         <v>0</v>
@@ -13298,78 +13342,76 @@
         <v>69</v>
       </c>
       <c r="E624">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="F624">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="G624">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="625" spans="1:7">
       <c r="A625" s="1"/>
       <c r="B625" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C625">
-        <v>0.7</v>
+        <v>0</v>
+      </c>
+      <c r="D625" t="s">
+        <v>69</v>
       </c>
       <c r="E625">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="F625">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="G625">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="626" spans="1:7">
       <c r="A626" s="1"/>
       <c r="B626" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C626">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="E626">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="F626">
         <v>0.7</v>
       </c>
       <c r="G626">
-        <v>1.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="627" spans="1:7">
-      <c r="A627" s="1" t="s">
-        <v>185</v>
-      </c>
+      <c r="A627" s="1"/>
       <c r="B627" s="1" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C627">
-        <v>0</v>
-      </c>
-      <c r="D627" t="s">
-        <v>69</v>
+        <v>0.7</v>
       </c>
       <c r="E627">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F627">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G627">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="628" spans="1:7">
       <c r="A628" s="1"/>
       <c r="B628" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C628">
         <v>0</v>
@@ -13378,55 +13420,55 @@
         <v>69</v>
       </c>
       <c r="E628">
+        <v>1.8</v>
+      </c>
+      <c r="F628">
         <v>1.5</v>
       </c>
-      <c r="F628">
-        <v>1.2</v>
-      </c>
       <c r="G628">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="629" spans="1:7">
       <c r="A629" s="1"/>
       <c r="B629" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C629">
         <v>0.1</v>
       </c>
       <c r="E629">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="F629">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="G629">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="630" spans="1:7">
       <c r="A630" s="1"/>
       <c r="B630" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C630">
         <v>0.7</v>
       </c>
       <c r="E630">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F630">
         <v>0.8</v>
       </c>
       <c r="G630">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="631" spans="1:7">
       <c r="A631" s="1"/>
       <c r="B631" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C631">
         <v>0</v>
@@ -13435,94 +13477,99 @@
         <v>69</v>
       </c>
       <c r="E631">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="F631">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="G631">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="632" spans="1:7">
       <c r="A632" s="1"/>
       <c r="B632" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C632">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E632">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="F632">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G632">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="633" spans="1:7">
       <c r="A633" s="1"/>
       <c r="B633" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C633">
-        <v>0.7</v>
+        <v>0</v>
+      </c>
+      <c r="D633" t="s">
+        <v>69</v>
       </c>
       <c r="E633">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="F633">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="G633">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="634" spans="1:7">
       <c r="A634" s="1"/>
       <c r="B634" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C634">
-        <v>0</v>
-      </c>
-      <c r="D634" t="s">
-        <v>69</v>
+        <v>0.4</v>
       </c>
       <c r="E634">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="F634">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="G634">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="635" spans="1:7">
       <c r="A635" s="1"/>
       <c r="B635" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C635">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="D635" t="s">
+        <v>69</v>
       </c>
       <c r="E635">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="F635">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G635">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="636" spans="1:7">
-      <c r="A636" s="1"/>
+      <c r="A636" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="B636" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C636">
         <v>0</v>
@@ -13531,28 +13578,28 @@
         <v>69</v>
       </c>
       <c r="E636">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="F636">
-        <v>2.7</v>
+        <v>0.2</v>
       </c>
       <c r="G636">
-        <v>4.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="637" spans="1:7">
       <c r="A637" s="1"/>
       <c r="B637" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C637">
         <v>0.4</v>
       </c>
       <c r="E637">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="F637">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="G637">
         <v>1.4</v>
@@ -13561,87 +13608,85 @@
     <row r="638" spans="1:7">
       <c r="A638" s="1"/>
       <c r="B638" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C638">
-        <v>0</v>
-      </c>
-      <c r="D638" t="s">
-        <v>69</v>
+        <v>0.7</v>
       </c>
       <c r="E638">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="F638">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="G638">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="639" spans="1:7">
-      <c r="A639" s="1" t="s">
-        <v>97</v>
-      </c>
+      <c r="A639" s="1"/>
       <c r="B639" s="1" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C639">
-        <v>0</v>
-      </c>
-      <c r="D639" t="s">
-        <v>69</v>
+        <v>0.2</v>
       </c>
       <c r="E639">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="F639">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="G639">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="640" spans="1:7">
       <c r="A640" s="1"/>
       <c r="B640" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C640">
-        <v>0.4</v>
+        <v>0</v>
+      </c>
+      <c r="D640" t="s">
+        <v>69</v>
       </c>
       <c r="E640">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="F640">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="G640">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="641" spans="1:7">
       <c r="A641" s="1"/>
       <c r="B641" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C641">
-        <v>0.7</v>
+        <v>0</v>
+      </c>
+      <c r="D641" t="s">
+        <v>69</v>
       </c>
       <c r="E641">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F641">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G641">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="642" spans="1:7">
       <c r="A642" s="1"/>
       <c r="B642" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C642">
         <v>0.2</v>
@@ -13650,16 +13695,16 @@
         <v>0.8</v>
       </c>
       <c r="F642">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G642">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="643" spans="1:7">
       <c r="A643" s="1"/>
       <c r="B643" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C643">
         <v>0</v>
@@ -13668,150 +13713,90 @@
         <v>69</v>
       </c>
       <c r="E643">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="F643">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="G643">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="644" spans="1:7">
       <c r="A644" s="1"/>
       <c r="B644" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C644">
-        <v>0</v>
-      </c>
-      <c r="D644" t="s">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="E644">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F644">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G644">
-        <v>1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="645" spans="1:7">
       <c r="A645" s="1"/>
       <c r="B645" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C645">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="D645" t="s">
+        <v>69</v>
       </c>
       <c r="E645">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="F645">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="G645">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="646" spans="1:7">
       <c r="A646" s="1"/>
       <c r="B646" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C646">
-        <v>0</v>
-      </c>
-      <c r="D646" t="s">
-        <v>69</v>
+        <v>0.8</v>
       </c>
       <c r="E646">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="F646">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="G646">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="647" spans="1:7">
       <c r="A647" s="1"/>
       <c r="B647" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C647">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D647" t="s">
+        <v>69</v>
       </c>
       <c r="E647">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F647">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G647">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="648" spans="1:7">
-      <c r="A648" s="1"/>
-      <c r="B648" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C648">
-        <v>0</v>
-      </c>
-      <c r="D648" t="s">
-        <v>69</v>
-      </c>
-      <c r="E648">
-        <v>1.7</v>
-      </c>
-      <c r="F648">
-        <v>1.3</v>
-      </c>
-      <c r="G648">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="649" spans="1:7">
-      <c r="A649" s="1"/>
-      <c r="B649" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C649">
-        <v>0.8</v>
-      </c>
-      <c r="E649">
-        <v>0.9</v>
-      </c>
-      <c r="F649">
-        <v>0.5</v>
-      </c>
-      <c r="G649">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="650" spans="1:7">
-      <c r="A650" s="1"/>
-      <c r="B650" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C650">
-        <v>0</v>
-      </c>
-      <c r="D650" t="s">
-        <v>69</v>
-      </c>
-      <c r="E650">
-        <v>0.5</v>
-      </c>
-      <c r="F650">
-        <v>0.3</v>
-      </c>
-      <c r="G650">
         <v>0.8</v>
       </c>
     </row>
@@ -13828,12 +13813,12 @@
     <mergeCell ref="A358:A366"/>
     <mergeCell ref="A367:A375"/>
     <mergeCell ref="A376:A384"/>
-    <mergeCell ref="A579:A590"/>
-    <mergeCell ref="A591:A602"/>
-    <mergeCell ref="A603:A614"/>
-    <mergeCell ref="A615:A626"/>
-    <mergeCell ref="A627:A638"/>
-    <mergeCell ref="A639:A650"/>
+    <mergeCell ref="A576:A587"/>
+    <mergeCell ref="A588:A599"/>
+    <mergeCell ref="A600:A611"/>
+    <mergeCell ref="A612:A623"/>
+    <mergeCell ref="A624:A635"/>
+    <mergeCell ref="A636:A647"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assets_output/07_multinomial_logistic_regression.xlsx
+++ b/assets_output/07_multinomial_logistic_regression.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="186">
   <si>
     <t>MNLogit: 'Entry point into BAHSA services (pathway type and level)', table 0</t>
   </si>
@@ -49,7 +49,7 @@
     <t>y</t>
   </si>
   <si>
-    <t>2026-05-22 23:29</t>
+    <t>2026-05-31 10:30</t>
   </si>
   <si>
     <t>3391</t>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>rt_outcome</t>
+  </si>
+  <si>
+    <t>2026-05-31 10:31</t>
   </si>
   <si>
     <t>2195</t>
@@ -5371,7 +5374,7 @@
         <v>18</v>
       </c>
       <c r="E213" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -5382,13 +5385,13 @@
         <v>3</v>
       </c>
       <c r="C214" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="D214" t="s">
         <v>19</v>
       </c>
       <c r="E214" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -5399,13 +5402,13 @@
         <v>4</v>
       </c>
       <c r="C215" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D215" t="s">
         <v>20</v>
       </c>
       <c r="E215" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="216" spans="1:8">
@@ -5416,13 +5419,13 @@
         <v>5</v>
       </c>
       <c r="C216" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D216" t="s">
         <v>21</v>
       </c>
       <c r="E216" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="217" spans="1:8">
@@ -5433,13 +5436,13 @@
         <v>6</v>
       </c>
       <c r="C217" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D217" t="s">
         <v>22</v>
       </c>
       <c r="E217" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -5456,7 +5459,7 @@
         <v>23</v>
       </c>
       <c r="E218" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -5467,7 +5470,7 @@
         <v>8</v>
       </c>
       <c r="C219" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D219" t="s">
         <v>24</v>
@@ -5478,12 +5481,12 @@
     </row>
     <row r="221" spans="1:8">
       <c r="A221" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="222" spans="1:8">
       <c r="B222" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>34</v>
@@ -5610,10 +5613,10 @@
     </row>
     <row r="227" spans="1:8">
       <c r="A227" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B227" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C227">
         <v>0.3</v>
@@ -5740,10 +5743,10 @@
     </row>
     <row r="232" spans="1:8">
       <c r="A232" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B232" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C232">
         <v>1.7</v>
@@ -5792,12 +5795,12 @@
     </row>
     <row r="235" spans="1:8">
       <c r="A235" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="236" spans="1:8">
       <c r="B236" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>34</v>
@@ -5924,10 +5927,10 @@
     </row>
     <row r="241" spans="1:8">
       <c r="A241" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B241" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C241">
         <v>0.1</v>
@@ -6054,10 +6057,10 @@
     </row>
     <row r="246" spans="1:8">
       <c r="A246" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B246" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C246">
         <v>2</v>
@@ -6106,12 +6109,12 @@
     </row>
     <row r="249" spans="1:8">
       <c r="A249" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="250" spans="1:8">
       <c r="B250" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>34</v>
@@ -6238,10 +6241,10 @@
     </row>
     <row r="255" spans="1:8">
       <c r="A255" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B255" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C255">
         <v>-0.5</v>
@@ -6368,10 +6371,10 @@
     </row>
     <row r="260" spans="1:8">
       <c r="A260" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B260" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C260">
         <v>2.9</v>
@@ -6420,7 +6423,7 @@
     </row>
     <row r="263" spans="1:8">
       <c r="A263" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -6442,7 +6445,7 @@
     </row>
     <row r="265" spans="1:8">
       <c r="A265" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>40</v>
@@ -6466,7 +6469,7 @@
     <row r="266" spans="1:8">
       <c r="A266" s="1"/>
       <c r="B266" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C266">
         <v>0.3</v>
@@ -6574,7 +6577,7 @@
     <row r="272" spans="1:8">
       <c r="A272" s="1"/>
       <c r="B272" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C272">
         <v>0</v>
@@ -6651,7 +6654,7 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>40</v>
@@ -6675,7 +6678,7 @@
     <row r="277" spans="1:7">
       <c r="A277" s="1"/>
       <c r="B277" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C277">
         <v>0</v>
@@ -6798,7 +6801,7 @@
     <row r="283" spans="1:7">
       <c r="A283" s="1"/>
       <c r="B283" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C283">
         <v>0</v>
@@ -6878,7 +6881,7 @@
     </row>
     <row r="287" spans="1:7">
       <c r="A287" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B287" s="1" t="s">
         <v>40</v>
@@ -6902,7 +6905,7 @@
     <row r="288" spans="1:7">
       <c r="A288" s="1"/>
       <c r="B288" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C288">
         <v>0.3</v>
@@ -7019,7 +7022,7 @@
     <row r="294" spans="1:7">
       <c r="A294" s="1"/>
       <c r="B294" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C294">
         <v>0</v>
@@ -7099,7 +7102,7 @@
     </row>
     <row r="299" spans="1:7">
       <c r="A299" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="300" spans="1:7">
@@ -7141,13 +7144,13 @@
         <v>2</v>
       </c>
       <c r="C302" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D302" t="s">
         <v>18</v>
       </c>
       <c r="E302" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -7158,13 +7161,13 @@
         <v>3</v>
       </c>
       <c r="C303" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="D303" t="s">
         <v>19</v>
       </c>
       <c r="E303" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="304" spans="1:7">
@@ -7175,13 +7178,13 @@
         <v>4</v>
       </c>
       <c r="C304" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D304" t="s">
         <v>20</v>
       </c>
       <c r="E304" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -7192,13 +7195,13 @@
         <v>5</v>
       </c>
       <c r="C305" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D305" t="s">
         <v>21</v>
       </c>
       <c r="E305" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -7209,13 +7212,13 @@
         <v>6</v>
       </c>
       <c r="C306" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D306" t="s">
         <v>22</v>
       </c>
       <c r="E306" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="307" spans="1:8">
@@ -7232,7 +7235,7 @@
         <v>23</v>
       </c>
       <c r="E307" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="308" spans="1:8">
@@ -7243,7 +7246,7 @@
         <v>8</v>
       </c>
       <c r="C308" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D308" t="s">
         <v>24</v>
@@ -7254,12 +7257,12 @@
     </row>
     <row r="310" spans="1:8">
       <c r="A310" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="311" spans="1:8">
       <c r="B311" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>34</v>
@@ -7360,10 +7363,10 @@
     </row>
     <row r="315" spans="1:8">
       <c r="A315" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B315" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C315">
         <v>0.3</v>
@@ -7490,10 +7493,10 @@
     </row>
     <row r="320" spans="1:8">
       <c r="A320" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B320" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C320">
         <v>1.7</v>
@@ -7516,12 +7519,12 @@
     </row>
     <row r="322" spans="1:8">
       <c r="A322" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="323" spans="1:8">
       <c r="B323" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>34</v>
@@ -7622,10 +7625,10 @@
     </row>
     <row r="327" spans="1:8">
       <c r="A327" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B327" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C327">
         <v>0.2</v>
@@ -7752,10 +7755,10 @@
     </row>
     <row r="332" spans="1:8">
       <c r="A332" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B332" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C332">
         <v>1.8</v>
@@ -7778,12 +7781,12 @@
     </row>
     <row r="334" spans="1:8">
       <c r="A334" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="335" spans="1:8">
       <c r="B335" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>34</v>
@@ -7884,10 +7887,10 @@
     </row>
     <row r="339" spans="1:8">
       <c r="A339" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B339" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C339">
         <v>-0.5</v>
@@ -8014,10 +8017,10 @@
     </row>
     <row r="344" spans="1:8">
       <c r="A344" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B344" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C344">
         <v>2.2</v>
@@ -8040,7 +8043,7 @@
     </row>
     <row r="346" spans="1:8">
       <c r="A346" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="347" spans="1:8">
@@ -8062,7 +8065,7 @@
     </row>
     <row r="348" spans="1:8">
       <c r="A348" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B348" s="1" t="s">
         <v>40</v>
@@ -8086,7 +8089,7 @@
     <row r="349" spans="1:8">
       <c r="A349" s="1"/>
       <c r="B349" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C349">
         <v>0.3</v>
@@ -8158,7 +8161,7 @@
     <row r="353" spans="1:7">
       <c r="A353" s="1"/>
       <c r="B353" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C353">
         <v>0.1</v>
@@ -8232,7 +8235,7 @@
     </row>
     <row r="357" spans="1:7">
       <c r="A357" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B357" s="1" t="s">
         <v>40</v>
@@ -8256,7 +8259,7 @@
     <row r="358" spans="1:7">
       <c r="A358" s="1"/>
       <c r="B358" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C358">
         <v>0</v>
@@ -8340,7 +8343,7 @@
     <row r="362" spans="1:7">
       <c r="A362" s="1"/>
       <c r="B362" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C362">
         <v>0</v>
@@ -8420,7 +8423,7 @@
     </row>
     <row r="366" spans="1:7">
       <c r="A366" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>40</v>
@@ -8444,7 +8447,7 @@
     <row r="367" spans="1:7">
       <c r="A367" s="1"/>
       <c r="B367" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C367">
         <v>0.1</v>
@@ -8522,7 +8525,7 @@
     <row r="371" spans="1:7">
       <c r="A371" s="1"/>
       <c r="B371" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C371">
         <v>0</v>
@@ -8602,7 +8605,7 @@
     </row>
     <row r="376" spans="1:7">
       <c r="A376" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="377" spans="1:7">
@@ -8627,7 +8630,7 @@
         <v>1</v>
       </c>
       <c r="C378" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D378" t="s">
         <v>17</v>
@@ -8644,13 +8647,13 @@
         <v>2</v>
       </c>
       <c r="C379" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D379" t="s">
         <v>18</v>
       </c>
       <c r="E379" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="380" spans="1:7">
@@ -8661,13 +8664,13 @@
         <v>3</v>
       </c>
       <c r="C380" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="D380" t="s">
         <v>19</v>
       </c>
       <c r="E380" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="381" spans="1:7">
@@ -8678,13 +8681,13 @@
         <v>4</v>
       </c>
       <c r="C381" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D381" t="s">
         <v>20</v>
       </c>
       <c r="E381" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="382" spans="1:7">
@@ -8695,13 +8698,13 @@
         <v>5</v>
       </c>
       <c r="C382" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D382" t="s">
         <v>21</v>
       </c>
       <c r="E382" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="383" spans="1:7">
@@ -8712,13 +8715,13 @@
         <v>6</v>
       </c>
       <c r="C383" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D383" t="s">
         <v>22</v>
       </c>
       <c r="E383" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="384" spans="1:7">
@@ -8735,7 +8738,7 @@
         <v>23</v>
       </c>
       <c r="E384" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="385" spans="1:7">
@@ -8746,7 +8749,7 @@
         <v>8</v>
       </c>
       <c r="C385" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D385" t="s">
         <v>24</v>
@@ -8757,7 +8760,7 @@
     </row>
     <row r="387" spans="1:7">
       <c r="A387" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="388" spans="1:7">
@@ -8768,10 +8771,10 @@
         <v>35</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F388" s="1" t="s">
         <v>38</v>
@@ -8805,7 +8808,7 @@
     </row>
     <row r="390" spans="1:7">
       <c r="A390" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B390">
         <v>0.4</v>
@@ -8920,7 +8923,7 @@
     </row>
     <row r="395" spans="1:7">
       <c r="A395" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B395">
         <v>0.8</v>
@@ -8943,7 +8946,7 @@
     </row>
     <row r="397" spans="1:7">
       <c r="A397" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="398" spans="1:7">
@@ -8985,7 +8988,7 @@
     </row>
     <row r="400" spans="1:7">
       <c r="A400" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B400">
         <v>0</v>
@@ -9065,7 +9068,7 @@
     </row>
     <row r="404" spans="1:6">
       <c r="A404" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B404">
         <v>0</v>
@@ -9105,7 +9108,7 @@
     </row>
     <row r="407" spans="1:6">
       <c r="A407" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="408" spans="1:6">
@@ -9130,7 +9133,7 @@
         <v>1</v>
       </c>
       <c r="C409" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D409" t="s">
         <v>17</v>
@@ -9147,13 +9150,13 @@
         <v>2</v>
       </c>
       <c r="C410" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D410" t="s">
         <v>18</v>
       </c>
       <c r="E410" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="411" spans="1:6">
@@ -9164,13 +9167,13 @@
         <v>3</v>
       </c>
       <c r="C411" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="D411" t="s">
         <v>19</v>
       </c>
       <c r="E411" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="412" spans="1:6">
@@ -9181,13 +9184,13 @@
         <v>4</v>
       </c>
       <c r="C412" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D412" t="s">
         <v>20</v>
       </c>
       <c r="E412" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="413" spans="1:6">
@@ -9198,13 +9201,13 @@
         <v>5</v>
       </c>
       <c r="C413" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D413" t="s">
         <v>21</v>
       </c>
       <c r="E413" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="414" spans="1:6">
@@ -9215,13 +9218,13 @@
         <v>6</v>
       </c>
       <c r="C414" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D414" t="s">
         <v>22</v>
       </c>
       <c r="E414" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="415" spans="1:6">
@@ -9238,7 +9241,7 @@
         <v>23</v>
       </c>
       <c r="E415" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="416" spans="1:6">
@@ -9249,7 +9252,7 @@
         <v>8</v>
       </c>
       <c r="C416" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D416" t="s">
         <v>24</v>
@@ -9260,7 +9263,7 @@
     </row>
     <row r="418" spans="1:7">
       <c r="A418" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="419" spans="1:7">
@@ -9271,10 +9274,10 @@
         <v>35</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F419" s="1" t="s">
         <v>38</v>
@@ -9331,7 +9334,7 @@
     </row>
     <row r="422" spans="1:7">
       <c r="A422" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B422">
         <v>-0.5</v>
@@ -9446,7 +9449,7 @@
     </row>
     <row r="428" spans="1:7">
       <c r="A428" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="429" spans="1:7">
@@ -9488,7 +9491,7 @@
     </row>
     <row r="431" spans="1:7">
       <c r="A431" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B431">
         <v>0</v>
@@ -9608,7 +9611,7 @@
     </row>
     <row r="438" spans="1:6">
       <c r="A438" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="439" spans="1:6">
@@ -9633,7 +9636,7 @@
         <v>1</v>
       </c>
       <c r="C440" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D440" t="s">
         <v>17</v>
@@ -9650,13 +9653,13 @@
         <v>2</v>
       </c>
       <c r="C441" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D441" t="s">
         <v>18</v>
       </c>
       <c r="E441" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="442" spans="1:6">
@@ -9667,13 +9670,13 @@
         <v>3</v>
       </c>
       <c r="C442" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="D442" t="s">
         <v>19</v>
       </c>
       <c r="E442" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="443" spans="1:6">
@@ -9684,13 +9687,13 @@
         <v>4</v>
       </c>
       <c r="C443" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D443" t="s">
         <v>20</v>
       </c>
       <c r="E443" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="444" spans="1:6">
@@ -9701,13 +9704,13 @@
         <v>5</v>
       </c>
       <c r="C444" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D444" t="s">
         <v>21</v>
       </c>
       <c r="E444" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="445" spans="1:6">
@@ -9718,13 +9721,13 @@
         <v>6</v>
       </c>
       <c r="C445" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D445" t="s">
         <v>22</v>
       </c>
       <c r="E445" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="446" spans="1:6">
@@ -9741,7 +9744,7 @@
         <v>23</v>
       </c>
       <c r="E446" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="447" spans="1:6">
@@ -9752,7 +9755,7 @@
         <v>8</v>
       </c>
       <c r="C447" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D447" t="s">
         <v>24</v>
@@ -9763,7 +9766,7 @@
     </row>
     <row r="449" spans="1:7">
       <c r="A449" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="450" spans="1:7">
@@ -9774,10 +9777,10 @@
         <v>35</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F450" s="1" t="s">
         <v>38</v>
@@ -9880,7 +9883,7 @@
     </row>
     <row r="456" spans="1:7">
       <c r="A456" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="457" spans="1:7">
@@ -9979,7 +9982,7 @@
     </row>
     <row r="463" spans="1:7">
       <c r="A463" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="464" spans="1:7">
@@ -10021,13 +10024,13 @@
         <v>2</v>
       </c>
       <c r="C466" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D466" t="s">
         <v>18</v>
       </c>
       <c r="E466" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="467" spans="1:8">
@@ -10038,13 +10041,13 @@
         <v>3</v>
       </c>
       <c r="C467" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="D467" t="s">
         <v>19</v>
       </c>
       <c r="E467" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="468" spans="1:8">
@@ -10055,13 +10058,13 @@
         <v>4</v>
       </c>
       <c r="C468" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D468" t="s">
         <v>20</v>
       </c>
       <c r="E468" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="469" spans="1:8">
@@ -10072,13 +10075,13 @@
         <v>5</v>
       </c>
       <c r="C469" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D469" t="s">
         <v>21</v>
       </c>
       <c r="E469" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="470" spans="1:8">
@@ -10089,13 +10092,13 @@
         <v>6</v>
       </c>
       <c r="C470" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D470" t="s">
         <v>22</v>
       </c>
       <c r="E470" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="471" spans="1:8">
@@ -10112,7 +10115,7 @@
         <v>23</v>
       </c>
       <c r="E471" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="472" spans="1:8">
@@ -10134,12 +10137,12 @@
     </row>
     <row r="474" spans="1:8">
       <c r="A474" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="475" spans="1:8">
       <c r="B475" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C475" s="1" t="s">
         <v>34</v>
@@ -10266,10 +10269,10 @@
     </row>
     <row r="480" spans="1:8">
       <c r="A480" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B480" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C480">
         <v>-0.1</v>
@@ -10422,10 +10425,10 @@
     </row>
     <row r="486" spans="1:8">
       <c r="A486" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B486" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C486">
         <v>-1.1</v>
@@ -10474,12 +10477,12 @@
     </row>
     <row r="489" spans="1:8">
       <c r="A489" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="490" spans="1:8">
       <c r="B490" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C490" s="1" t="s">
         <v>34</v>
@@ -10606,10 +10609,10 @@
     </row>
     <row r="495" spans="1:8">
       <c r="A495" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B495" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C495">
         <v>0.4</v>
@@ -10762,10 +10765,10 @@
     </row>
     <row r="501" spans="1:8">
       <c r="A501" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B501" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C501">
         <v>0.3</v>
@@ -10814,12 +10817,12 @@
     </row>
     <row r="504" spans="1:8">
       <c r="A504" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="505" spans="1:8">
       <c r="B505" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C505" s="1" t="s">
         <v>34</v>
@@ -10946,10 +10949,10 @@
     </row>
     <row r="510" spans="1:8">
       <c r="A510" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B510" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C510">
         <v>0.1</v>
@@ -11102,10 +11105,10 @@
     </row>
     <row r="516" spans="1:8">
       <c r="A516" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B516" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C516">
         <v>0</v>
@@ -11154,12 +11157,12 @@
     </row>
     <row r="519" spans="1:8">
       <c r="A519" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="520" spans="1:8">
       <c r="B520" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C520" s="1" t="s">
         <v>34</v>
@@ -11286,10 +11289,10 @@
     </row>
     <row r="525" spans="1:8">
       <c r="A525" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B525" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C525">
         <v>0.1</v>
@@ -11442,10 +11445,10 @@
     </row>
     <row r="531" spans="1:8">
       <c r="A531" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B531" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C531">
         <v>0.1</v>
@@ -11494,12 +11497,12 @@
     </row>
     <row r="534" spans="1:8">
       <c r="A534" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="535" spans="1:8">
       <c r="B535" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C535" s="1" t="s">
         <v>34</v>
@@ -11626,10 +11629,10 @@
     </row>
     <row r="540" spans="1:8">
       <c r="A540" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B540" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C540">
         <v>0.3</v>
@@ -11782,10 +11785,10 @@
     </row>
     <row r="546" spans="1:8">
       <c r="A546" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B546" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C546">
         <v>-0.4</v>
@@ -11834,12 +11837,12 @@
     </row>
     <row r="549" spans="1:8">
       <c r="A549" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="550" spans="1:8">
       <c r="B550" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C550" s="1" t="s">
         <v>34</v>
@@ -11966,10 +11969,10 @@
     </row>
     <row r="555" spans="1:8">
       <c r="A555" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B555" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C555">
         <v>-0.6</v>
@@ -12122,10 +12125,10 @@
     </row>
     <row r="561" spans="1:8">
       <c r="A561" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B561" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C561">
         <v>0.6</v>
@@ -12174,7 +12177,7 @@
     </row>
     <row r="564" spans="1:8">
       <c r="A564" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="565" spans="1:8">
@@ -12196,7 +12199,7 @@
     </row>
     <row r="566" spans="1:8">
       <c r="A566" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B566" s="1" t="s">
         <v>40</v>
@@ -12220,7 +12223,7 @@
     <row r="567" spans="1:8">
       <c r="A567" s="1"/>
       <c r="B567" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C567">
         <v>0.1</v>
@@ -12352,7 +12355,7 @@
     <row r="574" spans="1:8">
       <c r="A574" s="1"/>
       <c r="B574" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C574">
         <v>0.5</v>
@@ -12426,7 +12429,7 @@
     </row>
     <row r="578" spans="1:7">
       <c r="A578" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B578" s="1" t="s">
         <v>40</v>
@@ -12447,7 +12450,7 @@
     <row r="579" spans="1:7">
       <c r="A579" s="1"/>
       <c r="B579" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C579">
         <v>0.5</v>
@@ -12579,7 +12582,7 @@
     <row r="586" spans="1:7">
       <c r="A586" s="1"/>
       <c r="B586" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C586">
         <v>0.1</v>
@@ -12653,7 +12656,7 @@
     </row>
     <row r="590" spans="1:7">
       <c r="A590" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B590" s="1" t="s">
         <v>40</v>
@@ -12677,7 +12680,7 @@
     <row r="591" spans="1:7">
       <c r="A591" s="1"/>
       <c r="B591" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C591">
         <v>0</v>
@@ -12812,7 +12815,7 @@
     <row r="598" spans="1:7">
       <c r="A598" s="1"/>
       <c r="B598" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C598">
         <v>0.3</v>
@@ -12883,7 +12886,7 @@
     </row>
     <row r="602" spans="1:7">
       <c r="A602" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B602" s="1" t="s">
         <v>40</v>
@@ -12907,7 +12910,7 @@
     <row r="603" spans="1:7">
       <c r="A603" s="1"/>
       <c r="B603" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C603">
         <v>0.5</v>
@@ -13033,7 +13036,7 @@
     <row r="610" spans="1:7">
       <c r="A610" s="1"/>
       <c r="B610" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C610">
         <v>0.6</v>
@@ -13107,7 +13110,7 @@
     </row>
     <row r="614" spans="1:7">
       <c r="A614" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B614" s="1" t="s">
         <v>40</v>
@@ -13131,7 +13134,7 @@
     <row r="615" spans="1:7">
       <c r="A615" s="1"/>
       <c r="B615" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C615">
         <v>0</v>
@@ -13266,7 +13269,7 @@
     <row r="622" spans="1:7">
       <c r="A622" s="1"/>
       <c r="B622" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C622">
         <v>0.2</v>
@@ -13343,7 +13346,7 @@
     </row>
     <row r="626" spans="1:7">
       <c r="A626" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B626" s="1" t="s">
         <v>40</v>
@@ -13367,7 +13370,7 @@
     <row r="627" spans="1:7">
       <c r="A627" s="1"/>
       <c r="B627" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C627">
         <v>0.4</v>
@@ -13502,7 +13505,7 @@
     <row r="634" spans="1:7">
       <c r="A634" s="1"/>
       <c r="B634" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C634">
         <v>1</v>

--- a/assets_output/07_multinomial_logistic_regression.xlsx
+++ b/assets_output/07_multinomial_logistic_regression.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="185">
   <si>
     <t>MNLogit: 'Entry point into BAHSA services (pathway type and level)', table 0</t>
   </si>
@@ -49,7 +49,7 @@
     <t>y</t>
   </si>
   <si>
-    <t>2026-05-31 10:30</t>
+    <t>2026-05-31 11:22</t>
   </si>
   <si>
     <t>3391</t>
@@ -245,9 +245,6 @@
   </si>
   <si>
     <t>rt_outcome</t>
-  </si>
-  <si>
-    <t>2026-05-31 10:31</t>
   </si>
   <si>
     <t>2195</t>
@@ -5374,7 +5371,7 @@
         <v>18</v>
       </c>
       <c r="E213" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -5385,13 +5382,13 @@
         <v>3</v>
       </c>
       <c r="C214" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="D214" t="s">
         <v>19</v>
       </c>
       <c r="E214" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -5402,13 +5399,13 @@
         <v>4</v>
       </c>
       <c r="C215" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D215" t="s">
         <v>20</v>
       </c>
       <c r="E215" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="216" spans="1:8">
@@ -5419,13 +5416,13 @@
         <v>5</v>
       </c>
       <c r="C216" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D216" t="s">
         <v>21</v>
       </c>
       <c r="E216" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="217" spans="1:8">
@@ -5436,13 +5433,13 @@
         <v>6</v>
       </c>
       <c r="C217" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D217" t="s">
         <v>22</v>
       </c>
       <c r="E217" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -5459,7 +5456,7 @@
         <v>23</v>
       </c>
       <c r="E218" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -5470,7 +5467,7 @@
         <v>8</v>
       </c>
       <c r="C219" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D219" t="s">
         <v>24</v>
@@ -5481,12 +5478,12 @@
     </row>
     <row r="221" spans="1:8">
       <c r="A221" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="222" spans="1:8">
       <c r="B222" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>34</v>
@@ -5613,10 +5610,10 @@
     </row>
     <row r="227" spans="1:8">
       <c r="A227" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B227" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C227">
         <v>0.3</v>
@@ -5743,10 +5740,10 @@
     </row>
     <row r="232" spans="1:8">
       <c r="A232" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B232" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C232">
         <v>1.7</v>
@@ -5795,12 +5792,12 @@
     </row>
     <row r="235" spans="1:8">
       <c r="A235" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="236" spans="1:8">
       <c r="B236" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>34</v>
@@ -5927,10 +5924,10 @@
     </row>
     <row r="241" spans="1:8">
       <c r="A241" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B241" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C241">
         <v>0.1</v>
@@ -6057,10 +6054,10 @@
     </row>
     <row r="246" spans="1:8">
       <c r="A246" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B246" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C246">
         <v>2</v>
@@ -6109,12 +6106,12 @@
     </row>
     <row r="249" spans="1:8">
       <c r="A249" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="250" spans="1:8">
       <c r="B250" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>34</v>
@@ -6241,10 +6238,10 @@
     </row>
     <row r="255" spans="1:8">
       <c r="A255" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B255" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C255">
         <v>-0.5</v>
@@ -6371,10 +6368,10 @@
     </row>
     <row r="260" spans="1:8">
       <c r="A260" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B260" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C260">
         <v>2.9</v>
@@ -6423,7 +6420,7 @@
     </row>
     <row r="263" spans="1:8">
       <c r="A263" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -6445,7 +6442,7 @@
     </row>
     <row r="265" spans="1:8">
       <c r="A265" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>40</v>
@@ -6469,7 +6466,7 @@
     <row r="266" spans="1:8">
       <c r="A266" s="1"/>
       <c r="B266" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C266">
         <v>0.3</v>
@@ -6577,7 +6574,7 @@
     <row r="272" spans="1:8">
       <c r="A272" s="1"/>
       <c r="B272" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C272">
         <v>0</v>
@@ -6654,7 +6651,7 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>40</v>
@@ -6678,7 +6675,7 @@
     <row r="277" spans="1:7">
       <c r="A277" s="1"/>
       <c r="B277" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C277">
         <v>0</v>
@@ -6801,7 +6798,7 @@
     <row r="283" spans="1:7">
       <c r="A283" s="1"/>
       <c r="B283" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C283">
         <v>0</v>
@@ -6881,7 +6878,7 @@
     </row>
     <row r="287" spans="1:7">
       <c r="A287" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B287" s="1" t="s">
         <v>40</v>
@@ -6905,7 +6902,7 @@
     <row r="288" spans="1:7">
       <c r="A288" s="1"/>
       <c r="B288" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C288">
         <v>0.3</v>
@@ -7022,7 +7019,7 @@
     <row r="294" spans="1:7">
       <c r="A294" s="1"/>
       <c r="B294" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C294">
         <v>0</v>
@@ -7102,7 +7099,7 @@
     </row>
     <row r="299" spans="1:7">
       <c r="A299" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="300" spans="1:7">
@@ -7144,13 +7141,13 @@
         <v>2</v>
       </c>
       <c r="C302" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D302" t="s">
         <v>18</v>
       </c>
       <c r="E302" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -7161,13 +7158,13 @@
         <v>3</v>
       </c>
       <c r="C303" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="D303" t="s">
         <v>19</v>
       </c>
       <c r="E303" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="304" spans="1:7">
@@ -7178,13 +7175,13 @@
         <v>4</v>
       </c>
       <c r="C304" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D304" t="s">
         <v>20</v>
       </c>
       <c r="E304" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -7195,13 +7192,13 @@
         <v>5</v>
       </c>
       <c r="C305" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D305" t="s">
         <v>21</v>
       </c>
       <c r="E305" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -7212,13 +7209,13 @@
         <v>6</v>
       </c>
       <c r="C306" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D306" t="s">
         <v>22</v>
       </c>
       <c r="E306" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="307" spans="1:8">
@@ -7235,7 +7232,7 @@
         <v>23</v>
       </c>
       <c r="E307" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="308" spans="1:8">
@@ -7246,7 +7243,7 @@
         <v>8</v>
       </c>
       <c r="C308" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D308" t="s">
         <v>24</v>
@@ -7257,12 +7254,12 @@
     </row>
     <row r="310" spans="1:8">
       <c r="A310" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="311" spans="1:8">
       <c r="B311" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>34</v>
@@ -7363,10 +7360,10 @@
     </row>
     <row r="315" spans="1:8">
       <c r="A315" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B315" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C315">
         <v>0.3</v>
@@ -7493,10 +7490,10 @@
     </row>
     <row r="320" spans="1:8">
       <c r="A320" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B320" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C320">
         <v>1.7</v>
@@ -7519,12 +7516,12 @@
     </row>
     <row r="322" spans="1:8">
       <c r="A322" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="323" spans="1:8">
       <c r="B323" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>34</v>
@@ -7625,10 +7622,10 @@
     </row>
     <row r="327" spans="1:8">
       <c r="A327" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B327" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C327">
         <v>0.2</v>
@@ -7755,10 +7752,10 @@
     </row>
     <row r="332" spans="1:8">
       <c r="A332" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B332" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C332">
         <v>1.8</v>
@@ -7781,12 +7778,12 @@
     </row>
     <row r="334" spans="1:8">
       <c r="A334" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="335" spans="1:8">
       <c r="B335" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>34</v>
@@ -7887,10 +7884,10 @@
     </row>
     <row r="339" spans="1:8">
       <c r="A339" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B339" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C339">
         <v>-0.5</v>
@@ -8017,10 +8014,10 @@
     </row>
     <row r="344" spans="1:8">
       <c r="A344" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B344" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C344">
         <v>2.2</v>
@@ -8043,7 +8040,7 @@
     </row>
     <row r="346" spans="1:8">
       <c r="A346" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="347" spans="1:8">
@@ -8065,7 +8062,7 @@
     </row>
     <row r="348" spans="1:8">
       <c r="A348" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B348" s="1" t="s">
         <v>40</v>
@@ -8089,7 +8086,7 @@
     <row r="349" spans="1:8">
       <c r="A349" s="1"/>
       <c r="B349" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C349">
         <v>0.3</v>
@@ -8161,7 +8158,7 @@
     <row r="353" spans="1:7">
       <c r="A353" s="1"/>
       <c r="B353" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C353">
         <v>0.1</v>
@@ -8235,7 +8232,7 @@
     </row>
     <row r="357" spans="1:7">
       <c r="A357" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B357" s="1" t="s">
         <v>40</v>
@@ -8259,7 +8256,7 @@
     <row r="358" spans="1:7">
       <c r="A358" s="1"/>
       <c r="B358" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C358">
         <v>0</v>
@@ -8343,7 +8340,7 @@
     <row r="362" spans="1:7">
       <c r="A362" s="1"/>
       <c r="B362" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C362">
         <v>0</v>
@@ -8423,7 +8420,7 @@
     </row>
     <row r="366" spans="1:7">
       <c r="A366" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>40</v>
@@ -8447,7 +8444,7 @@
     <row r="367" spans="1:7">
       <c r="A367" s="1"/>
       <c r="B367" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C367">
         <v>0.1</v>
@@ -8525,7 +8522,7 @@
     <row r="371" spans="1:7">
       <c r="A371" s="1"/>
       <c r="B371" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C371">
         <v>0</v>
@@ -8605,7 +8602,7 @@
     </row>
     <row r="376" spans="1:7">
       <c r="A376" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="377" spans="1:7">
@@ -8630,7 +8627,7 @@
         <v>1</v>
       </c>
       <c r="C378" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D378" t="s">
         <v>17</v>
@@ -8647,13 +8644,13 @@
         <v>2</v>
       </c>
       <c r="C379" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D379" t="s">
         <v>18</v>
       </c>
       <c r="E379" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="380" spans="1:7">
@@ -8664,13 +8661,13 @@
         <v>3</v>
       </c>
       <c r="C380" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="D380" t="s">
         <v>19</v>
       </c>
       <c r="E380" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="381" spans="1:7">
@@ -8681,13 +8678,13 @@
         <v>4</v>
       </c>
       <c r="C381" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D381" t="s">
         <v>20</v>
       </c>
       <c r="E381" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="382" spans="1:7">
@@ -8698,13 +8695,13 @@
         <v>5</v>
       </c>
       <c r="C382" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D382" t="s">
         <v>21</v>
       </c>
       <c r="E382" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="383" spans="1:7">
@@ -8715,13 +8712,13 @@
         <v>6</v>
       </c>
       <c r="C383" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D383" t="s">
         <v>22</v>
       </c>
       <c r="E383" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="384" spans="1:7">
@@ -8738,7 +8735,7 @@
         <v>23</v>
       </c>
       <c r="E384" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="385" spans="1:7">
@@ -8749,7 +8746,7 @@
         <v>8</v>
       </c>
       <c r="C385" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D385" t="s">
         <v>24</v>
@@ -8760,7 +8757,7 @@
     </row>
     <row r="387" spans="1:7">
       <c r="A387" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="388" spans="1:7">
@@ -8771,10 +8768,10 @@
         <v>35</v>
       </c>
       <c r="D388" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E388" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="E388" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="F388" s="1" t="s">
         <v>38</v>
@@ -8808,7 +8805,7 @@
     </row>
     <row r="390" spans="1:7">
       <c r="A390" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B390">
         <v>0.4</v>
@@ -8923,7 +8920,7 @@
     </row>
     <row r="395" spans="1:7">
       <c r="A395" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B395">
         <v>0.8</v>
@@ -8946,7 +8943,7 @@
     </row>
     <row r="397" spans="1:7">
       <c r="A397" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="398" spans="1:7">
@@ -8988,7 +8985,7 @@
     </row>
     <row r="400" spans="1:7">
       <c r="A400" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B400">
         <v>0</v>
@@ -9068,7 +9065,7 @@
     </row>
     <row r="404" spans="1:6">
       <c r="A404" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B404">
         <v>0</v>
@@ -9108,7 +9105,7 @@
     </row>
     <row r="407" spans="1:6">
       <c r="A407" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="408" spans="1:6">
@@ -9133,7 +9130,7 @@
         <v>1</v>
       </c>
       <c r="C409" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D409" t="s">
         <v>17</v>
@@ -9150,13 +9147,13 @@
         <v>2</v>
       </c>
       <c r="C410" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D410" t="s">
         <v>18</v>
       </c>
       <c r="E410" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="411" spans="1:6">
@@ -9167,13 +9164,13 @@
         <v>3</v>
       </c>
       <c r="C411" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="D411" t="s">
         <v>19</v>
       </c>
       <c r="E411" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="412" spans="1:6">
@@ -9184,13 +9181,13 @@
         <v>4</v>
       </c>
       <c r="C412" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D412" t="s">
         <v>20</v>
       </c>
       <c r="E412" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="413" spans="1:6">
@@ -9201,13 +9198,13 @@
         <v>5</v>
       </c>
       <c r="C413" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D413" t="s">
         <v>21</v>
       </c>
       <c r="E413" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="414" spans="1:6">
@@ -9218,13 +9215,13 @@
         <v>6</v>
       </c>
       <c r="C414" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D414" t="s">
         <v>22</v>
       </c>
       <c r="E414" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="415" spans="1:6">
@@ -9241,7 +9238,7 @@
         <v>23</v>
       </c>
       <c r="E415" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="416" spans="1:6">
@@ -9252,7 +9249,7 @@
         <v>8</v>
       </c>
       <c r="C416" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D416" t="s">
         <v>24</v>
@@ -9263,7 +9260,7 @@
     </row>
     <row r="418" spans="1:7">
       <c r="A418" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="419" spans="1:7">
@@ -9274,10 +9271,10 @@
         <v>35</v>
       </c>
       <c r="D419" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E419" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="E419" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="F419" s="1" t="s">
         <v>38</v>
@@ -9334,7 +9331,7 @@
     </row>
     <row r="422" spans="1:7">
       <c r="A422" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B422">
         <v>-0.5</v>
@@ -9449,7 +9446,7 @@
     </row>
     <row r="428" spans="1:7">
       <c r="A428" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="429" spans="1:7">
@@ -9491,7 +9488,7 @@
     </row>
     <row r="431" spans="1:7">
       <c r="A431" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B431">
         <v>0</v>
@@ -9611,7 +9608,7 @@
     </row>
     <row r="438" spans="1:6">
       <c r="A438" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="439" spans="1:6">
@@ -9636,7 +9633,7 @@
         <v>1</v>
       </c>
       <c r="C440" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D440" t="s">
         <v>17</v>
@@ -9653,13 +9650,13 @@
         <v>2</v>
       </c>
       <c r="C441" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D441" t="s">
         <v>18</v>
       </c>
       <c r="E441" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="442" spans="1:6">
@@ -9670,13 +9667,13 @@
         <v>3</v>
       </c>
       <c r="C442" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="D442" t="s">
         <v>19</v>
       </c>
       <c r="E442" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="443" spans="1:6">
@@ -9687,13 +9684,13 @@
         <v>4</v>
       </c>
       <c r="C443" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D443" t="s">
         <v>20</v>
       </c>
       <c r="E443" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="444" spans="1:6">
@@ -9704,13 +9701,13 @@
         <v>5</v>
       </c>
       <c r="C444" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D444" t="s">
         <v>21</v>
       </c>
       <c r="E444" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="445" spans="1:6">
@@ -9721,13 +9718,13 @@
         <v>6</v>
       </c>
       <c r="C445" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D445" t="s">
         <v>22</v>
       </c>
       <c r="E445" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="446" spans="1:6">
@@ -9744,7 +9741,7 @@
         <v>23</v>
       </c>
       <c r="E446" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="447" spans="1:6">
@@ -9755,7 +9752,7 @@
         <v>8</v>
       </c>
       <c r="C447" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D447" t="s">
         <v>24</v>
@@ -9766,7 +9763,7 @@
     </row>
     <row r="449" spans="1:7">
       <c r="A449" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="450" spans="1:7">
@@ -9777,10 +9774,10 @@
         <v>35</v>
       </c>
       <c r="D450" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E450" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="E450" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="F450" s="1" t="s">
         <v>38</v>
@@ -9883,7 +9880,7 @@
     </row>
     <row r="456" spans="1:7">
       <c r="A456" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="457" spans="1:7">
@@ -9982,7 +9979,7 @@
     </row>
     <row r="463" spans="1:7">
       <c r="A463" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="464" spans="1:7">
@@ -10024,13 +10021,13 @@
         <v>2</v>
       </c>
       <c r="C466" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D466" t="s">
         <v>18</v>
       </c>
       <c r="E466" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="467" spans="1:8">
@@ -10041,13 +10038,13 @@
         <v>3</v>
       </c>
       <c r="C467" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="D467" t="s">
         <v>19</v>
       </c>
       <c r="E467" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="468" spans="1:8">
@@ -10058,13 +10055,13 @@
         <v>4</v>
       </c>
       <c r="C468" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D468" t="s">
         <v>20</v>
       </c>
       <c r="E468" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="469" spans="1:8">
@@ -10075,13 +10072,13 @@
         <v>5</v>
       </c>
       <c r="C469" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D469" t="s">
         <v>21</v>
       </c>
       <c r="E469" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="470" spans="1:8">
@@ -10092,13 +10089,13 @@
         <v>6</v>
       </c>
       <c r="C470" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D470" t="s">
         <v>22</v>
       </c>
       <c r="E470" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="471" spans="1:8">
@@ -10115,7 +10112,7 @@
         <v>23</v>
       </c>
       <c r="E471" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="472" spans="1:8">
@@ -10137,12 +10134,12 @@
     </row>
     <row r="474" spans="1:8">
       <c r="A474" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="475" spans="1:8">
       <c r="B475" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C475" s="1" t="s">
         <v>34</v>
@@ -10269,10 +10266,10 @@
     </row>
     <row r="480" spans="1:8">
       <c r="A480" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B480" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C480">
         <v>-0.1</v>
@@ -10425,10 +10422,10 @@
     </row>
     <row r="486" spans="1:8">
       <c r="A486" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B486" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C486">
         <v>-1.1</v>
@@ -10477,12 +10474,12 @@
     </row>
     <row r="489" spans="1:8">
       <c r="A489" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="490" spans="1:8">
       <c r="B490" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C490" s="1" t="s">
         <v>34</v>
@@ -10609,10 +10606,10 @@
     </row>
     <row r="495" spans="1:8">
       <c r="A495" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B495" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C495">
         <v>0.4</v>
@@ -10765,10 +10762,10 @@
     </row>
     <row r="501" spans="1:8">
       <c r="A501" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B501" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C501">
         <v>0.3</v>
@@ -10817,12 +10814,12 @@
     </row>
     <row r="504" spans="1:8">
       <c r="A504" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="505" spans="1:8">
       <c r="B505" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C505" s="1" t="s">
         <v>34</v>
@@ -10949,10 +10946,10 @@
     </row>
     <row r="510" spans="1:8">
       <c r="A510" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B510" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C510">
         <v>0.1</v>
@@ -11105,10 +11102,10 @@
     </row>
     <row r="516" spans="1:8">
       <c r="A516" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B516" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C516">
         <v>0</v>
@@ -11157,12 +11154,12 @@
     </row>
     <row r="519" spans="1:8">
       <c r="A519" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="520" spans="1:8">
       <c r="B520" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C520" s="1" t="s">
         <v>34</v>
@@ -11289,10 +11286,10 @@
     </row>
     <row r="525" spans="1:8">
       <c r="A525" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B525" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C525">
         <v>0.1</v>
@@ -11445,10 +11442,10 @@
     </row>
     <row r="531" spans="1:8">
       <c r="A531" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B531" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C531">
         <v>0.1</v>
@@ -11497,12 +11494,12 @@
     </row>
     <row r="534" spans="1:8">
       <c r="A534" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="535" spans="1:8">
       <c r="B535" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C535" s="1" t="s">
         <v>34</v>
@@ -11629,10 +11626,10 @@
     </row>
     <row r="540" spans="1:8">
       <c r="A540" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B540" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C540">
         <v>0.3</v>
@@ -11785,10 +11782,10 @@
     </row>
     <row r="546" spans="1:8">
       <c r="A546" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B546" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C546">
         <v>-0.4</v>
@@ -11837,12 +11834,12 @@
     </row>
     <row r="549" spans="1:8">
       <c r="A549" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="550" spans="1:8">
       <c r="B550" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C550" s="1" t="s">
         <v>34</v>
@@ -11969,10 +11966,10 @@
     </row>
     <row r="555" spans="1:8">
       <c r="A555" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B555" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C555">
         <v>-0.6</v>
@@ -12125,10 +12122,10 @@
     </row>
     <row r="561" spans="1:8">
       <c r="A561" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B561" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C561">
         <v>0.6</v>
@@ -12177,7 +12174,7 @@
     </row>
     <row r="564" spans="1:8">
       <c r="A564" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="565" spans="1:8">
@@ -12199,7 +12196,7 @@
     </row>
     <row r="566" spans="1:8">
       <c r="A566" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B566" s="1" t="s">
         <v>40</v>
@@ -12223,7 +12220,7 @@
     <row r="567" spans="1:8">
       <c r="A567" s="1"/>
       <c r="B567" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C567">
         <v>0.1</v>
@@ -12355,7 +12352,7 @@
     <row r="574" spans="1:8">
       <c r="A574" s="1"/>
       <c r="B574" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C574">
         <v>0.5</v>
@@ -12429,7 +12426,7 @@
     </row>
     <row r="578" spans="1:7">
       <c r="A578" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B578" s="1" t="s">
         <v>40</v>
@@ -12450,7 +12447,7 @@
     <row r="579" spans="1:7">
       <c r="A579" s="1"/>
       <c r="B579" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C579">
         <v>0.5</v>
@@ -12582,7 +12579,7 @@
     <row r="586" spans="1:7">
       <c r="A586" s="1"/>
       <c r="B586" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C586">
         <v>0.1</v>
@@ -12656,7 +12653,7 @@
     </row>
     <row r="590" spans="1:7">
       <c r="A590" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B590" s="1" t="s">
         <v>40</v>
@@ -12680,7 +12677,7 @@
     <row r="591" spans="1:7">
       <c r="A591" s="1"/>
       <c r="B591" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C591">
         <v>0</v>
@@ -12815,7 +12812,7 @@
     <row r="598" spans="1:7">
       <c r="A598" s="1"/>
       <c r="B598" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C598">
         <v>0.3</v>
@@ -12886,7 +12883,7 @@
     </row>
     <row r="602" spans="1:7">
       <c r="A602" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B602" s="1" t="s">
         <v>40</v>
@@ -12910,7 +12907,7 @@
     <row r="603" spans="1:7">
       <c r="A603" s="1"/>
       <c r="B603" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C603">
         <v>0.5</v>
@@ -13036,7 +13033,7 @@
     <row r="610" spans="1:7">
       <c r="A610" s="1"/>
       <c r="B610" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C610">
         <v>0.6</v>
@@ -13110,7 +13107,7 @@
     </row>
     <row r="614" spans="1:7">
       <c r="A614" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B614" s="1" t="s">
         <v>40</v>
@@ -13134,7 +13131,7 @@
     <row r="615" spans="1:7">
       <c r="A615" s="1"/>
       <c r="B615" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C615">
         <v>0</v>
@@ -13269,7 +13266,7 @@
     <row r="622" spans="1:7">
       <c r="A622" s="1"/>
       <c r="B622" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C622">
         <v>0.2</v>
@@ -13346,7 +13343,7 @@
     </row>
     <row r="626" spans="1:7">
       <c r="A626" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B626" s="1" t="s">
         <v>40</v>
@@ -13370,7 +13367,7 @@
     <row r="627" spans="1:7">
       <c r="A627" s="1"/>
       <c r="B627" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C627">
         <v>0.4</v>
@@ -13505,7 +13502,7 @@
     <row r="634" spans="1:7">
       <c r="A634" s="1"/>
       <c r="B634" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C634">
         <v>1</v>

--- a/assets_output/07_multinomial_logistic_regression.xlsx
+++ b/assets_output/07_multinomial_logistic_regression.xlsx
@@ -49,7 +49,7 @@
     <t>y</t>
   </si>
   <si>
-    <t>2026-05-31 11:22</t>
+    <t>2026-05-31 15:09</t>
   </si>
   <si>
     <t>3391</t>

--- a/assets_output/07_multinomial_logistic_regression.xlsx
+++ b/assets_output/07_multinomial_logistic_regression.xlsx
@@ -49,7 +49,7 @@
     <t>y</t>
   </si>
   <si>
-    <t>2026-05-31 15:09</t>
+    <t>2026-05-31 15:16</t>
   </si>
   <si>
     <t>3391</t>

--- a/assets_output/07_multinomial_logistic_regression.xlsx
+++ b/assets_output/07_multinomial_logistic_regression.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="186">
   <si>
     <t>MNLogit: 'Entry point into BAHSA services (pathway type and level)', table 0</t>
   </si>
@@ -49,7 +49,7 @@
     <t>y</t>
   </si>
   <si>
-    <t>2026-05-31 15:16</t>
+    <t>2026-06-01 21:48</t>
   </si>
   <si>
     <t>3391</t>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>rt_outcome</t>
+  </si>
+  <si>
+    <t>2026-06-01 21:49</t>
   </si>
   <si>
     <t>2195</t>
@@ -5371,7 +5374,7 @@
         <v>18</v>
       </c>
       <c r="E213" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -5382,13 +5385,13 @@
         <v>3</v>
       </c>
       <c r="C214" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="D214" t="s">
         <v>19</v>
       </c>
       <c r="E214" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -5399,13 +5402,13 @@
         <v>4</v>
       </c>
       <c r="C215" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D215" t="s">
         <v>20</v>
       </c>
       <c r="E215" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="216" spans="1:8">
@@ -5416,13 +5419,13 @@
         <v>5</v>
       </c>
       <c r="C216" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D216" t="s">
         <v>21</v>
       </c>
       <c r="E216" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="217" spans="1:8">
@@ -5433,13 +5436,13 @@
         <v>6</v>
       </c>
       <c r="C217" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D217" t="s">
         <v>22</v>
       </c>
       <c r="E217" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -5456,7 +5459,7 @@
         <v>23</v>
       </c>
       <c r="E218" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -5467,7 +5470,7 @@
         <v>8</v>
       </c>
       <c r="C219" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D219" t="s">
         <v>24</v>
@@ -5478,12 +5481,12 @@
     </row>
     <row r="221" spans="1:8">
       <c r="A221" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="222" spans="1:8">
       <c r="B222" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>34</v>
@@ -5610,10 +5613,10 @@
     </row>
     <row r="227" spans="1:8">
       <c r="A227" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B227" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C227">
         <v>0.3</v>
@@ -5740,10 +5743,10 @@
     </row>
     <row r="232" spans="1:8">
       <c r="A232" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B232" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C232">
         <v>1.7</v>
@@ -5792,12 +5795,12 @@
     </row>
     <row r="235" spans="1:8">
       <c r="A235" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="236" spans="1:8">
       <c r="B236" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>34</v>
@@ -5924,10 +5927,10 @@
     </row>
     <row r="241" spans="1:8">
       <c r="A241" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B241" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C241">
         <v>0.1</v>
@@ -6054,10 +6057,10 @@
     </row>
     <row r="246" spans="1:8">
       <c r="A246" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B246" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C246">
         <v>2</v>
@@ -6106,12 +6109,12 @@
     </row>
     <row r="249" spans="1:8">
       <c r="A249" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="250" spans="1:8">
       <c r="B250" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>34</v>
@@ -6238,10 +6241,10 @@
     </row>
     <row r="255" spans="1:8">
       <c r="A255" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B255" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C255">
         <v>-0.5</v>
@@ -6368,10 +6371,10 @@
     </row>
     <row r="260" spans="1:8">
       <c r="A260" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B260" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C260">
         <v>2.9</v>
@@ -6420,7 +6423,7 @@
     </row>
     <row r="263" spans="1:8">
       <c r="A263" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -6442,7 +6445,7 @@
     </row>
     <row r="265" spans="1:8">
       <c r="A265" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>40</v>
@@ -6466,7 +6469,7 @@
     <row r="266" spans="1:8">
       <c r="A266" s="1"/>
       <c r="B266" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C266">
         <v>0.3</v>
@@ -6574,7 +6577,7 @@
     <row r="272" spans="1:8">
       <c r="A272" s="1"/>
       <c r="B272" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C272">
         <v>0</v>
@@ -6651,7 +6654,7 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>40</v>
@@ -6675,7 +6678,7 @@
     <row r="277" spans="1:7">
       <c r="A277" s="1"/>
       <c r="B277" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C277">
         <v>0</v>
@@ -6798,7 +6801,7 @@
     <row r="283" spans="1:7">
       <c r="A283" s="1"/>
       <c r="B283" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C283">
         <v>0</v>
@@ -6878,7 +6881,7 @@
     </row>
     <row r="287" spans="1:7">
       <c r="A287" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B287" s="1" t="s">
         <v>40</v>
@@ -6902,7 +6905,7 @@
     <row r="288" spans="1:7">
       <c r="A288" s="1"/>
       <c r="B288" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C288">
         <v>0.3</v>
@@ -7019,7 +7022,7 @@
     <row r="294" spans="1:7">
       <c r="A294" s="1"/>
       <c r="B294" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C294">
         <v>0</v>
@@ -7099,7 +7102,7 @@
     </row>
     <row r="299" spans="1:7">
       <c r="A299" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="300" spans="1:7">
@@ -7141,13 +7144,13 @@
         <v>2</v>
       </c>
       <c r="C302" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D302" t="s">
         <v>18</v>
       </c>
       <c r="E302" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -7158,13 +7161,13 @@
         <v>3</v>
       </c>
       <c r="C303" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="D303" t="s">
         <v>19</v>
       </c>
       <c r="E303" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="304" spans="1:7">
@@ -7175,13 +7178,13 @@
         <v>4</v>
       </c>
       <c r="C304" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D304" t="s">
         <v>20</v>
       </c>
       <c r="E304" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -7192,13 +7195,13 @@
         <v>5</v>
       </c>
       <c r="C305" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D305" t="s">
         <v>21</v>
       </c>
       <c r="E305" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -7209,13 +7212,13 @@
         <v>6</v>
       </c>
       <c r="C306" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D306" t="s">
         <v>22</v>
       </c>
       <c r="E306" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="307" spans="1:8">
@@ -7232,7 +7235,7 @@
         <v>23</v>
       </c>
       <c r="E307" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="308" spans="1:8">
@@ -7243,7 +7246,7 @@
         <v>8</v>
       </c>
       <c r="C308" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D308" t="s">
         <v>24</v>
@@ -7254,12 +7257,12 @@
     </row>
     <row r="310" spans="1:8">
       <c r="A310" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="311" spans="1:8">
       <c r="B311" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>34</v>
@@ -7360,10 +7363,10 @@
     </row>
     <row r="315" spans="1:8">
       <c r="A315" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B315" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C315">
         <v>0.3</v>
@@ -7490,10 +7493,10 @@
     </row>
     <row r="320" spans="1:8">
       <c r="A320" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B320" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C320">
         <v>1.7</v>
@@ -7516,12 +7519,12 @@
     </row>
     <row r="322" spans="1:8">
       <c r="A322" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="323" spans="1:8">
       <c r="B323" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>34</v>
@@ -7622,10 +7625,10 @@
     </row>
     <row r="327" spans="1:8">
       <c r="A327" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B327" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C327">
         <v>0.2</v>
@@ -7752,10 +7755,10 @@
     </row>
     <row r="332" spans="1:8">
       <c r="A332" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B332" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C332">
         <v>1.8</v>
@@ -7778,12 +7781,12 @@
     </row>
     <row r="334" spans="1:8">
       <c r="A334" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="335" spans="1:8">
       <c r="B335" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>34</v>
@@ -7884,10 +7887,10 @@
     </row>
     <row r="339" spans="1:8">
       <c r="A339" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B339" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C339">
         <v>-0.5</v>
@@ -8014,10 +8017,10 @@
     </row>
     <row r="344" spans="1:8">
       <c r="A344" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B344" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C344">
         <v>2.2</v>
@@ -8040,7 +8043,7 @@
     </row>
     <row r="346" spans="1:8">
       <c r="A346" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="347" spans="1:8">
@@ -8062,7 +8065,7 @@
     </row>
     <row r="348" spans="1:8">
       <c r="A348" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B348" s="1" t="s">
         <v>40</v>
@@ -8086,7 +8089,7 @@
     <row r="349" spans="1:8">
       <c r="A349" s="1"/>
       <c r="B349" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C349">
         <v>0.3</v>
@@ -8158,7 +8161,7 @@
     <row r="353" spans="1:7">
       <c r="A353" s="1"/>
       <c r="B353" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C353">
         <v>0.1</v>
@@ -8232,7 +8235,7 @@
     </row>
     <row r="357" spans="1:7">
       <c r="A357" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B357" s="1" t="s">
         <v>40</v>
@@ -8256,7 +8259,7 @@
     <row r="358" spans="1:7">
       <c r="A358" s="1"/>
       <c r="B358" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C358">
         <v>0</v>
@@ -8340,7 +8343,7 @@
     <row r="362" spans="1:7">
       <c r="A362" s="1"/>
       <c r="B362" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C362">
         <v>0</v>
@@ -8420,7 +8423,7 @@
     </row>
     <row r="366" spans="1:7">
       <c r="A366" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>40</v>
@@ -8444,7 +8447,7 @@
     <row r="367" spans="1:7">
       <c r="A367" s="1"/>
       <c r="B367" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C367">
         <v>0.1</v>
@@ -8522,7 +8525,7 @@
     <row r="371" spans="1:7">
       <c r="A371" s="1"/>
       <c r="B371" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C371">
         <v>0</v>
@@ -8602,7 +8605,7 @@
     </row>
     <row r="376" spans="1:7">
       <c r="A376" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="377" spans="1:7">
@@ -8627,7 +8630,7 @@
         <v>1</v>
       </c>
       <c r="C378" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D378" t="s">
         <v>17</v>
@@ -8644,13 +8647,13 @@
         <v>2</v>
       </c>
       <c r="C379" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D379" t="s">
         <v>18</v>
       </c>
       <c r="E379" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="380" spans="1:7">
@@ -8661,13 +8664,13 @@
         <v>3</v>
       </c>
       <c r="C380" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="D380" t="s">
         <v>19</v>
       </c>
       <c r="E380" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="381" spans="1:7">
@@ -8678,13 +8681,13 @@
         <v>4</v>
       </c>
       <c r="C381" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D381" t="s">
         <v>20</v>
       </c>
       <c r="E381" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="382" spans="1:7">
@@ -8695,13 +8698,13 @@
         <v>5</v>
       </c>
       <c r="C382" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D382" t="s">
         <v>21</v>
       </c>
       <c r="E382" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="383" spans="1:7">
@@ -8712,13 +8715,13 @@
         <v>6</v>
       </c>
       <c r="C383" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D383" t="s">
         <v>22</v>
       </c>
       <c r="E383" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="384" spans="1:7">
@@ -8735,7 +8738,7 @@
         <v>23</v>
       </c>
       <c r="E384" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="385" spans="1:7">
@@ -8746,7 +8749,7 @@
         <v>8</v>
       </c>
       <c r="C385" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D385" t="s">
         <v>24</v>
@@ -8757,7 +8760,7 @@
     </row>
     <row r="387" spans="1:7">
       <c r="A387" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="388" spans="1:7">
@@ -8768,10 +8771,10 @@
         <v>35</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F388" s="1" t="s">
         <v>38</v>
@@ -8805,7 +8808,7 @@
     </row>
     <row r="390" spans="1:7">
       <c r="A390" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B390">
         <v>0.4</v>
@@ -8920,7 +8923,7 @@
     </row>
     <row r="395" spans="1:7">
       <c r="A395" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B395">
         <v>0.8</v>
@@ -8943,7 +8946,7 @@
     </row>
     <row r="397" spans="1:7">
       <c r="A397" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="398" spans="1:7">
@@ -8985,7 +8988,7 @@
     </row>
     <row r="400" spans="1:7">
       <c r="A400" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B400">
         <v>0</v>
@@ -9065,7 +9068,7 @@
     </row>
     <row r="404" spans="1:6">
       <c r="A404" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B404">
         <v>0</v>
@@ -9105,7 +9108,7 @@
     </row>
     <row r="407" spans="1:6">
       <c r="A407" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="408" spans="1:6">
@@ -9130,7 +9133,7 @@
         <v>1</v>
       </c>
       <c r="C409" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D409" t="s">
         <v>17</v>
@@ -9147,13 +9150,13 @@
         <v>2</v>
       </c>
       <c r="C410" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D410" t="s">
         <v>18</v>
       </c>
       <c r="E410" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="411" spans="1:6">
@@ -9164,13 +9167,13 @@
         <v>3</v>
       </c>
       <c r="C411" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="D411" t="s">
         <v>19</v>
       </c>
       <c r="E411" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="412" spans="1:6">
@@ -9181,13 +9184,13 @@
         <v>4</v>
       </c>
       <c r="C412" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D412" t="s">
         <v>20</v>
       </c>
       <c r="E412" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="413" spans="1:6">
@@ -9198,13 +9201,13 @@
         <v>5</v>
       </c>
       <c r="C413" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D413" t="s">
         <v>21</v>
       </c>
       <c r="E413" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="414" spans="1:6">
@@ -9215,13 +9218,13 @@
         <v>6</v>
       </c>
       <c r="C414" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D414" t="s">
         <v>22</v>
       </c>
       <c r="E414" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="415" spans="1:6">
@@ -9238,7 +9241,7 @@
         <v>23</v>
       </c>
       <c r="E415" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="416" spans="1:6">
@@ -9249,7 +9252,7 @@
         <v>8</v>
       </c>
       <c r="C416" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D416" t="s">
         <v>24</v>
@@ -9260,7 +9263,7 @@
     </row>
     <row r="418" spans="1:7">
       <c r="A418" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="419" spans="1:7">
@@ -9271,10 +9274,10 @@
         <v>35</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F419" s="1" t="s">
         <v>38</v>
@@ -9331,7 +9334,7 @@
     </row>
     <row r="422" spans="1:7">
       <c r="A422" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B422">
         <v>-0.5</v>
@@ -9446,7 +9449,7 @@
     </row>
     <row r="428" spans="1:7">
       <c r="A428" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="429" spans="1:7">
@@ -9488,7 +9491,7 @@
     </row>
     <row r="431" spans="1:7">
       <c r="A431" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B431">
         <v>0</v>
@@ -9608,7 +9611,7 @@
     </row>
     <row r="438" spans="1:6">
       <c r="A438" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="439" spans="1:6">
@@ -9633,7 +9636,7 @@
         <v>1</v>
       </c>
       <c r="C440" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D440" t="s">
         <v>17</v>
@@ -9650,13 +9653,13 @@
         <v>2</v>
       </c>
       <c r="C441" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D441" t="s">
         <v>18</v>
       </c>
       <c r="E441" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="442" spans="1:6">
@@ -9667,13 +9670,13 @@
         <v>3</v>
       </c>
       <c r="C442" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="D442" t="s">
         <v>19</v>
       </c>
       <c r="E442" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="443" spans="1:6">
@@ -9684,13 +9687,13 @@
         <v>4</v>
       </c>
       <c r="C443" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D443" t="s">
         <v>20</v>
       </c>
       <c r="E443" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="444" spans="1:6">
@@ -9701,13 +9704,13 @@
         <v>5</v>
       </c>
       <c r="C444" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D444" t="s">
         <v>21</v>
       </c>
       <c r="E444" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="445" spans="1:6">
@@ -9718,13 +9721,13 @@
         <v>6</v>
       </c>
       <c r="C445" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D445" t="s">
         <v>22</v>
       </c>
       <c r="E445" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="446" spans="1:6">
@@ -9741,7 +9744,7 @@
         <v>23</v>
       </c>
       <c r="E446" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="447" spans="1:6">
@@ -9752,7 +9755,7 @@
         <v>8</v>
       </c>
       <c r="C447" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D447" t="s">
         <v>24</v>
@@ -9763,7 +9766,7 @@
     </row>
     <row r="449" spans="1:7">
       <c r="A449" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="450" spans="1:7">
@@ -9774,10 +9777,10 @@
         <v>35</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F450" s="1" t="s">
         <v>38</v>
@@ -9880,7 +9883,7 @@
     </row>
     <row r="456" spans="1:7">
       <c r="A456" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="457" spans="1:7">
@@ -9979,7 +9982,7 @@
     </row>
     <row r="463" spans="1:7">
       <c r="A463" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="464" spans="1:7">
@@ -10021,13 +10024,13 @@
         <v>2</v>
       </c>
       <c r="C466" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D466" t="s">
         <v>18</v>
       </c>
       <c r="E466" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="467" spans="1:8">
@@ -10038,13 +10041,13 @@
         <v>3</v>
       </c>
       <c r="C467" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="D467" t="s">
         <v>19</v>
       </c>
       <c r="E467" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="468" spans="1:8">
@@ -10055,13 +10058,13 @@
         <v>4</v>
       </c>
       <c r="C468" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D468" t="s">
         <v>20</v>
       </c>
       <c r="E468" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="469" spans="1:8">
@@ -10072,13 +10075,13 @@
         <v>5</v>
       </c>
       <c r="C469" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D469" t="s">
         <v>21</v>
       </c>
       <c r="E469" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="470" spans="1:8">
@@ -10089,13 +10092,13 @@
         <v>6</v>
       </c>
       <c r="C470" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D470" t="s">
         <v>22</v>
       </c>
       <c r="E470" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="471" spans="1:8">
@@ -10112,7 +10115,7 @@
         <v>23</v>
       </c>
       <c r="E471" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="472" spans="1:8">
@@ -10134,12 +10137,12 @@
     </row>
     <row r="474" spans="1:8">
       <c r="A474" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="475" spans="1:8">
       <c r="B475" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C475" s="1" t="s">
         <v>34</v>
@@ -10266,10 +10269,10 @@
     </row>
     <row r="480" spans="1:8">
       <c r="A480" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B480" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C480">
         <v>-0.1</v>
@@ -10422,10 +10425,10 @@
     </row>
     <row r="486" spans="1:8">
       <c r="A486" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B486" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C486">
         <v>-1.1</v>
@@ -10474,12 +10477,12 @@
     </row>
     <row r="489" spans="1:8">
       <c r="A489" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="490" spans="1:8">
       <c r="B490" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C490" s="1" t="s">
         <v>34</v>
@@ -10606,10 +10609,10 @@
     </row>
     <row r="495" spans="1:8">
       <c r="A495" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B495" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C495">
         <v>0.4</v>
@@ -10762,10 +10765,10 @@
     </row>
     <row r="501" spans="1:8">
       <c r="A501" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B501" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C501">
         <v>0.3</v>
@@ -10814,12 +10817,12 @@
     </row>
     <row r="504" spans="1:8">
       <c r="A504" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="505" spans="1:8">
       <c r="B505" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C505" s="1" t="s">
         <v>34</v>
@@ -10946,10 +10949,10 @@
     </row>
     <row r="510" spans="1:8">
       <c r="A510" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B510" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C510">
         <v>0.1</v>
@@ -11102,10 +11105,10 @@
     </row>
     <row r="516" spans="1:8">
       <c r="A516" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B516" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C516">
         <v>0</v>
@@ -11154,12 +11157,12 @@
     </row>
     <row r="519" spans="1:8">
       <c r="A519" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="520" spans="1:8">
       <c r="B520" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C520" s="1" t="s">
         <v>34</v>
@@ -11286,10 +11289,10 @@
     </row>
     <row r="525" spans="1:8">
       <c r="A525" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B525" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C525">
         <v>0.1</v>
@@ -11442,10 +11445,10 @@
     </row>
     <row r="531" spans="1:8">
       <c r="A531" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B531" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C531">
         <v>0.1</v>
@@ -11494,12 +11497,12 @@
     </row>
     <row r="534" spans="1:8">
       <c r="A534" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="535" spans="1:8">
       <c r="B535" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C535" s="1" t="s">
         <v>34</v>
@@ -11626,10 +11629,10 @@
     </row>
     <row r="540" spans="1:8">
       <c r="A540" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B540" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C540">
         <v>0.3</v>
@@ -11782,10 +11785,10 @@
     </row>
     <row r="546" spans="1:8">
       <c r="A546" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B546" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C546">
         <v>-0.4</v>
@@ -11834,12 +11837,12 @@
     </row>
     <row r="549" spans="1:8">
       <c r="A549" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="550" spans="1:8">
       <c r="B550" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C550" s="1" t="s">
         <v>34</v>
@@ -11966,10 +11969,10 @@
     </row>
     <row r="555" spans="1:8">
       <c r="A555" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B555" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C555">
         <v>-0.6</v>
@@ -12122,10 +12125,10 @@
     </row>
     <row r="561" spans="1:8">
       <c r="A561" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B561" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C561">
         <v>0.6</v>
@@ -12174,7 +12177,7 @@
     </row>
     <row r="564" spans="1:8">
       <c r="A564" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="565" spans="1:8">
@@ -12196,7 +12199,7 @@
     </row>
     <row r="566" spans="1:8">
       <c r="A566" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B566" s="1" t="s">
         <v>40</v>
@@ -12220,7 +12223,7 @@
     <row r="567" spans="1:8">
       <c r="A567" s="1"/>
       <c r="B567" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C567">
         <v>0.1</v>
@@ -12352,7 +12355,7 @@
     <row r="574" spans="1:8">
       <c r="A574" s="1"/>
       <c r="B574" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C574">
         <v>0.5</v>
@@ -12426,7 +12429,7 @@
     </row>
     <row r="578" spans="1:7">
       <c r="A578" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B578" s="1" t="s">
         <v>40</v>
@@ -12447,7 +12450,7 @@
     <row r="579" spans="1:7">
       <c r="A579" s="1"/>
       <c r="B579" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C579">
         <v>0.5</v>
@@ -12579,7 +12582,7 @@
     <row r="586" spans="1:7">
       <c r="A586" s="1"/>
       <c r="B586" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C586">
         <v>0.1</v>
@@ -12653,7 +12656,7 @@
     </row>
     <row r="590" spans="1:7">
       <c r="A590" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B590" s="1" t="s">
         <v>40</v>
@@ -12677,7 +12680,7 @@
     <row r="591" spans="1:7">
       <c r="A591" s="1"/>
       <c r="B591" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C591">
         <v>0</v>
@@ -12812,7 +12815,7 @@
     <row r="598" spans="1:7">
       <c r="A598" s="1"/>
       <c r="B598" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C598">
         <v>0.3</v>
@@ -12883,7 +12886,7 @@
     </row>
     <row r="602" spans="1:7">
       <c r="A602" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B602" s="1" t="s">
         <v>40</v>
@@ -12907,7 +12910,7 @@
     <row r="603" spans="1:7">
       <c r="A603" s="1"/>
       <c r="B603" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C603">
         <v>0.5</v>
@@ -13033,7 +13036,7 @@
     <row r="610" spans="1:7">
       <c r="A610" s="1"/>
       <c r="B610" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C610">
         <v>0.6</v>
@@ -13107,7 +13110,7 @@
     </row>
     <row r="614" spans="1:7">
       <c r="A614" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B614" s="1" t="s">
         <v>40</v>
@@ -13131,7 +13134,7 @@
     <row r="615" spans="1:7">
       <c r="A615" s="1"/>
       <c r="B615" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C615">
         <v>0</v>
@@ -13266,7 +13269,7 @@
     <row r="622" spans="1:7">
       <c r="A622" s="1"/>
       <c r="B622" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C622">
         <v>0.2</v>
@@ -13343,7 +13346,7 @@
     </row>
     <row r="626" spans="1:7">
       <c r="A626" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B626" s="1" t="s">
         <v>40</v>
@@ -13367,7 +13370,7 @@
     <row r="627" spans="1:7">
       <c r="A627" s="1"/>
       <c r="B627" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C627">
         <v>0.4</v>
@@ -13502,7 +13505,7 @@
     <row r="634" spans="1:7">
       <c r="A634" s="1"/>
       <c r="B634" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C634">
         <v>1</v>
